--- a/민원데이터.xlsx
+++ b/민원데이터.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\바탕화면\코딩\민원관리 대시보드\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\바탕화면\박현식\박현식 개인\코딩\민원관리 대시보드\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C93A6E1B-D65C-4F59-BBC9-3FF08A3A4248}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24A17CE2-8D89-4DCC-AED3-0689CB1A392E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="390" yWindow="390" windowWidth="28470" windowHeight="15030" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1860" yWindow="615" windowWidth="26835" windowHeight="14145" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="420" uniqueCount="237">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="588" uniqueCount="324">
   <si>
     <t>민원번호</t>
   </si>
@@ -785,6 +785,360 @@
   </si>
   <si>
     <t>진행중</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>문기호</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>이재철</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>예정</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>다운~굴화 징검다리 안전대책 및 민원 접수 처리현황 문의</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>태화강국가정원 입구~스타벅스 건널목 일원 주정차량 발생 억제 목적 탄력봉 신규/이동/보수 설치 요청
+ - 불법주정차로 인한 보행자 시야 제한 발생하여 안전사고 발생 우려 높음</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>복산동 남운아파트 정류장(30912) 선풍기 미작동 수리 요청</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>성안동 상가번영회 주도 골목형상점가 등록 추진 중 온누리상품권 정산 방법 문의</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>도화골4길 62~울산새중앙교회 앞 모퉁이 공사장생활폐기물 처리 봉투 수거 요청</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>백양로 세계로마트 일원 가로수(은행나무) 가지치기 요청 (점포 간판 가림, 전선 간섭 발생 등 사유)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>학성로 227 일원 가로수(은행나무) 가지치기 요청 (점포 간판 가림, 전선 간섭 발생 등 사유)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>학성배수장 내 중구마을교육지원센터 입주로 화장실 수요 충족을 위한 공공 시설물(화장실) 개방 협조 요청</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>복산초~센트리지 3,4단지 교차로 건널목 앞 등굣길 그늘막 설치 요청</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>학성새벽시장 노상공영주차장 휴무일 변경 요청(현행 일,월,화 휴무 → 목,금,토,일로 변경 요청)
+ - 현행 유지시 월요일 새벽시간대 인근 주민 주차로 월정기이용자 이용 불가 상황 초래</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>충의사 내 대나무 제거 요청</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>명정공원~명정천 사이 횡단보도 일원 보행자 , 운전자 안전을 위한 교통안전시설 보강 필요</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>반구동 408-6 일원, 내황배수장 인근 데크 일원 등 주변 풀베기 요청</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>병영로 42 (뚱이횟집) 앞 도로에서 로드킬 동물 사체 처리 요청</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>성동1길 87 진입 농로변 나무 웃자람에 따른 전선 간섭 발생</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>복산동 광림빌라(손골1길 10) 방역 요청</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>유곡로 인근 상권 활성화 위해 불법주정차 단속 CCTV 운영시간 조정 요청</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>유곡로 22-2 거주자 주거환경 개선(도배, 장판 교체, 타일 보수 등) 요청에 따른 고충 청취</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>구역전시장 상인(춘자네가방) 전치26주 상당 사고로 영조물 배상 대상 여부 확인 요청</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>복산동 동덕현대아파트 101동 앞(손골2길, 손골3길 교차지점) 탄력봉 바닥 고정나사 미제거분 제거 요청</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>고지배수터널 공사 손해보험에 대한 홍보 부족 불만  ※현재 접수기한 경과로 접수 불가</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>자전거 탑승 중 사고 피해 발생 접수. 자전거 보험 보장범위 및 접수 방법 안내 요망</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>학성동 436-11 필지(구역전족발 등 상가) 조경면적 및 주차공간을 창고로 용도 변경시 가능여부와 절차 문의</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>장현산단 내 외솔큰길 시례동 방면, 공사 펜스 인접 가로등 점등상태 불량 다수 있음</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>북부순환도로 857 건물 신축 공사 중 파손된 동천4길 아스팔트 보수 요청</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>과거 병영 외솔기념관을 경유하는 지선 버스 노선 부활 요청</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>옥성공원 선풍기 고장으로 수리 요청</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>학성로 188 식당으로 용도변겅 가능여부 및 절차 문의
+ - 60년째 가설건축물로 영업행위, 세금 납부 상황에서 식당 용도 변경 희망</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>구 복산2동행정복지센터 인근에서 발생한 사고에 대해 사고자가 영조물 배상 대상에 해당하는지 확인 요청</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>곽남길 병영새마을금고 앞 횡단보도 보행자 신호 개설 요청</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>동천5길 출발농산~학생사 구간 배수로 및 꿀꿀이숯불석쇠구이 입구 아스콘 포장 요청</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>장현산단 진입도로 개설공사 현장 옆 외솔큰길 일부 구간 승용/대형/특수 차량 주정차 및 장기 방치, 공사 자재 등 적치물 다수로 환경정비 필요</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>동동 675번지 휴게쉼터 용도 변경(공용주차장 희망)
+ - 2025년 빈집정비사업으로 조성되었으나 ▲개방 공간으로 폭염, 한파, 우천에 취약 ▲파쇄석 바닥은 어르신 보행 불편 ▲진입로 연석 단차로 미끄럼 및 넘어짐 사고 빈번 ▲골목 협소, 주택 밀집 구간 거주자우선주차제 폐지 후 주차 갈등 빈번 ▲현장 방문 결과 진입로 정비 및 주차선 설치 작업만으로 저예산, 신속하게 조성 가능 판단</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>서동 385번지 휴게쉼터 용도 변경(운동시설 설치 희망)
+ - 2022년 빈집정비사업으로 그늘막 설치, 꽃나무 등 식재된 휴게쉼터이나 ▲관리소홀 ▲인접지 소공원 조성에 따른 기능 중복으로 활용도 및 실용성 저조. 어르신용 운동기구 설치 희망</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>(연번 416 민원인 재방문)성안동192-2 필지, 장기 미경작으로 인한 대나무 우거짐. 벌목희망하나 공유지분 소유자(공동소유인 사망 후 상속 배우자, 자녀4명) 동의서 징수 불가시 다른 방안 있는지 문의</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>사회적협동조합 설립 관련 절차 및 요건, 지원 방법 등 상담 문의</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>남외동 남외3길 해오름공원~에일린의뜰아파트 105동 사이 구간에서 하수 역류 발생으로 준설 등 조치 요청</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>병영모터스(병영로 82) 부지에 편의점으로 업종 변경 희망하나, 인근 담배소매업소로 등록된 업체 존재(동동 551번지)로 정리 필요한 상황. 진행 절차 및 직권폐지 요청
+ - 민원인(김경수)이 확인한 결과, 동동 551번지 거주자는 담배소매업소 등록 여부 모른다고 응답</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>성안동 함월6길 도로 재포장 요청(표면 박리로 인한 분진 피해 발생)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>북부순환도로~이예로~원유곡지하차도 방면 진입구간 교통섬에 설치된 '혁신도시'조명 완전 고장으로 정비 또는 철거 요청</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>울산 중구 다운동 831-1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>울산 중구 태화동 107</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>울산 중구 복산동 357</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>울산 중구 성안동 804-10</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>울산 중구 복산동 376-14</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>울산 중구 성안동 852-1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>울산 중구 학성동 331-14</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>울산 중구 학성동 471</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>울산 중구 복산동 444-13</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>울산 중구 학성동 349-25</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>울산 중구 학성동 45-1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>울산 중구 태화동 1061</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>울산 중구 반구동 408-6</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>울산 중구 동동 692-1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>울산 중구 성안동 1625</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>울산 중구 복산동 304-26</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>울산 중구 우정동 725-6</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>울산 중구 학성동 433-2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>울산 중구 태화동 40</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>울산 중구 복산동 677-17</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>울산 중구 태화동 110-13</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>울산 중구 복산동 180-1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>울산 중구 장현동 179-2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>울산 중구 서동 43-11</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>울산 중구 동동 613</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>울산 중구 학성동 432-351</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>울산 중구 복산동 358</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>울산 중구 약사동 625-36</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>울산 중구 서동 41-13</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>울산 중구 장현동 80</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>울산 중구 동동 675</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>울산 중구 서동 385</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>울산 중구 성안동 192-2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>울산 중구 서동 613</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>울산 중구 성남동 219-200</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>울산 중구 성남동 226-4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>구 소방서 부지(시/도유지) 물웅덩이 및 잡초 번식으로 모기 서식 환경임. 집중 방역 및 제초작업 요청.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>건설 예정 부지(법인 소유) 물웅덩이 및 잡초 번식으로 모기 서식 환경임. 집중 방역 및 제초작업 요청.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>울산 중구 남외동 517</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>울산 중구 동동 59</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>울산 중구 성안동 833-1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>울산 중구 유곡동 214-4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>진행중</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>장기과제</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -842,7 +1196,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -861,6 +1215,25 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1164,7 +1537,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H87"/>
+  <dimension ref="A1:H130"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="11.125" bestFit="1" customWidth="1"/>
@@ -3180,145 +3553,1043 @@
         <v>196</v>
       </c>
     </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A81">
+    <row r="81" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A81" s="7">
         <v>80</v>
       </c>
-      <c r="B81" s="1">
+      <c r="B81" s="8">
         <v>46164</v>
       </c>
-      <c r="C81" t="s">
+      <c r="C81" s="7" t="s">
         <v>199</v>
       </c>
-      <c r="D81" s="4" t="s">
+      <c r="D81" s="9" t="s">
         <v>192</v>
       </c>
-      <c r="E81" s="3" t="s">
+      <c r="E81" s="10" t="s">
         <v>195</v>
       </c>
-      <c r="F81" s="4" t="s">
+      <c r="F81" s="9" t="s">
         <v>236</v>
       </c>
-    </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A82">
+      <c r="G81" s="7"/>
+    </row>
+    <row r="82" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A82" s="7">
         <v>81</v>
       </c>
-      <c r="B82" s="1">
+      <c r="B82" s="8">
         <v>46168</v>
       </c>
-      <c r="C82" t="s">
+      <c r="C82" s="7" t="s">
         <v>198</v>
       </c>
-      <c r="D82" s="4" t="s">
+      <c r="D82" s="9" t="s">
         <v>193</v>
       </c>
-      <c r="E82" s="3" t="s">
+      <c r="E82" s="10" t="s">
         <v>194</v>
       </c>
-      <c r="F82" s="4" t="s">
+      <c r="F82" s="9" t="s">
         <v>196</v>
       </c>
-    </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A83">
+      <c r="G82" s="7"/>
+    </row>
+    <row r="83" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A83" s="7">
         <v>82</v>
       </c>
-      <c r="B83" s="1">
+      <c r="B83" s="8">
         <v>46168</v>
       </c>
-      <c r="C83" t="s">
+      <c r="C83" s="7" t="s">
         <v>197</v>
       </c>
-      <c r="D83" s="4" t="s">
+      <c r="D83" s="9" t="s">
         <v>216</v>
       </c>
-      <c r="E83" s="3" t="s">
+      <c r="E83" s="10" t="s">
         <v>194</v>
       </c>
-      <c r="F83" s="4" t="s">
+      <c r="F83" s="9" t="s">
         <v>196</v>
       </c>
-    </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A84">
+      <c r="G83" s="7"/>
+    </row>
+    <row r="84" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A84" s="7">
         <v>83</v>
       </c>
-      <c r="B84" s="1">
+      <c r="B84" s="8">
         <v>46169</v>
       </c>
-      <c r="C84" t="s">
+      <c r="C84" s="7" t="s">
         <v>203</v>
       </c>
-      <c r="D84" s="4" t="s">
+      <c r="D84" s="9" t="s">
         <v>217</v>
       </c>
-      <c r="E84" s="3" t="s">
+      <c r="E84" s="10" t="s">
         <v>194</v>
       </c>
-      <c r="F84" s="4" t="s">
+      <c r="F84" s="9" t="s">
         <v>196</v>
       </c>
-    </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A85">
+      <c r="G84" s="7"/>
+    </row>
+    <row r="85" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A85" s="7">
         <v>84</v>
       </c>
-      <c r="B85" s="1">
+      <c r="B85" s="8">
         <v>46170</v>
       </c>
-      <c r="C85" t="s">
+      <c r="C85" s="7" t="s">
         <v>233</v>
       </c>
-      <c r="D85" s="4" t="s">
+      <c r="D85" s="9" t="s">
         <v>218</v>
       </c>
-      <c r="E85" s="3" t="s">
+      <c r="E85" s="10" t="s">
         <v>209</v>
       </c>
-      <c r="F85" s="4" t="s">
+      <c r="F85" s="9" t="s">
         <v>196</v>
       </c>
-    </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A86">
+      <c r="G85" s="7"/>
+    </row>
+    <row r="86" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A86" s="7">
         <v>85</v>
       </c>
-      <c r="B86" s="1">
+      <c r="B86" s="8">
         <v>46171</v>
       </c>
-      <c r="C86" t="s">
+      <c r="C86" s="7" t="s">
         <v>234</v>
       </c>
-      <c r="D86" s="4" t="s">
+      <c r="D86" s="9" t="s">
         <v>219</v>
       </c>
-      <c r="E86" s="3" t="s">
+      <c r="E86" s="10" t="s">
         <v>194</v>
       </c>
-      <c r="F86" s="4" t="s">
+      <c r="F86" s="9" t="s">
         <v>196</v>
       </c>
-    </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A87">
+      <c r="G86" s="7"/>
+    </row>
+    <row r="87" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A87" s="7">
         <v>86</v>
       </c>
-      <c r="B87" s="1">
+      <c r="B87" s="8">
         <v>46171</v>
       </c>
-      <c r="C87" t="s">
+      <c r="C87" s="7" t="s">
         <v>235</v>
       </c>
-      <c r="D87" s="4" t="s">
+      <c r="D87" s="9" t="s">
         <v>220</v>
       </c>
-      <c r="E87" s="3" t="s">
+      <c r="E87" s="10" t="s">
         <v>194</v>
       </c>
-      <c r="F87" s="4" t="s">
+      <c r="F87" s="9" t="s">
         <v>236</v>
       </c>
+      <c r="G87" s="7"/>
+    </row>
+    <row r="88" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A88" s="7">
+        <v>87</v>
+      </c>
+      <c r="B88" s="8">
+        <v>46181</v>
+      </c>
+      <c r="C88" s="7" t="s">
+        <v>280</v>
+      </c>
+      <c r="D88" s="9" t="s">
+        <v>240</v>
+      </c>
+      <c r="E88" s="10" t="s">
+        <v>208</v>
+      </c>
+      <c r="F88" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="G88" s="7"/>
+    </row>
+    <row r="89" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+      <c r="A89" s="7">
+        <v>88</v>
+      </c>
+      <c r="B89" s="8">
+        <v>46182</v>
+      </c>
+      <c r="C89" s="7" t="s">
+        <v>281</v>
+      </c>
+      <c r="D89" s="11" t="s">
+        <v>241</v>
+      </c>
+      <c r="E89" s="10" t="s">
+        <v>208</v>
+      </c>
+      <c r="F89" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="G89" s="7"/>
+    </row>
+    <row r="90" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A90" s="7">
+        <v>89</v>
+      </c>
+      <c r="B90" s="8">
+        <v>46184</v>
+      </c>
+      <c r="C90" s="12" t="s">
+        <v>282</v>
+      </c>
+      <c r="D90" s="13" t="s">
+        <v>242</v>
+      </c>
+      <c r="E90" s="10" t="s">
+        <v>194</v>
+      </c>
+      <c r="F90" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="G90" s="7"/>
+    </row>
+    <row r="91" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A91" s="7">
+        <v>90</v>
+      </c>
+      <c r="B91" s="8">
+        <v>46185</v>
+      </c>
+      <c r="C91" s="7" t="s">
+        <v>283</v>
+      </c>
+      <c r="D91" s="13" t="s">
+        <v>243</v>
+      </c>
+      <c r="E91" s="10" t="s">
+        <v>194</v>
+      </c>
+      <c r="F91" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="G91" s="7"/>
+    </row>
+    <row r="92" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A92" s="7">
+        <v>91</v>
+      </c>
+      <c r="B92" s="8">
+        <v>46188</v>
+      </c>
+      <c r="C92" s="7" t="s">
+        <v>284</v>
+      </c>
+      <c r="D92" s="13" t="s">
+        <v>244</v>
+      </c>
+      <c r="E92" s="10" t="s">
+        <v>194</v>
+      </c>
+      <c r="F92" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="G92" s="7"/>
+    </row>
+    <row r="93" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A93" s="7">
+        <v>92</v>
+      </c>
+      <c r="B93" s="8">
+        <v>46188</v>
+      </c>
+      <c r="C93" s="12" t="s">
+        <v>285</v>
+      </c>
+      <c r="D93" s="13" t="s">
+        <v>245</v>
+      </c>
+      <c r="E93" s="10" t="s">
+        <v>194</v>
+      </c>
+      <c r="F93" s="10" t="s">
+        <v>239</v>
+      </c>
+      <c r="G93" s="7"/>
+    </row>
+    <row r="94" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A94" s="7">
+        <v>93</v>
+      </c>
+      <c r="B94" s="8">
+        <v>46188</v>
+      </c>
+      <c r="C94" s="7" t="s">
+        <v>286</v>
+      </c>
+      <c r="D94" s="13" t="s">
+        <v>246</v>
+      </c>
+      <c r="E94" s="10" t="s">
+        <v>194</v>
+      </c>
+      <c r="F94" s="10" t="s">
+        <v>239</v>
+      </c>
+      <c r="G94" s="7"/>
+    </row>
+    <row r="95" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A95" s="7">
+        <v>94</v>
+      </c>
+      <c r="B95" s="8">
+        <v>46188</v>
+      </c>
+      <c r="C95" s="7" t="s">
+        <v>287</v>
+      </c>
+      <c r="D95" s="13" t="s">
+        <v>247</v>
+      </c>
+      <c r="E95" s="10" t="s">
+        <v>194</v>
+      </c>
+      <c r="F95" s="10" t="s">
+        <v>221</v>
+      </c>
+      <c r="G95" s="7"/>
+    </row>
+    <row r="96" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A96" s="7">
+        <v>95</v>
+      </c>
+      <c r="B96" s="8">
+        <v>46188</v>
+      </c>
+      <c r="C96" s="7" t="s">
+        <v>288</v>
+      </c>
+      <c r="D96" s="13" t="s">
+        <v>248</v>
+      </c>
+      <c r="E96" s="10" t="s">
+        <v>194</v>
+      </c>
+      <c r="F96" s="10" t="s">
+        <v>236</v>
+      </c>
+      <c r="G96" s="7"/>
+    </row>
+    <row r="97" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+      <c r="A97" s="7">
+        <v>96</v>
+      </c>
+      <c r="B97" s="8">
+        <v>46188</v>
+      </c>
+      <c r="C97" s="7" t="s">
+        <v>289</v>
+      </c>
+      <c r="D97" s="11" t="s">
+        <v>249</v>
+      </c>
+      <c r="E97" s="10" t="s">
+        <v>194</v>
+      </c>
+      <c r="F97" s="10" t="s">
+        <v>236</v>
+      </c>
+      <c r="G97" s="7"/>
+    </row>
+    <row r="98" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A98" s="7">
+        <v>97</v>
+      </c>
+      <c r="B98" s="8">
+        <v>46188</v>
+      </c>
+      <c r="C98" s="7" t="s">
+        <v>290</v>
+      </c>
+      <c r="D98" s="13" t="s">
+        <v>250</v>
+      </c>
+      <c r="E98" s="10" t="s">
+        <v>194</v>
+      </c>
+      <c r="F98" s="10" t="s">
+        <v>221</v>
+      </c>
+      <c r="G98" s="7"/>
+    </row>
+    <row r="99" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A99" s="7">
+        <v>98</v>
+      </c>
+      <c r="B99" s="8">
+        <v>46190</v>
+      </c>
+      <c r="C99" s="7" t="s">
+        <v>291</v>
+      </c>
+      <c r="D99" s="9" t="s">
+        <v>251</v>
+      </c>
+      <c r="E99" s="10" t="s">
+        <v>237</v>
+      </c>
+      <c r="F99" s="13" t="s">
+        <v>322</v>
+      </c>
+      <c r="G99" s="7"/>
+    </row>
+    <row r="100" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A100" s="7">
+        <v>99</v>
+      </c>
+      <c r="B100" s="8">
+        <v>46190</v>
+      </c>
+      <c r="C100" s="7" t="s">
+        <v>292</v>
+      </c>
+      <c r="D100" s="9" t="s">
+        <v>252</v>
+      </c>
+      <c r="E100" s="10" t="s">
+        <v>209</v>
+      </c>
+      <c r="F100" s="10" t="s">
+        <v>239</v>
+      </c>
+      <c r="G100" s="7"/>
+    </row>
+    <row r="101" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A101" s="7">
+        <v>100</v>
+      </c>
+      <c r="B101" s="8">
+        <v>46191</v>
+      </c>
+      <c r="C101" s="7" t="s">
+        <v>293</v>
+      </c>
+      <c r="D101" s="13" t="s">
+        <v>253</v>
+      </c>
+      <c r="E101" s="10" t="s">
+        <v>194</v>
+      </c>
+      <c r="F101" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="G101" s="7"/>
+    </row>
+    <row r="102" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A102" s="7">
+        <v>101</v>
+      </c>
+      <c r="B102" s="8">
+        <v>46195</v>
+      </c>
+      <c r="C102" s="7" t="s">
+        <v>294</v>
+      </c>
+      <c r="D102" s="13" t="s">
+        <v>254</v>
+      </c>
+      <c r="E102" s="10" t="s">
+        <v>194</v>
+      </c>
+      <c r="F102" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="G102" s="7"/>
+    </row>
+    <row r="103" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A103" s="7">
+        <v>102</v>
+      </c>
+      <c r="B103" s="8">
+        <v>46195</v>
+      </c>
+      <c r="C103" s="7" t="s">
+        <v>295</v>
+      </c>
+      <c r="D103" s="13" t="s">
+        <v>255</v>
+      </c>
+      <c r="E103" s="10" t="s">
+        <v>194</v>
+      </c>
+      <c r="F103" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="G103" s="7"/>
+    </row>
+    <row r="104" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A104" s="7">
+        <v>103</v>
+      </c>
+      <c r="B104" s="8">
+        <v>46196</v>
+      </c>
+      <c r="C104" s="7" t="s">
+        <v>298</v>
+      </c>
+      <c r="D104" s="9" t="s">
+        <v>256</v>
+      </c>
+      <c r="E104" s="10" t="s">
+        <v>237</v>
+      </c>
+      <c r="F104" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="G104" s="7"/>
+    </row>
+    <row r="105" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A105" s="7">
+        <v>104</v>
+      </c>
+      <c r="B105" s="8">
+        <v>46197</v>
+      </c>
+      <c r="C105" s="7" t="s">
+        <v>296</v>
+      </c>
+      <c r="D105" s="13" t="s">
+        <v>257</v>
+      </c>
+      <c r="E105" s="10" t="s">
+        <v>194</v>
+      </c>
+      <c r="F105" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="G105" s="7"/>
+    </row>
+    <row r="106" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A106" s="7">
+        <v>105</v>
+      </c>
+      <c r="B106" s="8">
+        <v>46197</v>
+      </c>
+      <c r="C106" s="7" t="s">
+        <v>297</v>
+      </c>
+      <c r="D106" s="13" t="s">
+        <v>258</v>
+      </c>
+      <c r="E106" s="10" t="s">
+        <v>194</v>
+      </c>
+      <c r="F106" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="G106" s="7"/>
+    </row>
+    <row r="107" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A107" s="7">
+        <v>106</v>
+      </c>
+      <c r="B107" s="8">
+        <v>46198</v>
+      </c>
+      <c r="C107" s="7" t="s">
+        <v>299</v>
+      </c>
+      <c r="D107" s="13" t="s">
+        <v>259</v>
+      </c>
+      <c r="E107" s="10" t="s">
+        <v>194</v>
+      </c>
+      <c r="F107" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="G107" s="7"/>
+    </row>
+    <row r="108" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A108" s="7">
+        <v>107</v>
+      </c>
+      <c r="B108" s="8">
+        <v>46198</v>
+      </c>
+      <c r="C108" s="7" t="s">
+        <v>300</v>
+      </c>
+      <c r="D108" s="9" t="s">
+        <v>260</v>
+      </c>
+      <c r="E108" s="10" t="s">
+        <v>237</v>
+      </c>
+      <c r="F108" s="10" t="s">
+        <v>221</v>
+      </c>
+      <c r="G108" s="7"/>
+    </row>
+    <row r="109" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A109" s="7">
+        <v>108</v>
+      </c>
+      <c r="B109" s="8">
+        <v>46204</v>
+      </c>
+      <c r="C109" s="7" t="s">
+        <v>301</v>
+      </c>
+      <c r="D109" s="13" t="s">
+        <v>261</v>
+      </c>
+      <c r="E109" s="10" t="s">
+        <v>194</v>
+      </c>
+      <c r="F109" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="G109" s="7"/>
+    </row>
+    <row r="110" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A110" s="7">
+        <v>109</v>
+      </c>
+      <c r="B110" s="8">
+        <v>46206</v>
+      </c>
+      <c r="C110" s="7" t="s">
+        <v>229</v>
+      </c>
+      <c r="D110" s="13" t="s">
+        <v>262</v>
+      </c>
+      <c r="E110" s="10" t="s">
+        <v>194</v>
+      </c>
+      <c r="F110" s="10" t="s">
+        <v>221</v>
+      </c>
+      <c r="G110" s="7"/>
+    </row>
+    <row r="111" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A111" s="7">
+        <v>110</v>
+      </c>
+      <c r="B111" s="8">
+        <v>46211</v>
+      </c>
+      <c r="C111" s="7" t="s">
+        <v>309</v>
+      </c>
+      <c r="D111" s="13" t="s">
+        <v>263</v>
+      </c>
+      <c r="E111" s="10" t="s">
+        <v>238</v>
+      </c>
+      <c r="F111" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="G111" s="7"/>
+    </row>
+    <row r="112" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A112" s="7">
+        <v>111</v>
+      </c>
+      <c r="B112" s="8">
+        <v>46211</v>
+      </c>
+      <c r="C112" s="7" t="s">
+        <v>303</v>
+      </c>
+      <c r="D112" s="13" t="s">
+        <v>264</v>
+      </c>
+      <c r="E112" s="10" t="s">
+        <v>238</v>
+      </c>
+      <c r="F112" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="G112" s="7"/>
+    </row>
+    <row r="113" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A113" s="7">
+        <v>112</v>
+      </c>
+      <c r="B113" s="8">
+        <v>46211</v>
+      </c>
+      <c r="C113" s="7" t="s">
+        <v>304</v>
+      </c>
+      <c r="D113" s="13" t="s">
+        <v>265</v>
+      </c>
+      <c r="E113" s="10" t="s">
+        <v>238</v>
+      </c>
+      <c r="F113" s="10" t="s">
+        <v>221</v>
+      </c>
+      <c r="G113" s="7"/>
+    </row>
+    <row r="114" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A114" s="7">
+        <v>113</v>
+      </c>
+      <c r="B114" s="8">
+        <v>46211</v>
+      </c>
+      <c r="C114" s="7" t="s">
+        <v>200</v>
+      </c>
+      <c r="D114" s="13" t="s">
+        <v>266</v>
+      </c>
+      <c r="E114" s="10" t="s">
+        <v>194</v>
+      </c>
+      <c r="F114" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="G114" s="7"/>
+    </row>
+    <row r="115" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+      <c r="A115" s="7">
+        <v>114</v>
+      </c>
+      <c r="B115" s="8">
+        <v>46216</v>
+      </c>
+      <c r="C115" s="7" t="s">
+        <v>305</v>
+      </c>
+      <c r="D115" s="11" t="s">
+        <v>267</v>
+      </c>
+      <c r="E115" s="10" t="s">
+        <v>194</v>
+      </c>
+      <c r="F115" s="10" t="s">
+        <v>221</v>
+      </c>
+      <c r="G115" s="7"/>
+    </row>
+    <row r="116" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A116" s="7">
+        <v>115</v>
+      </c>
+      <c r="B116" s="8">
+        <v>46216</v>
+      </c>
+      <c r="C116" s="7" t="s">
+        <v>306</v>
+      </c>
+      <c r="D116" s="13" t="s">
+        <v>268</v>
+      </c>
+      <c r="E116" s="10" t="s">
+        <v>194</v>
+      </c>
+      <c r="F116" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="G116" s="7"/>
+    </row>
+    <row r="117" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A117" s="7">
+        <v>116</v>
+      </c>
+      <c r="B117" s="8">
+        <v>46224</v>
+      </c>
+      <c r="C117" s="7" t="s">
+        <v>307</v>
+      </c>
+      <c r="D117" s="13" t="s">
+        <v>269</v>
+      </c>
+      <c r="E117" s="10" t="s">
+        <v>238</v>
+      </c>
+      <c r="F117" s="10" t="s">
+        <v>221</v>
+      </c>
+      <c r="G117" s="7"/>
+    </row>
+    <row r="118" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A118" s="7">
+        <v>117</v>
+      </c>
+      <c r="B118" s="8">
+        <v>46225</v>
+      </c>
+      <c r="C118" s="12" t="s">
+        <v>308</v>
+      </c>
+      <c r="D118" s="13" t="s">
+        <v>270</v>
+      </c>
+      <c r="E118" s="10" t="s">
+        <v>238</v>
+      </c>
+      <c r="F118" s="10" t="s">
+        <v>323</v>
+      </c>
+      <c r="G118" s="7"/>
+    </row>
+    <row r="119" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A119" s="7">
+        <v>118</v>
+      </c>
+      <c r="B119" s="8">
+        <v>46225</v>
+      </c>
+      <c r="C119" s="7" t="s">
+        <v>302</v>
+      </c>
+      <c r="D119" s="11" t="s">
+        <v>271</v>
+      </c>
+      <c r="E119" s="10" t="s">
+        <v>238</v>
+      </c>
+      <c r="F119" s="10" t="s">
+        <v>323</v>
+      </c>
+      <c r="G119" s="7"/>
+    </row>
+    <row r="120" spans="1:7" ht="49.5" x14ac:dyDescent="0.3">
+      <c r="A120" s="7">
+        <v>119</v>
+      </c>
+      <c r="B120" s="8">
+        <v>46226</v>
+      </c>
+      <c r="C120" s="7" t="s">
+        <v>310</v>
+      </c>
+      <c r="D120" s="11" t="s">
+        <v>272</v>
+      </c>
+      <c r="E120" s="10" t="s">
+        <v>238</v>
+      </c>
+      <c r="F120" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="G120" s="7"/>
+    </row>
+    <row r="121" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+      <c r="A121" s="7">
+        <v>120</v>
+      </c>
+      <c r="B121" s="8">
+        <v>46226</v>
+      </c>
+      <c r="C121" s="7" t="s">
+        <v>311</v>
+      </c>
+      <c r="D121" s="11" t="s">
+        <v>273</v>
+      </c>
+      <c r="E121" s="10" t="s">
+        <v>238</v>
+      </c>
+      <c r="F121" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="G121" s="7"/>
+    </row>
+    <row r="122" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A122" s="7">
+        <v>121</v>
+      </c>
+      <c r="B122" s="8">
+        <v>46226</v>
+      </c>
+      <c r="C122" s="7" t="s">
+        <v>312</v>
+      </c>
+      <c r="D122" s="11" t="s">
+        <v>274</v>
+      </c>
+      <c r="E122" s="10" t="s">
+        <v>194</v>
+      </c>
+      <c r="F122" s="10" t="s">
+        <v>221</v>
+      </c>
+      <c r="G122" s="7"/>
+    </row>
+    <row r="123" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A123" s="7">
+        <v>122</v>
+      </c>
+      <c r="B123" s="8">
+        <v>46230</v>
+      </c>
+      <c r="C123" s="7" t="s">
+        <v>313</v>
+      </c>
+      <c r="D123" s="11" t="s">
+        <v>275</v>
+      </c>
+      <c r="E123" s="10" t="s">
+        <v>238</v>
+      </c>
+      <c r="F123" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="G123" s="7"/>
+    </row>
+    <row r="124" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A124" s="7">
+        <v>123</v>
+      </c>
+      <c r="B124" s="8">
+        <v>46230</v>
+      </c>
+      <c r="C124" s="7" t="s">
+        <v>314</v>
+      </c>
+      <c r="D124" s="11" t="s">
+        <v>316</v>
+      </c>
+      <c r="E124" s="10" t="s">
+        <v>194</v>
+      </c>
+      <c r="F124" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="G124" s="7"/>
+    </row>
+    <row r="125" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A125" s="7">
+        <v>124</v>
+      </c>
+      <c r="B125" s="8">
+        <v>46230</v>
+      </c>
+      <c r="C125" s="7" t="s">
+        <v>315</v>
+      </c>
+      <c r="D125" s="11" t="s">
+        <v>317</v>
+      </c>
+      <c r="E125" s="10" t="s">
+        <v>194</v>
+      </c>
+      <c r="F125" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="G125" s="7"/>
+    </row>
+    <row r="126" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A126" s="7">
+        <v>125</v>
+      </c>
+      <c r="B126" s="8">
+        <v>46234</v>
+      </c>
+      <c r="C126" s="7" t="s">
+        <v>318</v>
+      </c>
+      <c r="D126" s="11" t="s">
+        <v>276</v>
+      </c>
+      <c r="E126" s="10" t="s">
+        <v>238</v>
+      </c>
+      <c r="F126" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="G126" s="7"/>
+    </row>
+    <row r="127" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+      <c r="A127" s="7">
+        <v>126</v>
+      </c>
+      <c r="B127" s="8">
+        <v>46234</v>
+      </c>
+      <c r="C127" s="7" t="s">
+        <v>319</v>
+      </c>
+      <c r="D127" s="11" t="s">
+        <v>277</v>
+      </c>
+      <c r="E127" s="10" t="s">
+        <v>238</v>
+      </c>
+      <c r="F127" s="10" t="s">
+        <v>236</v>
+      </c>
+      <c r="G127" s="7"/>
+    </row>
+    <row r="128" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A128" s="7">
+        <v>127</v>
+      </c>
+      <c r="B128" s="8">
+        <v>46237</v>
+      </c>
+      <c r="C128" s="7" t="s">
+        <v>320</v>
+      </c>
+      <c r="D128" s="11" t="s">
+        <v>278</v>
+      </c>
+      <c r="E128" s="10" t="s">
+        <v>194</v>
+      </c>
+      <c r="F128" s="13" t="s">
+        <v>322</v>
+      </c>
+      <c r="G128" s="7"/>
+    </row>
+    <row r="129" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A129" s="7">
+        <v>128</v>
+      </c>
+      <c r="B129" s="8">
+        <v>46237</v>
+      </c>
+      <c r="C129" s="7" t="s">
+        <v>321</v>
+      </c>
+      <c r="D129" s="11" t="s">
+        <v>279</v>
+      </c>
+      <c r="E129" s="10" t="s">
+        <v>194</v>
+      </c>
+      <c r="F129" s="13" t="s">
+        <v>322</v>
+      </c>
+      <c r="G129" s="7"/>
+    </row>
+    <row r="130" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A130" s="7"/>
+      <c r="B130" s="7"/>
+      <c r="C130" s="7"/>
+      <c r="D130" s="7"/>
+      <c r="E130" s="7"/>
+      <c r="F130" s="7"/>
+      <c r="G130" s="7"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/민원데이터.xlsx
+++ b/민원데이터.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\바탕화면\박현식\박현식 개인\코딩\민원관리 대시보드\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24A17CE2-8D89-4DCC-AED3-0689CB1A392E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CD32E63-5BDD-437E-8FF8-B8668CB6F3D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1860" yWindow="615" windowWidth="26835" windowHeight="14145" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="165" yWindow="780" windowWidth="28635" windowHeight="14145" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1196,7 +1196,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1216,24 +1216,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3557,19 +3545,19 @@
       <c r="A81" s="7">
         <v>80</v>
       </c>
-      <c r="B81" s="8">
+      <c r="B81" s="1">
         <v>46164</v>
       </c>
       <c r="C81" s="7" t="s">
         <v>199</v>
       </c>
-      <c r="D81" s="9" t="s">
+      <c r="D81" s="4" t="s">
         <v>192</v>
       </c>
-      <c r="E81" s="10" t="s">
+      <c r="E81" s="3" t="s">
         <v>195</v>
       </c>
-      <c r="F81" s="9" t="s">
+      <c r="F81" s="4" t="s">
         <v>236</v>
       </c>
       <c r="G81" s="7"/>
@@ -3578,19 +3566,19 @@
       <c r="A82" s="7">
         <v>81</v>
       </c>
-      <c r="B82" s="8">
+      <c r="B82" s="1">
         <v>46168</v>
       </c>
       <c r="C82" s="7" t="s">
         <v>198</v>
       </c>
-      <c r="D82" s="9" t="s">
+      <c r="D82" s="4" t="s">
         <v>193</v>
       </c>
-      <c r="E82" s="10" t="s">
+      <c r="E82" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="F82" s="9" t="s">
+      <c r="F82" s="4" t="s">
         <v>196</v>
       </c>
       <c r="G82" s="7"/>
@@ -3599,19 +3587,19 @@
       <c r="A83" s="7">
         <v>82</v>
       </c>
-      <c r="B83" s="8">
+      <c r="B83" s="1">
         <v>46168</v>
       </c>
       <c r="C83" s="7" t="s">
         <v>197</v>
       </c>
-      <c r="D83" s="9" t="s">
+      <c r="D83" s="4" t="s">
         <v>216</v>
       </c>
-      <c r="E83" s="10" t="s">
+      <c r="E83" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="F83" s="9" t="s">
+      <c r="F83" s="4" t="s">
         <v>196</v>
       </c>
       <c r="G83" s="7"/>
@@ -3620,19 +3608,19 @@
       <c r="A84" s="7">
         <v>83</v>
       </c>
-      <c r="B84" s="8">
+      <c r="B84" s="1">
         <v>46169</v>
       </c>
       <c r="C84" s="7" t="s">
         <v>203</v>
       </c>
-      <c r="D84" s="9" t="s">
+      <c r="D84" s="4" t="s">
         <v>217</v>
       </c>
-      <c r="E84" s="10" t="s">
+      <c r="E84" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="F84" s="9" t="s">
+      <c r="F84" s="4" t="s">
         <v>196</v>
       </c>
       <c r="G84" s="7"/>
@@ -3641,19 +3629,19 @@
       <c r="A85" s="7">
         <v>84</v>
       </c>
-      <c r="B85" s="8">
+      <c r="B85" s="1">
         <v>46170</v>
       </c>
       <c r="C85" s="7" t="s">
         <v>233</v>
       </c>
-      <c r="D85" s="9" t="s">
+      <c r="D85" s="4" t="s">
         <v>218</v>
       </c>
-      <c r="E85" s="10" t="s">
+      <c r="E85" s="3" t="s">
         <v>209</v>
       </c>
-      <c r="F85" s="9" t="s">
+      <c r="F85" s="4" t="s">
         <v>196</v>
       </c>
       <c r="G85" s="7"/>
@@ -3662,19 +3650,19 @@
       <c r="A86" s="7">
         <v>85</v>
       </c>
-      <c r="B86" s="8">
+      <c r="B86" s="1">
         <v>46171</v>
       </c>
       <c r="C86" s="7" t="s">
         <v>234</v>
       </c>
-      <c r="D86" s="9" t="s">
+      <c r="D86" s="4" t="s">
         <v>219</v>
       </c>
-      <c r="E86" s="10" t="s">
+      <c r="E86" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="F86" s="9" t="s">
+      <c r="F86" s="4" t="s">
         <v>196</v>
       </c>
       <c r="G86" s="7"/>
@@ -3683,20 +3671,20 @@
       <c r="A87" s="7">
         <v>86</v>
       </c>
-      <c r="B87" s="8">
+      <c r="B87" s="1">
         <v>46171</v>
       </c>
       <c r="C87" s="7" t="s">
         <v>235</v>
       </c>
-      <c r="D87" s="9" t="s">
+      <c r="D87" s="4" t="s">
         <v>220</v>
       </c>
-      <c r="E87" s="10" t="s">
+      <c r="E87" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="F87" s="9" t="s">
-        <v>236</v>
+      <c r="F87" s="4" t="s">
+        <v>196</v>
       </c>
       <c r="G87" s="7"/>
     </row>
@@ -3704,19 +3692,19 @@
       <c r="A88" s="7">
         <v>87</v>
       </c>
-      <c r="B88" s="8">
+      <c r="B88" s="1">
         <v>46181</v>
       </c>
       <c r="C88" s="7" t="s">
         <v>280</v>
       </c>
-      <c r="D88" s="9" t="s">
+      <c r="D88" s="4" t="s">
         <v>240</v>
       </c>
-      <c r="E88" s="10" t="s">
+      <c r="E88" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="F88" s="10" t="s">
+      <c r="F88" s="3" t="s">
         <v>196</v>
       </c>
       <c r="G88" s="7"/>
@@ -3725,19 +3713,19 @@
       <c r="A89" s="7">
         <v>88</v>
       </c>
-      <c r="B89" s="8">
+      <c r="B89" s="1">
         <v>46182</v>
       </c>
       <c r="C89" s="7" t="s">
         <v>281</v>
       </c>
-      <c r="D89" s="11" t="s">
+      <c r="D89" s="8" t="s">
         <v>241</v>
       </c>
-      <c r="E89" s="10" t="s">
+      <c r="E89" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="F89" s="10" t="s">
+      <c r="F89" s="3" t="s">
         <v>196</v>
       </c>
       <c r="G89" s="7"/>
@@ -3746,19 +3734,19 @@
       <c r="A90" s="7">
         <v>89</v>
       </c>
-      <c r="B90" s="8">
+      <c r="B90" s="1">
         <v>46184</v>
       </c>
-      <c r="C90" s="12" t="s">
+      <c r="C90" s="9" t="s">
         <v>282</v>
       </c>
-      <c r="D90" s="13" t="s">
+      <c r="D90" s="2" t="s">
         <v>242</v>
       </c>
-      <c r="E90" s="10" t="s">
+      <c r="E90" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="F90" s="10" t="s">
+      <c r="F90" s="3" t="s">
         <v>196</v>
       </c>
       <c r="G90" s="7"/>
@@ -3767,19 +3755,19 @@
       <c r="A91" s="7">
         <v>90</v>
       </c>
-      <c r="B91" s="8">
+      <c r="B91" s="1">
         <v>46185</v>
       </c>
       <c r="C91" s="7" t="s">
         <v>283</v>
       </c>
-      <c r="D91" s="13" t="s">
+      <c r="D91" s="2" t="s">
         <v>243</v>
       </c>
-      <c r="E91" s="10" t="s">
+      <c r="E91" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="F91" s="10" t="s">
+      <c r="F91" s="3" t="s">
         <v>196</v>
       </c>
       <c r="G91" s="7"/>
@@ -3788,19 +3776,19 @@
       <c r="A92" s="7">
         <v>91</v>
       </c>
-      <c r="B92" s="8">
+      <c r="B92" s="1">
         <v>46188</v>
       </c>
       <c r="C92" s="7" t="s">
         <v>284</v>
       </c>
-      <c r="D92" s="13" t="s">
+      <c r="D92" s="2" t="s">
         <v>244</v>
       </c>
-      <c r="E92" s="10" t="s">
+      <c r="E92" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="F92" s="10" t="s">
+      <c r="F92" s="3" t="s">
         <v>196</v>
       </c>
       <c r="G92" s="7"/>
@@ -3809,19 +3797,19 @@
       <c r="A93" s="7">
         <v>92</v>
       </c>
-      <c r="B93" s="8">
+      <c r="B93" s="1">
         <v>46188</v>
       </c>
-      <c r="C93" s="12" t="s">
+      <c r="C93" s="9" t="s">
         <v>285</v>
       </c>
-      <c r="D93" s="13" t="s">
+      <c r="D93" s="2" t="s">
         <v>245</v>
       </c>
-      <c r="E93" s="10" t="s">
+      <c r="E93" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="F93" s="10" t="s">
+      <c r="F93" s="3" t="s">
         <v>239</v>
       </c>
       <c r="G93" s="7"/>
@@ -3830,19 +3818,19 @@
       <c r="A94" s="7">
         <v>93</v>
       </c>
-      <c r="B94" s="8">
+      <c r="B94" s="1">
         <v>46188</v>
       </c>
       <c r="C94" s="7" t="s">
         <v>286</v>
       </c>
-      <c r="D94" s="13" t="s">
+      <c r="D94" s="2" t="s">
         <v>246</v>
       </c>
-      <c r="E94" s="10" t="s">
+      <c r="E94" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="F94" s="10" t="s">
+      <c r="F94" s="3" t="s">
         <v>239</v>
       </c>
       <c r="G94" s="7"/>
@@ -3851,19 +3839,19 @@
       <c r="A95" s="7">
         <v>94</v>
       </c>
-      <c r="B95" s="8">
+      <c r="B95" s="1">
         <v>46188</v>
       </c>
       <c r="C95" s="7" t="s">
         <v>287</v>
       </c>
-      <c r="D95" s="13" t="s">
+      <c r="D95" s="2" t="s">
         <v>247</v>
       </c>
-      <c r="E95" s="10" t="s">
+      <c r="E95" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="F95" s="10" t="s">
+      <c r="F95" s="3" t="s">
         <v>221</v>
       </c>
       <c r="G95" s="7"/>
@@ -3872,20 +3860,20 @@
       <c r="A96" s="7">
         <v>95</v>
       </c>
-      <c r="B96" s="8">
+      <c r="B96" s="1">
         <v>46188</v>
       </c>
       <c r="C96" s="7" t="s">
         <v>288</v>
       </c>
-      <c r="D96" s="13" t="s">
+      <c r="D96" s="2" t="s">
         <v>248</v>
       </c>
-      <c r="E96" s="10" t="s">
+      <c r="E96" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="F96" s="10" t="s">
-        <v>236</v>
+      <c r="F96" s="3" t="s">
+        <v>323</v>
       </c>
       <c r="G96" s="7"/>
     </row>
@@ -3893,19 +3881,19 @@
       <c r="A97" s="7">
         <v>96</v>
       </c>
-      <c r="B97" s="8">
+      <c r="B97" s="1">
         <v>46188</v>
       </c>
       <c r="C97" s="7" t="s">
         <v>289</v>
       </c>
-      <c r="D97" s="11" t="s">
+      <c r="D97" s="8" t="s">
         <v>249</v>
       </c>
-      <c r="E97" s="10" t="s">
+      <c r="E97" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="F97" s="10" t="s">
+      <c r="F97" s="3" t="s">
         <v>236</v>
       </c>
       <c r="G97" s="7"/>
@@ -3914,19 +3902,19 @@
       <c r="A98" s="7">
         <v>97</v>
       </c>
-      <c r="B98" s="8">
+      <c r="B98" s="1">
         <v>46188</v>
       </c>
       <c r="C98" s="7" t="s">
         <v>290</v>
       </c>
-      <c r="D98" s="13" t="s">
+      <c r="D98" s="2" t="s">
         <v>250</v>
       </c>
-      <c r="E98" s="10" t="s">
+      <c r="E98" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="F98" s="10" t="s">
+      <c r="F98" s="3" t="s">
         <v>221</v>
       </c>
       <c r="G98" s="7"/>
@@ -3935,19 +3923,19 @@
       <c r="A99" s="7">
         <v>98</v>
       </c>
-      <c r="B99" s="8">
+      <c r="B99" s="1">
         <v>46190</v>
       </c>
       <c r="C99" s="7" t="s">
         <v>291</v>
       </c>
-      <c r="D99" s="9" t="s">
+      <c r="D99" s="4" t="s">
         <v>251</v>
       </c>
-      <c r="E99" s="10" t="s">
+      <c r="E99" s="3" t="s">
         <v>237</v>
       </c>
-      <c r="F99" s="13" t="s">
+      <c r="F99" s="2" t="s">
         <v>322</v>
       </c>
       <c r="G99" s="7"/>
@@ -3956,19 +3944,19 @@
       <c r="A100" s="7">
         <v>99</v>
       </c>
-      <c r="B100" s="8">
+      <c r="B100" s="1">
         <v>46190</v>
       </c>
       <c r="C100" s="7" t="s">
         <v>292</v>
       </c>
-      <c r="D100" s="9" t="s">
+      <c r="D100" s="4" t="s">
         <v>252</v>
       </c>
-      <c r="E100" s="10" t="s">
+      <c r="E100" s="3" t="s">
         <v>209</v>
       </c>
-      <c r="F100" s="10" t="s">
+      <c r="F100" s="3" t="s">
         <v>239</v>
       </c>
       <c r="G100" s="7"/>
@@ -3977,19 +3965,19 @@
       <c r="A101" s="7">
         <v>100</v>
       </c>
-      <c r="B101" s="8">
+      <c r="B101" s="1">
         <v>46191</v>
       </c>
       <c r="C101" s="7" t="s">
         <v>293</v>
       </c>
-      <c r="D101" s="13" t="s">
+      <c r="D101" s="2" t="s">
         <v>253</v>
       </c>
-      <c r="E101" s="10" t="s">
+      <c r="E101" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="F101" s="10" t="s">
+      <c r="F101" s="3" t="s">
         <v>196</v>
       </c>
       <c r="G101" s="7"/>
@@ -3998,19 +3986,19 @@
       <c r="A102" s="7">
         <v>101</v>
       </c>
-      <c r="B102" s="8">
+      <c r="B102" s="1">
         <v>46195</v>
       </c>
       <c r="C102" s="7" t="s">
         <v>294</v>
       </c>
-      <c r="D102" s="13" t="s">
+      <c r="D102" s="2" t="s">
         <v>254</v>
       </c>
-      <c r="E102" s="10" t="s">
+      <c r="E102" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="F102" s="10" t="s">
+      <c r="F102" s="3" t="s">
         <v>196</v>
       </c>
       <c r="G102" s="7"/>
@@ -4019,19 +4007,19 @@
       <c r="A103" s="7">
         <v>102</v>
       </c>
-      <c r="B103" s="8">
+      <c r="B103" s="1">
         <v>46195</v>
       </c>
       <c r="C103" s="7" t="s">
         <v>295</v>
       </c>
-      <c r="D103" s="13" t="s">
+      <c r="D103" s="2" t="s">
         <v>255</v>
       </c>
-      <c r="E103" s="10" t="s">
+      <c r="E103" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="F103" s="10" t="s">
+      <c r="F103" s="3" t="s">
         <v>196</v>
       </c>
       <c r="G103" s="7"/>
@@ -4040,19 +4028,19 @@
       <c r="A104" s="7">
         <v>103</v>
       </c>
-      <c r="B104" s="8">
+      <c r="B104" s="1">
         <v>46196</v>
       </c>
       <c r="C104" s="7" t="s">
         <v>298</v>
       </c>
-      <c r="D104" s="9" t="s">
+      <c r="D104" s="4" t="s">
         <v>256</v>
       </c>
-      <c r="E104" s="10" t="s">
+      <c r="E104" s="3" t="s">
         <v>237</v>
       </c>
-      <c r="F104" s="10" t="s">
+      <c r="F104" s="3" t="s">
         <v>196</v>
       </c>
       <c r="G104" s="7"/>
@@ -4061,19 +4049,19 @@
       <c r="A105" s="7">
         <v>104</v>
       </c>
-      <c r="B105" s="8">
+      <c r="B105" s="1">
         <v>46197</v>
       </c>
       <c r="C105" s="7" t="s">
         <v>296</v>
       </c>
-      <c r="D105" s="13" t="s">
+      <c r="D105" s="2" t="s">
         <v>257</v>
       </c>
-      <c r="E105" s="10" t="s">
+      <c r="E105" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="F105" s="10" t="s">
+      <c r="F105" s="3" t="s">
         <v>196</v>
       </c>
       <c r="G105" s="7"/>
@@ -4082,19 +4070,19 @@
       <c r="A106" s="7">
         <v>105</v>
       </c>
-      <c r="B106" s="8">
+      <c r="B106" s="1">
         <v>46197</v>
       </c>
       <c r="C106" s="7" t="s">
         <v>297</v>
       </c>
-      <c r="D106" s="13" t="s">
+      <c r="D106" s="2" t="s">
         <v>258</v>
       </c>
-      <c r="E106" s="10" t="s">
+      <c r="E106" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="F106" s="10" t="s">
+      <c r="F106" s="3" t="s">
         <v>196</v>
       </c>
       <c r="G106" s="7"/>
@@ -4103,19 +4091,19 @@
       <c r="A107" s="7">
         <v>106</v>
       </c>
-      <c r="B107" s="8">
+      <c r="B107" s="1">
         <v>46198</v>
       </c>
       <c r="C107" s="7" t="s">
         <v>299</v>
       </c>
-      <c r="D107" s="13" t="s">
+      <c r="D107" s="2" t="s">
         <v>259</v>
       </c>
-      <c r="E107" s="10" t="s">
+      <c r="E107" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="F107" s="10" t="s">
+      <c r="F107" s="3" t="s">
         <v>196</v>
       </c>
       <c r="G107" s="7"/>
@@ -4124,19 +4112,19 @@
       <c r="A108" s="7">
         <v>107</v>
       </c>
-      <c r="B108" s="8">
+      <c r="B108" s="1">
         <v>46198</v>
       </c>
       <c r="C108" s="7" t="s">
         <v>300</v>
       </c>
-      <c r="D108" s="9" t="s">
+      <c r="D108" s="4" t="s">
         <v>260</v>
       </c>
-      <c r="E108" s="10" t="s">
+      <c r="E108" s="3" t="s">
         <v>237</v>
       </c>
-      <c r="F108" s="10" t="s">
+      <c r="F108" s="3" t="s">
         <v>221</v>
       </c>
       <c r="G108" s="7"/>
@@ -4145,19 +4133,19 @@
       <c r="A109" s="7">
         <v>108</v>
       </c>
-      <c r="B109" s="8">
+      <c r="B109" s="1">
         <v>46204</v>
       </c>
       <c r="C109" s="7" t="s">
         <v>301</v>
       </c>
-      <c r="D109" s="13" t="s">
+      <c r="D109" s="2" t="s">
         <v>261</v>
       </c>
-      <c r="E109" s="10" t="s">
+      <c r="E109" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="F109" s="10" t="s">
+      <c r="F109" s="3" t="s">
         <v>196</v>
       </c>
       <c r="G109" s="7"/>
@@ -4166,19 +4154,19 @@
       <c r="A110" s="7">
         <v>109</v>
       </c>
-      <c r="B110" s="8">
+      <c r="B110" s="1">
         <v>46206</v>
       </c>
       <c r="C110" s="7" t="s">
         <v>229</v>
       </c>
-      <c r="D110" s="13" t="s">
+      <c r="D110" s="2" t="s">
         <v>262</v>
       </c>
-      <c r="E110" s="10" t="s">
+      <c r="E110" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="F110" s="10" t="s">
+      <c r="F110" s="3" t="s">
         <v>221</v>
       </c>
       <c r="G110" s="7"/>
@@ -4187,19 +4175,19 @@
       <c r="A111" s="7">
         <v>110</v>
       </c>
-      <c r="B111" s="8">
+      <c r="B111" s="1">
         <v>46211</v>
       </c>
       <c r="C111" s="7" t="s">
         <v>309</v>
       </c>
-      <c r="D111" s="13" t="s">
+      <c r="D111" s="2" t="s">
         <v>263</v>
       </c>
-      <c r="E111" s="10" t="s">
+      <c r="E111" s="3" t="s">
         <v>238</v>
       </c>
-      <c r="F111" s="10" t="s">
+      <c r="F111" s="3" t="s">
         <v>196</v>
       </c>
       <c r="G111" s="7"/>
@@ -4208,19 +4196,19 @@
       <c r="A112" s="7">
         <v>111</v>
       </c>
-      <c r="B112" s="8">
+      <c r="B112" s="1">
         <v>46211</v>
       </c>
       <c r="C112" s="7" t="s">
         <v>303</v>
       </c>
-      <c r="D112" s="13" t="s">
+      <c r="D112" s="2" t="s">
         <v>264</v>
       </c>
-      <c r="E112" s="10" t="s">
+      <c r="E112" s="3" t="s">
         <v>238</v>
       </c>
-      <c r="F112" s="10" t="s">
+      <c r="F112" s="3" t="s">
         <v>196</v>
       </c>
       <c r="G112" s="7"/>
@@ -4229,19 +4217,19 @@
       <c r="A113" s="7">
         <v>112</v>
       </c>
-      <c r="B113" s="8">
+      <c r="B113" s="1">
         <v>46211</v>
       </c>
       <c r="C113" s="7" t="s">
         <v>304</v>
       </c>
-      <c r="D113" s="13" t="s">
+      <c r="D113" s="2" t="s">
         <v>265</v>
       </c>
-      <c r="E113" s="10" t="s">
+      <c r="E113" s="3" t="s">
         <v>238</v>
       </c>
-      <c r="F113" s="10" t="s">
+      <c r="F113" s="3" t="s">
         <v>221</v>
       </c>
       <c r="G113" s="7"/>
@@ -4250,19 +4238,19 @@
       <c r="A114" s="7">
         <v>113</v>
       </c>
-      <c r="B114" s="8">
+      <c r="B114" s="1">
         <v>46211</v>
       </c>
       <c r="C114" s="7" t="s">
         <v>200</v>
       </c>
-      <c r="D114" s="13" t="s">
+      <c r="D114" s="2" t="s">
         <v>266</v>
       </c>
-      <c r="E114" s="10" t="s">
+      <c r="E114" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="F114" s="10" t="s">
+      <c r="F114" s="3" t="s">
         <v>196</v>
       </c>
       <c r="G114" s="7"/>
@@ -4271,19 +4259,19 @@
       <c r="A115" s="7">
         <v>114</v>
       </c>
-      <c r="B115" s="8">
+      <c r="B115" s="1">
         <v>46216</v>
       </c>
       <c r="C115" s="7" t="s">
         <v>305</v>
       </c>
-      <c r="D115" s="11" t="s">
+      <c r="D115" s="8" t="s">
         <v>267</v>
       </c>
-      <c r="E115" s="10" t="s">
+      <c r="E115" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="F115" s="10" t="s">
+      <c r="F115" s="3" t="s">
         <v>221</v>
       </c>
       <c r="G115" s="7"/>
@@ -4292,19 +4280,19 @@
       <c r="A116" s="7">
         <v>115</v>
       </c>
-      <c r="B116" s="8">
+      <c r="B116" s="1">
         <v>46216</v>
       </c>
       <c r="C116" s="7" t="s">
         <v>306</v>
       </c>
-      <c r="D116" s="13" t="s">
+      <c r="D116" s="2" t="s">
         <v>268</v>
       </c>
-      <c r="E116" s="10" t="s">
+      <c r="E116" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="F116" s="10" t="s">
+      <c r="F116" s="3" t="s">
         <v>196</v>
       </c>
       <c r="G116" s="7"/>
@@ -4313,19 +4301,19 @@
       <c r="A117" s="7">
         <v>116</v>
       </c>
-      <c r="B117" s="8">
+      <c r="B117" s="1">
         <v>46224</v>
       </c>
       <c r="C117" s="7" t="s">
         <v>307</v>
       </c>
-      <c r="D117" s="13" t="s">
+      <c r="D117" s="2" t="s">
         <v>269</v>
       </c>
-      <c r="E117" s="10" t="s">
+      <c r="E117" s="3" t="s">
         <v>238</v>
       </c>
-      <c r="F117" s="10" t="s">
+      <c r="F117" s="3" t="s">
         <v>221</v>
       </c>
       <c r="G117" s="7"/>
@@ -4334,19 +4322,19 @@
       <c r="A118" s="7">
         <v>117</v>
       </c>
-      <c r="B118" s="8">
+      <c r="B118" s="1">
         <v>46225</v>
       </c>
-      <c r="C118" s="12" t="s">
+      <c r="C118" s="9" t="s">
         <v>308</v>
       </c>
-      <c r="D118" s="13" t="s">
+      <c r="D118" s="2" t="s">
         <v>270</v>
       </c>
-      <c r="E118" s="10" t="s">
+      <c r="E118" s="3" t="s">
         <v>238</v>
       </c>
-      <c r="F118" s="10" t="s">
+      <c r="F118" s="3" t="s">
         <v>323</v>
       </c>
       <c r="G118" s="7"/>
@@ -4355,19 +4343,19 @@
       <c r="A119" s="7">
         <v>118</v>
       </c>
-      <c r="B119" s="8">
+      <c r="B119" s="1">
         <v>46225</v>
       </c>
       <c r="C119" s="7" t="s">
         <v>302</v>
       </c>
-      <c r="D119" s="11" t="s">
+      <c r="D119" s="8" t="s">
         <v>271</v>
       </c>
-      <c r="E119" s="10" t="s">
+      <c r="E119" s="3" t="s">
         <v>238</v>
       </c>
-      <c r="F119" s="10" t="s">
+      <c r="F119" s="3" t="s">
         <v>323</v>
       </c>
       <c r="G119" s="7"/>
@@ -4376,19 +4364,19 @@
       <c r="A120" s="7">
         <v>119</v>
       </c>
-      <c r="B120" s="8">
+      <c r="B120" s="1">
         <v>46226</v>
       </c>
       <c r="C120" s="7" t="s">
         <v>310</v>
       </c>
-      <c r="D120" s="11" t="s">
+      <c r="D120" s="8" t="s">
         <v>272</v>
       </c>
-      <c r="E120" s="10" t="s">
+      <c r="E120" s="3" t="s">
         <v>238</v>
       </c>
-      <c r="F120" s="10" t="s">
+      <c r="F120" s="3" t="s">
         <v>196</v>
       </c>
       <c r="G120" s="7"/>
@@ -4397,19 +4385,19 @@
       <c r="A121" s="7">
         <v>120</v>
       </c>
-      <c r="B121" s="8">
+      <c r="B121" s="1">
         <v>46226</v>
       </c>
       <c r="C121" s="7" t="s">
         <v>311</v>
       </c>
-      <c r="D121" s="11" t="s">
+      <c r="D121" s="8" t="s">
         <v>273</v>
       </c>
-      <c r="E121" s="10" t="s">
+      <c r="E121" s="3" t="s">
         <v>238</v>
       </c>
-      <c r="F121" s="10" t="s">
+      <c r="F121" s="3" t="s">
         <v>196</v>
       </c>
       <c r="G121" s="7"/>
@@ -4418,19 +4406,19 @@
       <c r="A122" s="7">
         <v>121</v>
       </c>
-      <c r="B122" s="8">
+      <c r="B122" s="1">
         <v>46226</v>
       </c>
       <c r="C122" s="7" t="s">
         <v>312</v>
       </c>
-      <c r="D122" s="11" t="s">
+      <c r="D122" s="8" t="s">
         <v>274</v>
       </c>
-      <c r="E122" s="10" t="s">
+      <c r="E122" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="F122" s="10" t="s">
+      <c r="F122" s="3" t="s">
         <v>221</v>
       </c>
       <c r="G122" s="7"/>
@@ -4439,19 +4427,19 @@
       <c r="A123" s="7">
         <v>122</v>
       </c>
-      <c r="B123" s="8">
+      <c r="B123" s="1">
         <v>46230</v>
       </c>
       <c r="C123" s="7" t="s">
         <v>313</v>
       </c>
-      <c r="D123" s="11" t="s">
+      <c r="D123" s="8" t="s">
         <v>275</v>
       </c>
-      <c r="E123" s="10" t="s">
+      <c r="E123" s="3" t="s">
         <v>238</v>
       </c>
-      <c r="F123" s="10" t="s">
+      <c r="F123" s="3" t="s">
         <v>196</v>
       </c>
       <c r="G123" s="7"/>
@@ -4460,19 +4448,19 @@
       <c r="A124" s="7">
         <v>123</v>
       </c>
-      <c r="B124" s="8">
+      <c r="B124" s="1">
         <v>46230</v>
       </c>
       <c r="C124" s="7" t="s">
         <v>314</v>
       </c>
-      <c r="D124" s="11" t="s">
+      <c r="D124" s="8" t="s">
         <v>316</v>
       </c>
-      <c r="E124" s="10" t="s">
+      <c r="E124" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="F124" s="10" t="s">
+      <c r="F124" s="3" t="s">
         <v>196</v>
       </c>
       <c r="G124" s="7"/>
@@ -4481,19 +4469,19 @@
       <c r="A125" s="7">
         <v>124</v>
       </c>
-      <c r="B125" s="8">
+      <c r="B125" s="1">
         <v>46230</v>
       </c>
       <c r="C125" s="7" t="s">
         <v>315</v>
       </c>
-      <c r="D125" s="11" t="s">
+      <c r="D125" s="8" t="s">
         <v>317</v>
       </c>
-      <c r="E125" s="10" t="s">
+      <c r="E125" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="F125" s="10" t="s">
+      <c r="F125" s="3" t="s">
         <v>196</v>
       </c>
       <c r="G125" s="7"/>
@@ -4502,19 +4490,19 @@
       <c r="A126" s="7">
         <v>125</v>
       </c>
-      <c r="B126" s="8">
+      <c r="B126" s="1">
         <v>46234</v>
       </c>
       <c r="C126" s="7" t="s">
         <v>318</v>
       </c>
-      <c r="D126" s="11" t="s">
+      <c r="D126" s="8" t="s">
         <v>276</v>
       </c>
-      <c r="E126" s="10" t="s">
+      <c r="E126" s="3" t="s">
         <v>238</v>
       </c>
-      <c r="F126" s="10" t="s">
+      <c r="F126" s="3" t="s">
         <v>196</v>
       </c>
       <c r="G126" s="7"/>
@@ -4523,19 +4511,19 @@
       <c r="A127" s="7">
         <v>126</v>
       </c>
-      <c r="B127" s="8">
+      <c r="B127" s="1">
         <v>46234</v>
       </c>
       <c r="C127" s="7" t="s">
         <v>319</v>
       </c>
-      <c r="D127" s="11" t="s">
+      <c r="D127" s="8" t="s">
         <v>277</v>
       </c>
-      <c r="E127" s="10" t="s">
+      <c r="E127" s="3" t="s">
         <v>238</v>
       </c>
-      <c r="F127" s="10" t="s">
+      <c r="F127" s="3" t="s">
         <v>236</v>
       </c>
       <c r="G127" s="7"/>
@@ -4544,19 +4532,19 @@
       <c r="A128" s="7">
         <v>127</v>
       </c>
-      <c r="B128" s="8">
+      <c r="B128" s="1">
         <v>46237</v>
       </c>
       <c r="C128" s="7" t="s">
         <v>320</v>
       </c>
-      <c r="D128" s="11" t="s">
+      <c r="D128" s="8" t="s">
         <v>278</v>
       </c>
-      <c r="E128" s="10" t="s">
+      <c r="E128" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="F128" s="13" t="s">
+      <c r="F128" s="2" t="s">
         <v>322</v>
       </c>
       <c r="G128" s="7"/>
@@ -4565,19 +4553,19 @@
       <c r="A129" s="7">
         <v>128</v>
       </c>
-      <c r="B129" s="8">
+      <c r="B129" s="1">
         <v>46237</v>
       </c>
       <c r="C129" s="7" t="s">
         <v>321</v>
       </c>
-      <c r="D129" s="11" t="s">
+      <c r="D129" s="8" t="s">
         <v>279</v>
       </c>
-      <c r="E129" s="10" t="s">
+      <c r="E129" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="F129" s="13" t="s">
+      <c r="F129" s="2" t="s">
         <v>322</v>
       </c>
       <c r="G129" s="7"/>

--- a/민원데이터.xlsx
+++ b/민원데이터.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\바탕화면\박현식\박현식 개인\코딩\민원관리 대시보드\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CD32E63-5BDD-437E-8FF8-B8668CB6F3D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{734AB351-B8BC-4F52-9EDE-997BA187B995}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="165" yWindow="780" windowWidth="28635" windowHeight="14145" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="165" yWindow="2055" windowWidth="28635" windowHeight="14145" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1992,7 +1992,7 @@
         <v>10</v>
       </c>
       <c r="F18" t="s">
-        <v>20</v>
+        <v>187</v>
       </c>
       <c r="G18">
         <v>35.557967985714299</v>
@@ -2564,7 +2564,7 @@
         <v>10</v>
       </c>
       <c r="F40" t="s">
-        <v>60</v>
+        <v>188</v>
       </c>
       <c r="G40">
         <v>35.5720641715236</v>
@@ -3831,7 +3831,7 @@
         <v>194</v>
       </c>
       <c r="F94" s="3" t="s">
-        <v>239</v>
+        <v>196</v>
       </c>
       <c r="G94" s="7"/>
     </row>

--- a/민원데이터.xlsx
+++ b/민원데이터.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\바탕화면\박현식\박현식 개인\코딩\민원관리 대시보드\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{734AB351-B8BC-4F52-9EDE-997BA187B995}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A5BBD4C-881A-4750-887F-765317F7E607}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="165" yWindow="2055" windowWidth="28635" windowHeight="14145" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-345" yWindow="1470" windowWidth="29100" windowHeight="13620" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="588" uniqueCount="324">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="708" uniqueCount="382">
   <si>
     <t>민원번호</t>
   </si>
@@ -1140,13 +1140,246 @@
   <si>
     <t>장기과제</t>
     <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>문승재</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>최병호</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>엄희순</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>김성민</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>다운2지구 A-6BL 일원(다운동 산119번지 분리 필지) 민원인 소유의 미보상 분리 필지가 출입도로가 없는 맹지로, 도시계획도로(소로)를 신설하여 맹지 상태 해소 요구</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>남외동 정지말공원 노후화로 안전사고가 우려되어 현장 점검 실시(7.15. 17시)
+ - 우레탄 바닥, 명패, 쉼터 조명, 화장실 앞 스탠드 조명, 화단 정비, 벤치 방향, 공사 장비 방치 등</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>B-04구역 주택재개발조합장 고발건 관련 편향성 지적 및 책임 소명 요구</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>태화 고지배수터널 공사손해보험 처리 관련</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>다운2지구 저류지 체육시설 및 복합 개발 제안 관련</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>반구2동 구교공원 누수·수목·조명 및 전기시설 정비</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>반구2동 낙원떡집 주차장 주변 무단투기 폐기물 정비</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>학성공원 중턱 주민 운동 장소 방역</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>내황초등학교 후문 뚝방길 수목 전지작업</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>성안동 월드골프장 영업 재개 절차, 실외기 및 소방시설 점검</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>약사동 삼성래미안 1단지 앞 스마트 버스승강장 설치 검토</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>반구2동 호텔 다움·CU편의점·르노코리아·구교쉼터 인근 방범용 CCTV 설치</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>약사동 경로당·행정복지센터 맞은편 버스승강장 차양 설치</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>동천강변 동강병원에서 서동 방향 구간 LED 조명 수리</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>반구정16길 버스정류장 조명 교체 및 환경정비</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>내황공원 노후 바닥 재포장</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>마제스타워아파트 주변 도로 교통 시스템 정비</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>구교8길 45 인근 골목길 차단 관련 현황 확인</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>학성공원 일원 막힌 배수구 준설 및 환경정비</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>약사고등학교 옆 가파른 돌계단 보수 및 안전시설 설치</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>반구1동 서원공원 사각정 의자 교체·증설 및 지붕 보수</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>반구1동 KCC페인트 앞 도로 과속방지시설 설치</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>태화강·동천강변 목재 의자 및 목재 운동기구 정비</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>태화강·동천강변 무단 방치 개인 의자 수거</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>태화강·동천강변 운동기구 노후·부식 문제, 전체·전수점검 후 오일스테인 도색 및 파손 부위 보수 요청</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>종가 18길 3-9 도로포장이 이상하여 조치 요청 민원</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>평산로2 도로변 자전거 거치대 파손으로 인한 수리 요청 민원</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">학성공원 일원 산책길 정비 요청(야자매트 설치 등) </t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>다운아파트입구 사거리 성남동 시내 방향 정류장(다운로111 앞) 내 온열의자가 켜져있어 조치 바람</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>건강 및 생계 문제가 심각한 이웃 주민에 대한 지원방안 문의(의회사무국 방문 민원)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>울산 중구 다운동 산 119</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>울산 중구 남외동 502-3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>울산 중구 북정동 58-15</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>울산 중구 다운동 135</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>울산 중구 반구동 38-3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>울산 중구 반구동 100-2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>울산 중구 학성동 100</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>울산 중구 반구동 845-1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>울산 중구 성안동 807-3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>울산 중구 약사동 612-38</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>울산 중구 반구동 110</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>울산 중구 약사동 590-5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>울산 중구 남외동 601-1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>울산 중구 반구동 887</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>울산 중구 반구동 784-7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>울산 중구 우정동 172</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>울산 중구 반구동 41-11</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>울산 중구 약사동 892-12</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>울산 중구 반구동 679</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>울산 중구 반구동 880-29</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>울산 중구 성남동 212</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>울산 중구 약사동 344-4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>울산 중구 약사동 630-30</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>울산 중구 다운동 779-6</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1175,6 +1408,19 @@
       <charset val="129"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="굴림"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -1196,7 +1442,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1222,6 +1468,41 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1525,15 +1806,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H130"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:H160"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="2" max="2" width="11.125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="35.875" customWidth="1"/>
     <col min="4" max="4" width="200.625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1559,7 +1840,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1585,7 +1866,7 @@
         <v>129.334708123821</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1611,7 +1892,7 @@
         <v>129.34914011636599</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1637,7 +1918,7 @@
         <v>129.341655674116</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8">
       <c r="A5">
         <v>4</v>
       </c>
@@ -1653,7 +1934,7 @@
       <c r="E5" t="s">
         <v>19</v>
       </c>
-      <c r="F5" t="s">
+      <c r="F5" s="6" t="s">
         <v>11</v>
       </c>
       <c r="G5">
@@ -1663,7 +1944,7 @@
         <v>129.348784402462</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8">
       <c r="A6">
         <v>5</v>
       </c>
@@ -1679,7 +1960,7 @@
       <c r="E6" t="s">
         <v>10</v>
       </c>
-      <c r="F6" t="s">
+      <c r="F6" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G6">
@@ -1689,7 +1970,7 @@
         <v>129.328386461436</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8">
       <c r="A7">
         <v>6</v>
       </c>
@@ -1705,7 +1986,7 @@
       <c r="E7" t="s">
         <v>10</v>
       </c>
-      <c r="F7" t="s">
+      <c r="F7" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G7">
@@ -1715,7 +1996,7 @@
         <v>129.293406307109</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:8">
       <c r="A8">
         <v>7</v>
       </c>
@@ -1731,7 +2012,7 @@
       <c r="E8" t="s">
         <v>10</v>
       </c>
-      <c r="F8" t="s">
+      <c r="F8" s="6" t="s">
         <v>20</v>
       </c>
       <c r="G8">
@@ -1741,7 +2022,7 @@
         <v>129.321138541696</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:8">
       <c r="A9">
         <v>8</v>
       </c>
@@ -1757,7 +2038,7 @@
       <c r="E9" t="s">
         <v>10</v>
       </c>
-      <c r="F9" t="s">
+      <c r="F9" s="6" t="s">
         <v>11</v>
       </c>
       <c r="G9">
@@ -1767,7 +2048,7 @@
         <v>129.336443953188</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:8">
       <c r="A10">
         <v>9</v>
       </c>
@@ -1783,7 +2064,7 @@
       <c r="E10" t="s">
         <v>36</v>
       </c>
-      <c r="F10" t="s">
+      <c r="F10" s="6" t="s">
         <v>11</v>
       </c>
       <c r="G10">
@@ -1793,7 +2074,7 @@
         <v>129.35126645610401</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:8">
       <c r="A11">
         <v>10</v>
       </c>
@@ -1809,7 +2090,7 @@
       <c r="E11" t="s">
         <v>19</v>
       </c>
-      <c r="F11" t="s">
+      <c r="F11" s="6" t="s">
         <v>11</v>
       </c>
       <c r="G11">
@@ -1819,7 +2100,7 @@
         <v>129.34604022411801</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:8">
       <c r="A12">
         <v>11</v>
       </c>
@@ -1835,7 +2116,7 @@
       <c r="E12" t="s">
         <v>19</v>
       </c>
-      <c r="F12" t="s">
+      <c r="F12" s="6" t="s">
         <v>41</v>
       </c>
       <c r="G12">
@@ -1845,7 +2126,7 @@
         <v>129.34512228457299</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:8">
       <c r="A13">
         <v>12</v>
       </c>
@@ -1861,7 +2142,7 @@
       <c r="E13" t="s">
         <v>186</v>
       </c>
-      <c r="F13" t="s">
+      <c r="F13" s="6" t="s">
         <v>11</v>
       </c>
       <c r="G13">
@@ -1871,7 +2152,7 @@
         <v>129.265769674285</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:8">
       <c r="A14">
         <v>13</v>
       </c>
@@ -1887,7 +2168,7 @@
       <c r="E14" t="s">
         <v>10</v>
       </c>
-      <c r="F14" t="s">
+      <c r="F14" s="6" t="s">
         <v>11</v>
       </c>
       <c r="G14">
@@ -1897,7 +2178,7 @@
         <v>129.328832230009</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:8">
       <c r="A15">
         <v>14</v>
       </c>
@@ -1913,7 +2194,7 @@
       <c r="E15" t="s">
         <v>10</v>
       </c>
-      <c r="F15" t="s">
+      <c r="F15" s="6" t="s">
         <v>11</v>
       </c>
       <c r="G15">
@@ -1923,7 +2204,7 @@
         <v>129.32766567982</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:8">
       <c r="A16">
         <v>15</v>
       </c>
@@ -1939,7 +2220,7 @@
       <c r="E16" t="s">
         <v>10</v>
       </c>
-      <c r="F16" t="s">
+      <c r="F16" s="6" t="s">
         <v>11</v>
       </c>
       <c r="G16">
@@ -1949,7 +2230,7 @@
         <v>129.32605295352801</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:8">
       <c r="A17">
         <v>16</v>
       </c>
@@ -1965,7 +2246,7 @@
       <c r="E17" t="s">
         <v>10</v>
       </c>
-      <c r="F17" t="s">
+      <c r="F17" s="6" t="s">
         <v>20</v>
       </c>
       <c r="G17">
@@ -1975,7 +2256,7 @@
         <v>129.32736074607899</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:8">
       <c r="A18">
         <v>17</v>
       </c>
@@ -1991,7 +2272,7 @@
       <c r="E18" t="s">
         <v>10</v>
       </c>
-      <c r="F18" t="s">
+      <c r="F18" s="6" t="s">
         <v>187</v>
       </c>
       <c r="G18">
@@ -2001,7 +2282,7 @@
         <v>129.327571456708</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:8">
       <c r="A19">
         <v>18</v>
       </c>
@@ -2017,7 +2298,7 @@
       <c r="E19" t="s">
         <v>59</v>
       </c>
-      <c r="F19" t="s">
+      <c r="F19" s="6" t="s">
         <v>60</v>
       </c>
       <c r="G19">
@@ -2027,7 +2308,7 @@
         <v>129.26688519197299</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:8">
       <c r="A20">
         <v>19</v>
       </c>
@@ -2043,7 +2324,7 @@
       <c r="E20" t="s">
         <v>64</v>
       </c>
-      <c r="F20" t="s">
+      <c r="F20" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G20">
@@ -2053,7 +2334,7 @@
         <v>129.29811305216501</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:8">
       <c r="A21">
         <v>20</v>
       </c>
@@ -2069,7 +2350,7 @@
       <c r="E21" t="s">
         <v>64</v>
       </c>
-      <c r="F21" t="s">
+      <c r="F21" s="6" t="s">
         <v>11</v>
       </c>
       <c r="G21">
@@ -2079,7 +2360,7 @@
         <v>129.29811305216501</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:8">
       <c r="A22">
         <v>21</v>
       </c>
@@ -2095,7 +2376,7 @@
       <c r="E22" t="s">
         <v>64</v>
       </c>
-      <c r="F22" t="s">
+      <c r="F22" s="6" t="s">
         <v>11</v>
       </c>
       <c r="G22">
@@ -2105,7 +2386,7 @@
         <v>129.300962239363</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:8">
       <c r="A23">
         <v>22</v>
       </c>
@@ -2121,7 +2402,7 @@
       <c r="E23" t="s">
         <v>64</v>
       </c>
-      <c r="F23" t="s">
+      <c r="F23" s="6" t="s">
         <v>11</v>
       </c>
       <c r="G23">
@@ -2131,7 +2412,7 @@
         <v>129.30058825465301</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:8">
       <c r="A24">
         <v>23</v>
       </c>
@@ -2147,7 +2428,7 @@
       <c r="E24" t="s">
         <v>64</v>
       </c>
-      <c r="F24" t="s">
+      <c r="F24" s="6" t="s">
         <v>11</v>
       </c>
       <c r="G24">
@@ -2157,7 +2438,7 @@
         <v>129.30058825465301</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:8">
       <c r="A25">
         <v>24</v>
       </c>
@@ -2173,7 +2454,7 @@
       <c r="E25" t="s">
         <v>10</v>
       </c>
-      <c r="F25" t="s">
+      <c r="F25" s="6" t="s">
         <v>11</v>
       </c>
       <c r="G25">
@@ -2183,7 +2464,7 @@
         <v>129.32200364813099</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:8">
       <c r="A26">
         <v>25</v>
       </c>
@@ -2199,7 +2480,7 @@
       <c r="E26" t="s">
         <v>10</v>
       </c>
-      <c r="F26" t="s">
+      <c r="F26" s="6" t="s">
         <v>41</v>
       </c>
       <c r="G26">
@@ -2209,7 +2490,7 @@
         <v>129.32531570361701</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:8">
       <c r="A27">
         <v>26</v>
       </c>
@@ -2225,7 +2506,7 @@
       <c r="E27" t="s">
         <v>10</v>
       </c>
-      <c r="F27" t="s">
+      <c r="F27" s="6" t="s">
         <v>11</v>
       </c>
       <c r="G27">
@@ -2235,7 +2516,7 @@
         <v>129.31827211577701</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:8">
       <c r="A28">
         <v>27</v>
       </c>
@@ -2251,7 +2532,7 @@
       <c r="E28" t="s">
         <v>82</v>
       </c>
-      <c r="F28" t="s">
+      <c r="F28" s="6" t="s">
         <v>11</v>
       </c>
       <c r="G28">
@@ -2261,7 +2542,7 @@
         <v>129.3211136704</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:8">
       <c r="A29">
         <v>28</v>
       </c>
@@ -2277,7 +2558,7 @@
       <c r="E29" t="s">
         <v>82</v>
       </c>
-      <c r="F29" t="s">
+      <c r="F29" s="6" t="s">
         <v>11</v>
       </c>
       <c r="G29">
@@ -2287,7 +2568,7 @@
         <v>129.28046149747701</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:8">
       <c r="A30">
         <v>29</v>
       </c>
@@ -2303,7 +2584,7 @@
       <c r="E30" t="s">
         <v>10</v>
       </c>
-      <c r="F30" t="s">
+      <c r="F30" s="6" t="s">
         <v>60</v>
       </c>
       <c r="G30">
@@ -2313,7 +2594,7 @@
         <v>129.34220700976999</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:8">
       <c r="A31">
         <v>30</v>
       </c>
@@ -2329,7 +2610,7 @@
       <c r="E31" t="s">
         <v>10</v>
       </c>
-      <c r="F31" t="s">
+      <c r="F31" s="6" t="s">
         <v>11</v>
       </c>
       <c r="G31">
@@ -2339,7 +2620,7 @@
         <v>129.308375901956</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:8">
       <c r="A32">
         <v>31</v>
       </c>
@@ -2355,7 +2636,7 @@
       <c r="E32" t="s">
         <v>93</v>
       </c>
-      <c r="F32" t="s">
+      <c r="F32" s="6" t="s">
         <v>60</v>
       </c>
       <c r="G32">
@@ -2365,7 +2646,7 @@
         <v>129.279177893774</v>
       </c>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:8">
       <c r="A33">
         <v>32</v>
       </c>
@@ -2381,7 +2662,7 @@
       <c r="E33" t="s">
         <v>10</v>
       </c>
-      <c r="F33" t="s">
+      <c r="F33" s="6" t="s">
         <v>11</v>
       </c>
       <c r="G33">
@@ -2391,7 +2672,7 @@
         <v>129.31901602761101</v>
       </c>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:8">
       <c r="A34">
         <v>33</v>
       </c>
@@ -2407,7 +2688,7 @@
       <c r="E34" t="s">
         <v>100</v>
       </c>
-      <c r="F34" t="s">
+      <c r="F34" s="6" t="s">
         <v>60</v>
       </c>
       <c r="G34">
@@ -2417,7 +2698,7 @@
         <v>129.346181351555</v>
       </c>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:8">
       <c r="A35">
         <v>34</v>
       </c>
@@ -2433,7 +2714,7 @@
       <c r="E35" t="s">
         <v>10</v>
       </c>
-      <c r="F35" t="s">
+      <c r="F35" s="6" t="s">
         <v>11</v>
       </c>
       <c r="G35">
@@ -2443,7 +2724,7 @@
         <v>129.32388107690801</v>
       </c>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:8">
       <c r="A36">
         <v>35</v>
       </c>
@@ -2459,7 +2740,7 @@
       <c r="E36" t="s">
         <v>10</v>
       </c>
-      <c r="F36" t="s">
+      <c r="F36" s="6" t="s">
         <v>11</v>
       </c>
       <c r="G36">
@@ -2469,7 +2750,7 @@
         <v>129.33754632059299</v>
       </c>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:8">
       <c r="A37">
         <v>36</v>
       </c>
@@ -2485,7 +2766,7 @@
       <c r="E37" t="s">
         <v>10</v>
       </c>
-      <c r="F37" t="s">
+      <c r="F37" s="6" t="s">
         <v>20</v>
       </c>
       <c r="G37">
@@ -2495,7 +2776,7 @@
         <v>129.33754632059299</v>
       </c>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:8">
       <c r="A38">
         <v>37</v>
       </c>
@@ -2511,7 +2792,7 @@
       <c r="E38" t="s">
         <v>10</v>
       </c>
-      <c r="F38" t="s">
+      <c r="F38" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G38">
@@ -2521,7 +2802,7 @@
         <v>129.32938991855301</v>
       </c>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:8">
       <c r="A39">
         <v>38</v>
       </c>
@@ -2537,7 +2818,7 @@
       <c r="E39" t="s">
         <v>64</v>
       </c>
-      <c r="F39" t="s">
+      <c r="F39" s="6" t="s">
         <v>11</v>
       </c>
       <c r="G39">
@@ -2547,7 +2828,7 @@
         <v>129.30858345615701</v>
       </c>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:8">
       <c r="A40">
         <v>39</v>
       </c>
@@ -2563,7 +2844,7 @@
       <c r="E40" t="s">
         <v>10</v>
       </c>
-      <c r="F40" t="s">
+      <c r="F40" s="6" t="s">
         <v>188</v>
       </c>
       <c r="G40">
@@ -2573,7 +2854,7 @@
         <v>129.32189922619699</v>
       </c>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:8">
       <c r="A41">
         <v>40</v>
       </c>
@@ -2589,7 +2870,7 @@
       <c r="E41" t="s">
         <v>10</v>
       </c>
-      <c r="F41" t="s">
+      <c r="F41" s="6" t="s">
         <v>11</v>
       </c>
       <c r="G41">
@@ -2599,7 +2880,7 @@
         <v>129.32189922619699</v>
       </c>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:8">
       <c r="A42">
         <v>41</v>
       </c>
@@ -2615,7 +2896,7 @@
       <c r="E42" t="s">
         <v>10</v>
       </c>
-      <c r="F42" t="s">
+      <c r="F42" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G42">
@@ -2625,7 +2906,7 @@
         <v>129.31846356317999</v>
       </c>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:8">
       <c r="A43">
         <v>42</v>
       </c>
@@ -2641,11 +2922,11 @@
       <c r="E43" t="s">
         <v>10</v>
       </c>
-      <c r="F43" t="s">
+      <c r="F43" s="6" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:8">
       <c r="A44">
         <v>43</v>
       </c>
@@ -2661,7 +2942,7 @@
       <c r="E44" t="s">
         <v>10</v>
       </c>
-      <c r="F44" t="s">
+      <c r="F44" s="6" t="s">
         <v>20</v>
       </c>
       <c r="G44">
@@ -2671,7 +2952,7 @@
         <v>129.31021759453901</v>
       </c>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:8">
       <c r="A45">
         <v>44</v>
       </c>
@@ -2687,7 +2968,7 @@
       <c r="E45" t="s">
         <v>64</v>
       </c>
-      <c r="F45" t="s">
+      <c r="F45" s="6" t="s">
         <v>11</v>
       </c>
       <c r="G45">
@@ -2697,7 +2978,7 @@
         <v>129.30858345615701</v>
       </c>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:8">
       <c r="A46">
         <v>45</v>
       </c>
@@ -2713,7 +2994,7 @@
       <c r="E46" t="s">
         <v>10</v>
       </c>
-      <c r="F46" t="s">
+      <c r="F46" s="6" t="s">
         <v>187</v>
       </c>
       <c r="G46">
@@ -2723,7 +3004,7 @@
         <v>129.334901038727</v>
       </c>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:8">
       <c r="A47">
         <v>46</v>
       </c>
@@ -2739,7 +3020,7 @@
       <c r="E47" t="s">
         <v>10</v>
       </c>
-      <c r="F47" t="s">
+      <c r="F47" s="6" t="s">
         <v>11</v>
       </c>
       <c r="G47">
@@ -2749,7 +3030,7 @@
         <v>129.32268218764199</v>
       </c>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:8">
       <c r="A48">
         <v>47</v>
       </c>
@@ -2765,7 +3046,7 @@
       <c r="E48" t="s">
         <v>135</v>
       </c>
-      <c r="F48" t="s">
+      <c r="F48" s="6" t="s">
         <v>11</v>
       </c>
       <c r="G48">
@@ -2775,7 +3056,7 @@
         <v>129.32704582909801</v>
       </c>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:8">
       <c r="A49">
         <v>48</v>
       </c>
@@ -2791,7 +3072,7 @@
       <c r="E49" t="s">
         <v>10</v>
       </c>
-      <c r="F49" t="s">
+      <c r="F49" s="6" t="s">
         <v>11</v>
       </c>
       <c r="G49">
@@ -2801,7 +3082,7 @@
         <v>129.32991157348201</v>
       </c>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:8">
       <c r="A50">
         <v>49</v>
       </c>
@@ -2817,7 +3098,7 @@
       <c r="E50" t="s">
         <v>93</v>
       </c>
-      <c r="F50" t="s">
+      <c r="F50" s="6" t="s">
         <v>11</v>
       </c>
       <c r="G50">
@@ -2827,7 +3108,7 @@
         <v>129.30194271522601</v>
       </c>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:8">
       <c r="A51">
         <v>50</v>
       </c>
@@ -2843,7 +3124,7 @@
       <c r="E51" t="s">
         <v>10</v>
       </c>
-      <c r="F51" t="s">
+      <c r="F51" s="6" t="s">
         <v>187</v>
       </c>
       <c r="G51">
@@ -2853,7 +3134,7 @@
         <v>129.31749376133601</v>
       </c>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:8">
       <c r="A52">
         <v>51</v>
       </c>
@@ -2869,7 +3150,7 @@
       <c r="E52" t="s">
         <v>10</v>
       </c>
-      <c r="F52" t="s">
+      <c r="F52" s="6" t="s">
         <v>11</v>
       </c>
       <c r="G52">
@@ -2879,7 +3160,7 @@
         <v>129.31749376133601</v>
       </c>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:8">
       <c r="A53">
         <v>52</v>
       </c>
@@ -2895,7 +3176,7 @@
       <c r="E53" t="s">
         <v>10</v>
       </c>
-      <c r="F53" t="s">
+      <c r="F53" s="6" t="s">
         <v>11</v>
       </c>
       <c r="G53">
@@ -2905,7 +3186,7 @@
         <v>129.337495790666</v>
       </c>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:8">
       <c r="A54">
         <v>53</v>
       </c>
@@ -2921,7 +3202,7 @@
       <c r="E54" t="s">
         <v>10</v>
       </c>
-      <c r="F54" t="s">
+      <c r="F54" s="6" t="s">
         <v>11</v>
       </c>
       <c r="G54">
@@ -2931,7 +3212,7 @@
         <v>129.32938991855301</v>
       </c>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:8">
       <c r="A55">
         <v>54</v>
       </c>
@@ -2947,7 +3228,7 @@
       <c r="E55" t="s">
         <v>10</v>
       </c>
-      <c r="F55" t="s">
+      <c r="F55" s="6" t="s">
         <v>188</v>
       </c>
       <c r="G55">
@@ -2957,7 +3238,7 @@
         <v>129.33276957269501</v>
       </c>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:8">
       <c r="A56">
         <v>55</v>
       </c>
@@ -2973,7 +3254,7 @@
       <c r="E56" t="s">
         <v>36</v>
       </c>
-      <c r="F56" t="s">
+      <c r="F56" s="6" t="s">
         <v>11</v>
       </c>
       <c r="G56">
@@ -2983,7 +3264,7 @@
         <v>129.34719219842799</v>
       </c>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:8">
       <c r="A57">
         <v>56</v>
       </c>
@@ -2999,7 +3280,7 @@
       <c r="E57" t="s">
         <v>36</v>
       </c>
-      <c r="F57" t="s">
+      <c r="F57" s="6" t="s">
         <v>11</v>
       </c>
       <c r="G57">
@@ -3009,7 +3290,7 @@
         <v>129.337436690766</v>
       </c>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:8">
       <c r="A58">
         <v>57</v>
       </c>
@@ -3025,7 +3306,7 @@
       <c r="E58" t="s">
         <v>64</v>
       </c>
-      <c r="F58" t="s">
+      <c r="F58" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G58">
@@ -3035,7 +3316,7 @@
         <v>129.30959998798701</v>
       </c>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:8">
       <c r="A59">
         <v>58</v>
       </c>
@@ -3061,7 +3342,7 @@
         <v>129.34773887451399</v>
       </c>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:8">
       <c r="A60">
         <v>59</v>
       </c>
@@ -3087,7 +3368,7 @@
         <v>129.32796607151101</v>
       </c>
     </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:8">
       <c r="A61">
         <v>60</v>
       </c>
@@ -3113,7 +3394,7 @@
         <v>129.32761912511799</v>
       </c>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:8">
       <c r="A62">
         <v>61</v>
       </c>
@@ -3139,7 +3420,7 @@
         <v>129.33454593378599</v>
       </c>
     </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:8">
       <c r="A63">
         <v>62</v>
       </c>
@@ -3165,7 +3446,7 @@
         <v>129.33141894784401</v>
       </c>
     </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:8">
       <c r="A64">
         <v>63</v>
       </c>
@@ -3191,7 +3472,7 @@
         <v>129.33133707067299</v>
       </c>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:8">
       <c r="A65">
         <v>64</v>
       </c>
@@ -3217,7 +3498,7 @@
         <v>129.34715485530299</v>
       </c>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:8">
       <c r="A66">
         <v>65</v>
       </c>
@@ -3243,7 +3524,7 @@
         <v>129.33926986466699</v>
       </c>
     </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:8">
       <c r="A67">
         <v>66</v>
       </c>
@@ -3269,7 +3550,7 @@
         <v>129.32761912511799</v>
       </c>
     </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:8">
       <c r="A68">
         <v>67</v>
       </c>
@@ -3295,7 +3576,7 @@
         <v>129.309630937603</v>
       </c>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:8">
       <c r="A69">
         <v>68</v>
       </c>
@@ -3321,7 +3602,7 @@
         <v>129.31561270768299</v>
       </c>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:8">
       <c r="A70">
         <v>69</v>
       </c>
@@ -3341,7 +3622,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:8">
       <c r="A71">
         <v>70</v>
       </c>
@@ -3361,7 +3642,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:8">
       <c r="A72">
         <v>71</v>
       </c>
@@ -3381,7 +3662,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:8">
       <c r="A73">
         <v>72</v>
       </c>
@@ -3401,7 +3682,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:8">
       <c r="A74">
         <v>73</v>
       </c>
@@ -3421,7 +3702,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:8">
       <c r="A75">
         <v>74</v>
       </c>
@@ -3441,7 +3722,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:8">
       <c r="A76">
         <v>75</v>
       </c>
@@ -3461,7 +3742,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:8">
       <c r="A77">
         <v>76</v>
       </c>
@@ -3481,7 +3762,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:8">
       <c r="A78">
         <v>77</v>
       </c>
@@ -3501,7 +3782,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:8">
       <c r="A79">
         <v>78</v>
       </c>
@@ -3521,7 +3802,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:8">
       <c r="A80">
         <v>79</v>
       </c>
@@ -3541,7 +3822,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:7">
       <c r="A81" s="7">
         <v>80</v>
       </c>
@@ -3562,7 +3843,7 @@
       </c>
       <c r="G81" s="7"/>
     </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:7">
       <c r="A82" s="7">
         <v>81</v>
       </c>
@@ -3583,7 +3864,7 @@
       </c>
       <c r="G82" s="7"/>
     </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:7">
       <c r="A83" s="7">
         <v>82</v>
       </c>
@@ -3604,7 +3885,7 @@
       </c>
       <c r="G83" s="7"/>
     </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:7">
       <c r="A84" s="7">
         <v>83</v>
       </c>
@@ -3625,7 +3906,7 @@
       </c>
       <c r="G84" s="7"/>
     </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:7">
       <c r="A85" s="7">
         <v>84</v>
       </c>
@@ -3646,7 +3927,7 @@
       </c>
       <c r="G85" s="7"/>
     </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:7">
       <c r="A86" s="7">
         <v>85</v>
       </c>
@@ -3667,7 +3948,7 @@
       </c>
       <c r="G86" s="7"/>
     </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:7">
       <c r="A87" s="7">
         <v>86</v>
       </c>
@@ -3688,7 +3969,7 @@
       </c>
       <c r="G87" s="7"/>
     </row>
-    <row r="88" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:7">
       <c r="A88" s="7">
         <v>87</v>
       </c>
@@ -3704,12 +3985,12 @@
       <c r="E88" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="F88" s="3" t="s">
+      <c r="F88" s="4" t="s">
         <v>196</v>
       </c>
       <c r="G88" s="7"/>
     </row>
-    <row r="89" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:7" ht="33">
       <c r="A89" s="7">
         <v>88</v>
       </c>
@@ -3725,12 +4006,12 @@
       <c r="E89" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="F89" s="3" t="s">
+      <c r="F89" s="4" t="s">
         <v>196</v>
       </c>
       <c r="G89" s="7"/>
     </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:7">
       <c r="A90" s="7">
         <v>89</v>
       </c>
@@ -3746,12 +4027,12 @@
       <c r="E90" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="F90" s="3" t="s">
+      <c r="F90" s="4" t="s">
         <v>196</v>
       </c>
       <c r="G90" s="7"/>
     </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:7">
       <c r="A91" s="7">
         <v>90</v>
       </c>
@@ -3767,12 +4048,12 @@
       <c r="E91" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="F91" s="3" t="s">
+      <c r="F91" s="4" t="s">
         <v>196</v>
       </c>
       <c r="G91" s="7"/>
     </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:7">
       <c r="A92" s="7">
         <v>91</v>
       </c>
@@ -3788,12 +4069,12 @@
       <c r="E92" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="F92" s="3" t="s">
+      <c r="F92" s="4" t="s">
         <v>196</v>
       </c>
       <c r="G92" s="7"/>
     </row>
-    <row r="93" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:7">
       <c r="A93" s="7">
         <v>92</v>
       </c>
@@ -3809,12 +4090,12 @@
       <c r="E93" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="F93" s="3" t="s">
+      <c r="F93" s="4" t="s">
         <v>239</v>
       </c>
       <c r="G93" s="7"/>
     </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:7">
       <c r="A94" s="7">
         <v>93</v>
       </c>
@@ -3830,12 +4111,12 @@
       <c r="E94" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="F94" s="3" t="s">
+      <c r="F94" s="4" t="s">
         <v>196</v>
       </c>
       <c r="G94" s="7"/>
     </row>
-    <row r="95" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:7">
       <c r="A95" s="7">
         <v>94</v>
       </c>
@@ -3851,12 +4132,12 @@
       <c r="E95" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="F95" s="3" t="s">
+      <c r="F95" s="4" t="s">
         <v>221</v>
       </c>
       <c r="G95" s="7"/>
     </row>
-    <row r="96" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:7">
       <c r="A96" s="7">
         <v>95</v>
       </c>
@@ -3872,12 +4153,12 @@
       <c r="E96" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="F96" s="3" t="s">
+      <c r="F96" s="4" t="s">
         <v>323</v>
       </c>
       <c r="G96" s="7"/>
     </row>
-    <row r="97" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:7" ht="33">
       <c r="A97" s="7">
         <v>96</v>
       </c>
@@ -3893,12 +4174,12 @@
       <c r="E97" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="F97" s="3" t="s">
+      <c r="F97" s="4" t="s">
         <v>236</v>
       </c>
       <c r="G97" s="7"/>
     </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:7">
       <c r="A98" s="7">
         <v>97</v>
       </c>
@@ -3914,12 +4195,12 @@
       <c r="E98" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="F98" s="3" t="s">
+      <c r="F98" s="4" t="s">
         <v>221</v>
       </c>
       <c r="G98" s="7"/>
     </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:7">
       <c r="A99" s="7">
         <v>98</v>
       </c>
@@ -3935,12 +4216,12 @@
       <c r="E99" s="3" t="s">
         <v>237</v>
       </c>
-      <c r="F99" s="2" t="s">
+      <c r="F99" s="4" t="s">
         <v>322</v>
       </c>
       <c r="G99" s="7"/>
     </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:7">
       <c r="A100" s="7">
         <v>99</v>
       </c>
@@ -3956,12 +4237,12 @@
       <c r="E100" s="3" t="s">
         <v>209</v>
       </c>
-      <c r="F100" s="3" t="s">
+      <c r="F100" s="4" t="s">
         <v>239</v>
       </c>
       <c r="G100" s="7"/>
     </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:7">
       <c r="A101" s="7">
         <v>100</v>
       </c>
@@ -3977,12 +4258,12 @@
       <c r="E101" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="F101" s="3" t="s">
+      <c r="F101" s="4" t="s">
         <v>196</v>
       </c>
       <c r="G101" s="7"/>
     </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:7">
       <c r="A102" s="7">
         <v>101</v>
       </c>
@@ -3998,12 +4279,12 @@
       <c r="E102" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="F102" s="3" t="s">
+      <c r="F102" s="4" t="s">
         <v>196</v>
       </c>
       <c r="G102" s="7"/>
     </row>
-    <row r="103" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:7">
       <c r="A103" s="7">
         <v>102</v>
       </c>
@@ -4019,12 +4300,12 @@
       <c r="E103" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="F103" s="3" t="s">
+      <c r="F103" s="4" t="s">
         <v>196</v>
       </c>
       <c r="G103" s="7"/>
     </row>
-    <row r="104" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:7">
       <c r="A104" s="7">
         <v>103</v>
       </c>
@@ -4040,12 +4321,12 @@
       <c r="E104" s="3" t="s">
         <v>237</v>
       </c>
-      <c r="F104" s="3" t="s">
+      <c r="F104" s="4" t="s">
         <v>196</v>
       </c>
       <c r="G104" s="7"/>
     </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:7">
       <c r="A105" s="7">
         <v>104</v>
       </c>
@@ -4061,12 +4342,12 @@
       <c r="E105" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="F105" s="3" t="s">
+      <c r="F105" s="4" t="s">
         <v>196</v>
       </c>
       <c r="G105" s="7"/>
     </row>
-    <row r="106" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:7">
       <c r="A106" s="7">
         <v>105</v>
       </c>
@@ -4082,12 +4363,12 @@
       <c r="E106" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="F106" s="3" t="s">
+      <c r="F106" s="4" t="s">
         <v>196</v>
       </c>
       <c r="G106" s="7"/>
     </row>
-    <row r="107" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:7">
       <c r="A107" s="7">
         <v>106</v>
       </c>
@@ -4103,12 +4384,12 @@
       <c r="E107" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="F107" s="3" t="s">
+      <c r="F107" s="4" t="s">
         <v>196</v>
       </c>
       <c r="G107" s="7"/>
     </row>
-    <row r="108" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:7">
       <c r="A108" s="7">
         <v>107</v>
       </c>
@@ -4124,12 +4405,12 @@
       <c r="E108" s="3" t="s">
         <v>237</v>
       </c>
-      <c r="F108" s="3" t="s">
+      <c r="F108" s="4" t="s">
         <v>221</v>
       </c>
       <c r="G108" s="7"/>
     </row>
-    <row r="109" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:7">
       <c r="A109" s="7">
         <v>108</v>
       </c>
@@ -4145,12 +4426,12 @@
       <c r="E109" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="F109" s="3" t="s">
+      <c r="F109" s="4" t="s">
         <v>196</v>
       </c>
       <c r="G109" s="7"/>
     </row>
-    <row r="110" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:7">
       <c r="A110" s="7">
         <v>109</v>
       </c>
@@ -4166,33 +4447,33 @@
       <c r="E110" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="F110" s="3" t="s">
+      <c r="F110" s="4" t="s">
         <v>221</v>
       </c>
       <c r="G110" s="7"/>
     </row>
-    <row r="111" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:7">
       <c r="A111" s="7">
         <v>110</v>
       </c>
-      <c r="B111" s="1">
-        <v>46211</v>
-      </c>
-      <c r="C111" s="7" t="s">
-        <v>309</v>
-      </c>
-      <c r="D111" s="2" t="s">
-        <v>263</v>
-      </c>
-      <c r="E111" s="3" t="s">
-        <v>238</v>
-      </c>
-      <c r="F111" s="3" t="s">
-        <v>196</v>
+      <c r="B111" s="11">
+        <v>46206</v>
+      </c>
+      <c r="C111" s="9" t="s">
+        <v>358</v>
+      </c>
+      <c r="D111" s="13" t="s">
+        <v>328</v>
+      </c>
+      <c r="E111" s="17" t="s">
+        <v>208</v>
+      </c>
+      <c r="F111" s="14" t="s">
+        <v>221</v>
       </c>
       <c r="G111" s="7"/>
     </row>
-    <row r="112" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:7">
       <c r="A112" s="7">
         <v>111</v>
       </c>
@@ -4200,20 +4481,20 @@
         <v>46211</v>
       </c>
       <c r="C112" s="7" t="s">
-        <v>303</v>
+        <v>309</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="E112" s="3" t="s">
         <v>238</v>
       </c>
-      <c r="F112" s="3" t="s">
+      <c r="F112" s="4" t="s">
         <v>196</v>
       </c>
       <c r="G112" s="7"/>
     </row>
-    <row r="113" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:7">
       <c r="A113" s="7">
         <v>112</v>
       </c>
@@ -4221,20 +4502,20 @@
         <v>46211</v>
       </c>
       <c r="C113" s="7" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D113" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="E113" s="3" t="s">
         <v>238</v>
       </c>
-      <c r="F113" s="3" t="s">
-        <v>221</v>
+      <c r="F113" s="4" t="s">
+        <v>196</v>
       </c>
       <c r="G113" s="7"/>
     </row>
-    <row r="114" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:7">
       <c r="A114" s="7">
         <v>113</v>
       </c>
@@ -4242,344 +4523,942 @@
         <v>46211</v>
       </c>
       <c r="C114" s="7" t="s">
-        <v>200</v>
+        <v>304</v>
       </c>
       <c r="D114" s="2" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="E114" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="F114" s="3" t="s">
-        <v>196</v>
+        <v>238</v>
+      </c>
+      <c r="F114" s="4" t="s">
+        <v>221</v>
       </c>
       <c r="G114" s="7"/>
     </row>
-    <row r="115" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:7">
       <c r="A115" s="7">
         <v>114</v>
       </c>
       <c r="B115" s="1">
-        <v>46216</v>
+        <v>46211</v>
       </c>
       <c r="C115" s="7" t="s">
-        <v>305</v>
-      </c>
-      <c r="D115" s="8" t="s">
-        <v>267</v>
+        <v>200</v>
+      </c>
+      <c r="D115" s="2" t="s">
+        <v>266</v>
       </c>
       <c r="E115" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="F115" s="3" t="s">
-        <v>221</v>
+      <c r="F115" s="4" t="s">
+        <v>196</v>
       </c>
       <c r="G115" s="7"/>
     </row>
-    <row r="116" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:7" ht="33">
       <c r="A116" s="7">
         <v>115</v>
       </c>
-      <c r="B116" s="1">
-        <v>46216</v>
-      </c>
-      <c r="C116" s="7" t="s">
-        <v>306</v>
-      </c>
-      <c r="D116" s="2" t="s">
-        <v>268</v>
-      </c>
-      <c r="E116" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="F116" s="3" t="s">
-        <v>196</v>
+      <c r="B116" s="11">
+        <v>46213</v>
+      </c>
+      <c r="C116" s="10" t="s">
+        <v>359</v>
+      </c>
+      <c r="D116" s="15" t="s">
+        <v>329</v>
+      </c>
+      <c r="E116" s="17" t="s">
+        <v>324</v>
+      </c>
+      <c r="F116" s="14" t="s">
+        <v>236</v>
       </c>
       <c r="G116" s="7"/>
     </row>
-    <row r="117" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:7" ht="33">
       <c r="A117" s="7">
         <v>116</v>
       </c>
       <c r="B117" s="1">
-        <v>46224</v>
+        <v>46216</v>
       </c>
       <c r="C117" s="7" t="s">
-        <v>307</v>
-      </c>
-      <c r="D117" s="2" t="s">
-        <v>269</v>
+        <v>305</v>
+      </c>
+      <c r="D117" s="8" t="s">
+        <v>267</v>
       </c>
       <c r="E117" s="3" t="s">
-        <v>238</v>
-      </c>
-      <c r="F117" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="F117" s="4" t="s">
         <v>221</v>
       </c>
       <c r="G117" s="7"/>
     </row>
-    <row r="118" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:7">
       <c r="A118" s="7">
         <v>117</v>
       </c>
       <c r="B118" s="1">
-        <v>46225</v>
-      </c>
-      <c r="C118" s="9" t="s">
-        <v>308</v>
+        <v>46216</v>
+      </c>
+      <c r="C118" s="7" t="s">
+        <v>306</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="E118" s="3" t="s">
-        <v>238</v>
-      </c>
-      <c r="F118" s="3" t="s">
-        <v>323</v>
+        <v>194</v>
+      </c>
+      <c r="F118" s="4" t="s">
+        <v>196</v>
       </c>
       <c r="G118" s="7"/>
     </row>
-    <row r="119" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:7">
       <c r="A119" s="7">
         <v>118</v>
       </c>
-      <c r="B119" s="1">
-        <v>46225</v>
-      </c>
-      <c r="C119" s="7" t="s">
-        <v>302</v>
-      </c>
-      <c r="D119" s="8" t="s">
-        <v>271</v>
-      </c>
-      <c r="E119" s="3" t="s">
-        <v>238</v>
-      </c>
-      <c r="F119" s="3" t="s">
-        <v>323</v>
+      <c r="B119" s="11">
+        <v>46216</v>
+      </c>
+      <c r="C119" s="10" t="s">
+        <v>360</v>
+      </c>
+      <c r="D119" s="14" t="s">
+        <v>330</v>
+      </c>
+      <c r="E119" s="17" t="s">
+        <v>206</v>
+      </c>
+      <c r="F119" s="14" t="s">
+        <v>196</v>
       </c>
       <c r="G119" s="7"/>
     </row>
-    <row r="120" spans="1:7" ht="49.5" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:7">
       <c r="A120" s="7">
         <v>119</v>
       </c>
-      <c r="B120" s="1">
-        <v>46226</v>
-      </c>
-      <c r="C120" s="7" t="s">
-        <v>310</v>
-      </c>
-      <c r="D120" s="8" t="s">
-        <v>272</v>
-      </c>
-      <c r="E120" s="3" t="s">
-        <v>238</v>
-      </c>
-      <c r="F120" s="3" t="s">
-        <v>196</v>
+      <c r="B120" s="11">
+        <v>46218</v>
+      </c>
+      <c r="C120" s="10" t="s">
+        <v>300</v>
+      </c>
+      <c r="D120" s="16" t="s">
+        <v>331</v>
+      </c>
+      <c r="E120" s="17" t="s">
+        <v>237</v>
+      </c>
+      <c r="F120" s="14" t="s">
+        <v>236</v>
       </c>
       <c r="G120" s="7"/>
     </row>
-    <row r="121" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:7">
       <c r="A121" s="7">
         <v>120</v>
       </c>
-      <c r="B121" s="1">
-        <v>46226</v>
-      </c>
-      <c r="C121" s="7" t="s">
-        <v>311</v>
-      </c>
-      <c r="D121" s="8" t="s">
-        <v>273</v>
-      </c>
-      <c r="E121" s="3" t="s">
-        <v>238</v>
-      </c>
-      <c r="F121" s="3" t="s">
-        <v>196</v>
+      <c r="B121" s="11">
+        <v>46223</v>
+      </c>
+      <c r="C121" s="10" t="s">
+        <v>361</v>
+      </c>
+      <c r="D121" s="14" t="s">
+        <v>332</v>
+      </c>
+      <c r="E121" s="17" t="s">
+        <v>237</v>
+      </c>
+      <c r="F121" s="14" t="s">
+        <v>236</v>
       </c>
       <c r="G121" s="7"/>
     </row>
-    <row r="122" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:7">
       <c r="A122" s="7">
         <v>121</v>
       </c>
-      <c r="B122" s="1">
-        <v>46226</v>
-      </c>
-      <c r="C122" s="7" t="s">
-        <v>312</v>
-      </c>
-      <c r="D122" s="8" t="s">
-        <v>274</v>
-      </c>
-      <c r="E122" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="F122" s="3" t="s">
-        <v>221</v>
+      <c r="B122" s="12">
+        <v>46223</v>
+      </c>
+      <c r="C122" s="10" t="s">
+        <v>362</v>
+      </c>
+      <c r="D122" s="14" t="s">
+        <v>333</v>
+      </c>
+      <c r="E122" s="17" t="s">
+        <v>325</v>
+      </c>
+      <c r="F122" s="14" t="s">
+        <v>196</v>
       </c>
       <c r="G122" s="7"/>
     </row>
-    <row r="123" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:7">
       <c r="A123" s="7">
         <v>122</v>
       </c>
-      <c r="B123" s="1">
-        <v>46230</v>
-      </c>
-      <c r="C123" s="7" t="s">
-        <v>313</v>
-      </c>
-      <c r="D123" s="8" t="s">
-        <v>275</v>
-      </c>
-      <c r="E123" s="3" t="s">
-        <v>238</v>
-      </c>
-      <c r="F123" s="3" t="s">
+      <c r="B123" s="12">
+        <v>46223</v>
+      </c>
+      <c r="C123" s="10" t="s">
+        <v>363</v>
+      </c>
+      <c r="D123" s="14" t="s">
+        <v>334</v>
+      </c>
+      <c r="E123" s="17" t="s">
+        <v>325</v>
+      </c>
+      <c r="F123" s="14" t="s">
         <v>196</v>
       </c>
       <c r="G123" s="7"/>
     </row>
-    <row r="124" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:7">
       <c r="A124" s="7">
         <v>123</v>
       </c>
-      <c r="B124" s="1">
+      <c r="B124" s="12">
+        <v>46223</v>
+      </c>
+      <c r="C124" s="10" t="s">
+        <v>364</v>
+      </c>
+      <c r="D124" s="14" t="s">
+        <v>335</v>
+      </c>
+      <c r="E124" s="17" t="s">
+        <v>325</v>
+      </c>
+      <c r="F124" s="14" t="s">
+        <v>196</v>
+      </c>
+      <c r="G124" s="7"/>
+    </row>
+    <row r="125" spans="1:7">
+      <c r="A125" s="18">
+        <v>124</v>
+      </c>
+      <c r="B125" s="12">
+        <v>46223</v>
+      </c>
+      <c r="C125" s="10" t="s">
+        <v>365</v>
+      </c>
+      <c r="D125" s="14" t="s">
+        <v>336</v>
+      </c>
+      <c r="E125" s="17" t="s">
+        <v>325</v>
+      </c>
+      <c r="F125" s="14" t="s">
+        <v>236</v>
+      </c>
+      <c r="G125" s="7"/>
+    </row>
+    <row r="126" spans="1:7">
+      <c r="A126" s="18">
+        <v>125</v>
+      </c>
+      <c r="B126" s="12">
+        <v>46223</v>
+      </c>
+      <c r="C126" s="10" t="s">
+        <v>366</v>
+      </c>
+      <c r="D126" s="14" t="s">
+        <v>337</v>
+      </c>
+      <c r="E126" s="17" t="s">
+        <v>325</v>
+      </c>
+      <c r="F126" s="14" t="s">
+        <v>221</v>
+      </c>
+      <c r="G126" s="7"/>
+    </row>
+    <row r="127" spans="1:7">
+      <c r="A127" s="18">
+        <v>126</v>
+      </c>
+      <c r="B127" s="12">
+        <v>46223</v>
+      </c>
+      <c r="C127" s="10" t="s">
+        <v>367</v>
+      </c>
+      <c r="D127" s="14" t="s">
+        <v>338</v>
+      </c>
+      <c r="E127" s="17" t="s">
+        <v>325</v>
+      </c>
+      <c r="F127" s="14" t="s">
+        <v>236</v>
+      </c>
+      <c r="G127" s="7"/>
+    </row>
+    <row r="128" spans="1:7">
+      <c r="A128" s="18">
+        <v>127</v>
+      </c>
+      <c r="B128" s="12">
+        <v>46223</v>
+      </c>
+      <c r="C128" s="10" t="s">
+        <v>368</v>
+      </c>
+      <c r="D128" s="14" t="s">
+        <v>339</v>
+      </c>
+      <c r="E128" s="17" t="s">
+        <v>325</v>
+      </c>
+      <c r="F128" s="14" t="s">
+        <v>236</v>
+      </c>
+      <c r="G128" s="7"/>
+    </row>
+    <row r="129" spans="1:7">
+      <c r="A129" s="18">
+        <v>128</v>
+      </c>
+      <c r="B129" s="12">
+        <v>46223</v>
+      </c>
+      <c r="C129" s="10" t="s">
+        <v>369</v>
+      </c>
+      <c r="D129" s="14" t="s">
+        <v>340</v>
+      </c>
+      <c r="E129" s="17" t="s">
+        <v>325</v>
+      </c>
+      <c r="F129" s="14" t="s">
+        <v>236</v>
+      </c>
+      <c r="G129" s="7"/>
+    </row>
+    <row r="130" spans="1:7">
+      <c r="A130" s="18">
+        <v>129</v>
+      </c>
+      <c r="B130" s="12">
+        <v>46223</v>
+      </c>
+      <c r="C130" s="10" t="s">
+        <v>370</v>
+      </c>
+      <c r="D130" s="14" t="s">
+        <v>341</v>
+      </c>
+      <c r="E130" s="17" t="s">
+        <v>325</v>
+      </c>
+      <c r="F130" s="14" t="s">
+        <v>236</v>
+      </c>
+      <c r="G130" s="7"/>
+    </row>
+    <row r="131" spans="1:7">
+      <c r="A131" s="18">
+        <v>130</v>
+      </c>
+      <c r="B131" s="12">
+        <v>46223</v>
+      </c>
+      <c r="C131" s="10" t="s">
+        <v>371</v>
+      </c>
+      <c r="D131" s="14" t="s">
+        <v>342</v>
+      </c>
+      <c r="E131" s="17" t="s">
+        <v>325</v>
+      </c>
+      <c r="F131" s="14" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="132" spans="1:7">
+      <c r="A132" s="18">
+        <v>131</v>
+      </c>
+      <c r="B132" s="12">
+        <v>46223</v>
+      </c>
+      <c r="C132" s="10" t="s">
+        <v>372</v>
+      </c>
+      <c r="D132" s="14" t="s">
+        <v>343</v>
+      </c>
+      <c r="E132" s="17" t="s">
+        <v>325</v>
+      </c>
+      <c r="F132" s="14" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="133" spans="1:7">
+      <c r="A133" s="18">
+        <v>132</v>
+      </c>
+      <c r="B133" s="12">
+        <v>46224</v>
+      </c>
+      <c r="C133" s="18" t="s">
+        <v>307</v>
+      </c>
+      <c r="D133" s="19" t="s">
+        <v>269</v>
+      </c>
+      <c r="E133" s="17" t="s">
+        <v>238</v>
+      </c>
+      <c r="F133" s="14" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="134" spans="1:7">
+      <c r="A134" s="18">
+        <v>133</v>
+      </c>
+      <c r="B134" s="12">
+        <v>46225</v>
+      </c>
+      <c r="C134" s="20" t="s">
+        <v>308</v>
+      </c>
+      <c r="D134" s="19" t="s">
+        <v>270</v>
+      </c>
+      <c r="E134" s="17" t="s">
+        <v>238</v>
+      </c>
+      <c r="F134" s="14" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="135" spans="1:7">
+      <c r="A135" s="18">
+        <v>134</v>
+      </c>
+      <c r="B135" s="12">
+        <v>46225</v>
+      </c>
+      <c r="C135" s="18" t="s">
+        <v>302</v>
+      </c>
+      <c r="D135" s="21" t="s">
+        <v>271</v>
+      </c>
+      <c r="E135" s="17" t="s">
+        <v>238</v>
+      </c>
+      <c r="F135" s="14" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="136" spans="1:7">
+      <c r="A136" s="18">
+        <v>135</v>
+      </c>
+      <c r="B136" s="11">
+        <v>46225</v>
+      </c>
+      <c r="C136" s="10" t="s">
+        <v>373</v>
+      </c>
+      <c r="D136" s="14" t="s">
+        <v>344</v>
+      </c>
+      <c r="E136" s="17" t="s">
+        <v>326</v>
+      </c>
+      <c r="F136" s="14" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="137" spans="1:7">
+      <c r="A137" s="18">
+        <v>136</v>
+      </c>
+      <c r="B137" s="12">
+        <v>46225</v>
+      </c>
+      <c r="C137" s="10" t="s">
+        <v>374</v>
+      </c>
+      <c r="D137" s="14" t="s">
+        <v>345</v>
+      </c>
+      <c r="E137" s="17" t="s">
+        <v>325</v>
+      </c>
+      <c r="F137" s="14" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="138" spans="1:7">
+      <c r="A138" s="18">
+        <v>137</v>
+      </c>
+      <c r="B138" s="12">
+        <v>46225</v>
+      </c>
+      <c r="C138" s="10" t="s">
+        <v>364</v>
+      </c>
+      <c r="D138" s="14" t="s">
+        <v>346</v>
+      </c>
+      <c r="E138" s="17" t="s">
+        <v>325</v>
+      </c>
+      <c r="F138" s="14" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="139" spans="1:7">
+      <c r="A139" s="18">
+        <v>138</v>
+      </c>
+      <c r="B139" s="12">
+        <v>46225</v>
+      </c>
+      <c r="C139" s="10" t="s">
+        <v>375</v>
+      </c>
+      <c r="D139" s="14" t="s">
+        <v>347</v>
+      </c>
+      <c r="E139" s="17" t="s">
+        <v>325</v>
+      </c>
+      <c r="F139" s="14" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="140" spans="1:7">
+      <c r="A140" s="18">
+        <v>139</v>
+      </c>
+      <c r="B140" s="12">
+        <v>46225</v>
+      </c>
+      <c r="C140" s="10" t="s">
+        <v>376</v>
+      </c>
+      <c r="D140" s="14" t="s">
+        <v>348</v>
+      </c>
+      <c r="E140" s="17" t="s">
+        <v>325</v>
+      </c>
+      <c r="F140" s="14" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="141" spans="1:7">
+      <c r="A141" s="18">
+        <v>140</v>
+      </c>
+      <c r="B141" s="12">
+        <v>46225</v>
+      </c>
+      <c r="C141" s="10" t="s">
+        <v>377</v>
+      </c>
+      <c r="D141" s="14" t="s">
+        <v>349</v>
+      </c>
+      <c r="E141" s="17" t="s">
+        <v>325</v>
+      </c>
+      <c r="F141" s="14" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="142" spans="1:7">
+      <c r="A142" s="18">
+        <v>141</v>
+      </c>
+      <c r="B142" s="12">
+        <v>46225</v>
+      </c>
+      <c r="C142" s="10" t="s">
+        <v>378</v>
+      </c>
+      <c r="D142" s="14" t="s">
+        <v>350</v>
+      </c>
+      <c r="E142" s="17" t="s">
+        <v>325</v>
+      </c>
+      <c r="F142" s="14" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="143" spans="1:7">
+      <c r="A143" s="18">
+        <v>142</v>
+      </c>
+      <c r="B143" s="12">
+        <v>46225</v>
+      </c>
+      <c r="C143" s="10" t="s">
+        <v>378</v>
+      </c>
+      <c r="D143" s="14" t="s">
+        <v>351</v>
+      </c>
+      <c r="E143" s="17" t="s">
+        <v>325</v>
+      </c>
+      <c r="F143" s="14" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="144" spans="1:7">
+      <c r="A144" s="18">
+        <v>143</v>
+      </c>
+      <c r="B144" s="12">
+        <v>46225</v>
+      </c>
+      <c r="C144" s="10" t="s">
+        <v>378</v>
+      </c>
+      <c r="D144" s="22" t="s">
+        <v>352</v>
+      </c>
+      <c r="E144" s="17" t="s">
+        <v>325</v>
+      </c>
+      <c r="F144" s="14" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="145" spans="1:6">
+      <c r="A145" s="18">
+        <v>144</v>
+      </c>
+      <c r="B145" s="12">
+        <v>46225</v>
+      </c>
+      <c r="C145" s="10" t="s">
+        <v>379</v>
+      </c>
+      <c r="D145" s="22" t="s">
+        <v>353</v>
+      </c>
+      <c r="E145" s="17" t="s">
+        <v>325</v>
+      </c>
+      <c r="F145" s="14" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="146" spans="1:6">
+      <c r="A146" s="18">
+        <v>145</v>
+      </c>
+      <c r="B146" s="12">
+        <v>46225</v>
+      </c>
+      <c r="C146" s="10" t="s">
+        <v>380</v>
+      </c>
+      <c r="D146" s="22" t="s">
+        <v>354</v>
+      </c>
+      <c r="E146" s="17" t="s">
+        <v>325</v>
+      </c>
+      <c r="F146" s="14" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="147" spans="1:6">
+      <c r="A147" s="18">
+        <v>146</v>
+      </c>
+      <c r="B147" s="12">
+        <v>46225</v>
+      </c>
+      <c r="C147" s="10" t="s">
+        <v>364</v>
+      </c>
+      <c r="D147" s="14" t="s">
+        <v>355</v>
+      </c>
+      <c r="E147" s="17" t="s">
+        <v>325</v>
+      </c>
+      <c r="F147" s="14" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="148" spans="1:6" ht="49.5">
+      <c r="A148" s="18">
+        <v>147</v>
+      </c>
+      <c r="B148" s="12">
+        <v>46226</v>
+      </c>
+      <c r="C148" s="18" t="s">
+        <v>310</v>
+      </c>
+      <c r="D148" s="21" t="s">
+        <v>272</v>
+      </c>
+      <c r="E148" s="17" t="s">
+        <v>238</v>
+      </c>
+      <c r="F148" s="14" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="149" spans="1:6" ht="33">
+      <c r="A149" s="18">
+        <v>148</v>
+      </c>
+      <c r="B149" s="12">
+        <v>46226</v>
+      </c>
+      <c r="C149" s="18" t="s">
+        <v>311</v>
+      </c>
+      <c r="D149" s="21" t="s">
+        <v>273</v>
+      </c>
+      <c r="E149" s="17" t="s">
+        <v>238</v>
+      </c>
+      <c r="F149" s="14" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="150" spans="1:6">
+      <c r="A150" s="18">
+        <v>149</v>
+      </c>
+      <c r="B150" s="12">
+        <v>46226</v>
+      </c>
+      <c r="C150" s="18" t="s">
+        <v>312</v>
+      </c>
+      <c r="D150" s="21" t="s">
+        <v>274</v>
+      </c>
+      <c r="E150" s="17" t="s">
+        <v>194</v>
+      </c>
+      <c r="F150" s="14" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="151" spans="1:6">
+      <c r="A151" s="18">
+        <v>150</v>
+      </c>
+      <c r="B151" s="11">
+        <v>46226</v>
+      </c>
+      <c r="C151" s="10" t="s">
+        <v>381</v>
+      </c>
+      <c r="D151" s="14" t="s">
+        <v>356</v>
+      </c>
+      <c r="E151" s="17" t="s">
+        <v>237</v>
+      </c>
+      <c r="F151" s="14" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="152" spans="1:6">
+      <c r="A152" s="18">
+        <v>151</v>
+      </c>
+      <c r="B152" s="12">
         <v>46230</v>
       </c>
-      <c r="C124" s="7" t="s">
+      <c r="C152" s="18" t="s">
+        <v>313</v>
+      </c>
+      <c r="D152" s="21" t="s">
+        <v>275</v>
+      </c>
+      <c r="E152" s="17" t="s">
+        <v>238</v>
+      </c>
+      <c r="F152" s="14" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="153" spans="1:6">
+      <c r="A153" s="18">
+        <v>152</v>
+      </c>
+      <c r="B153" s="12">
+        <v>46230</v>
+      </c>
+      <c r="C153" s="18" t="s">
         <v>314</v>
       </c>
-      <c r="D124" s="8" t="s">
+      <c r="D153" s="21" t="s">
         <v>316</v>
       </c>
-      <c r="E124" s="3" t="s">
+      <c r="E153" s="17" t="s">
         <v>194</v>
       </c>
-      <c r="F124" s="3" t="s">
+      <c r="F153" s="14" t="s">
         <v>196</v>
       </c>
-      <c r="G124" s="7"/>
-    </row>
-    <row r="125" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A125" s="7">
-        <v>124</v>
-      </c>
-      <c r="B125" s="1">
+    </row>
+    <row r="154" spans="1:6">
+      <c r="A154" s="18">
+        <v>153</v>
+      </c>
+      <c r="B154" s="12">
         <v>46230</v>
       </c>
-      <c r="C125" s="7" t="s">
+      <c r="C154" s="18" t="s">
         <v>315</v>
       </c>
-      <c r="D125" s="8" t="s">
+      <c r="D154" s="21" t="s">
         <v>317</v>
       </c>
-      <c r="E125" s="3" t="s">
+      <c r="E154" s="17" t="s">
         <v>194</v>
       </c>
-      <c r="F125" s="3" t="s">
+      <c r="F154" s="14" t="s">
         <v>196</v>
       </c>
-      <c r="G125" s="7"/>
-    </row>
-    <row r="126" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A126" s="7">
-        <v>125</v>
-      </c>
-      <c r="B126" s="1">
+    </row>
+    <row r="155" spans="1:6">
+      <c r="A155" s="18">
+        <v>154</v>
+      </c>
+      <c r="B155" s="12">
         <v>46234</v>
       </c>
-      <c r="C126" s="7" t="s">
+      <c r="C155" s="18" t="s">
         <v>318</v>
       </c>
-      <c r="D126" s="8" t="s">
+      <c r="D155" s="21" t="s">
         <v>276</v>
       </c>
-      <c r="E126" s="3" t="s">
+      <c r="E155" s="17" t="s">
         <v>238</v>
       </c>
-      <c r="F126" s="3" t="s">
+      <c r="F155" s="14" t="s">
         <v>196</v>
       </c>
-      <c r="G126" s="7"/>
-    </row>
-    <row r="127" spans="1:7" ht="33" x14ac:dyDescent="0.3">
-      <c r="A127" s="7">
-        <v>126</v>
-      </c>
-      <c r="B127" s="1">
+    </row>
+    <row r="156" spans="1:6" ht="33">
+      <c r="A156" s="18">
+        <v>155</v>
+      </c>
+      <c r="B156" s="12">
         <v>46234</v>
       </c>
-      <c r="C127" s="7" t="s">
+      <c r="C156" s="18" t="s">
         <v>319</v>
       </c>
-      <c r="D127" s="8" t="s">
+      <c r="D156" s="21" t="s">
         <v>277</v>
       </c>
-      <c r="E127" s="3" t="s">
+      <c r="E156" s="17" t="s">
         <v>238</v>
       </c>
-      <c r="F127" s="3" t="s">
+      <c r="F156" s="14" t="s">
         <v>236</v>
       </c>
-      <c r="G127" s="7"/>
-    </row>
-    <row r="128" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A128" s="7">
-        <v>127</v>
-      </c>
-      <c r="B128" s="1">
+    </row>
+    <row r="157" spans="1:6">
+      <c r="A157" s="18">
+        <v>156</v>
+      </c>
+      <c r="B157" s="11">
+        <v>46234</v>
+      </c>
+      <c r="C157" s="10" t="s">
+        <v>301</v>
+      </c>
+      <c r="D157" s="14" t="s">
+        <v>357</v>
+      </c>
+      <c r="E157" s="17" t="s">
+        <v>327</v>
+      </c>
+      <c r="F157" s="14" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="158" spans="1:6">
+      <c r="A158" s="18">
+        <v>157</v>
+      </c>
+      <c r="B158" s="12">
         <v>46237</v>
       </c>
-      <c r="C128" s="7" t="s">
+      <c r="C158" s="18" t="s">
         <v>320</v>
       </c>
-      <c r="D128" s="8" t="s">
+      <c r="D158" s="21" t="s">
         <v>278</v>
       </c>
-      <c r="E128" s="3" t="s">
+      <c r="E158" s="17" t="s">
         <v>194</v>
       </c>
-      <c r="F128" s="2" t="s">
+      <c r="F158" s="14" t="s">
         <v>322</v>
       </c>
-      <c r="G128" s="7"/>
-    </row>
-    <row r="129" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A129" s="7">
-        <v>128</v>
-      </c>
-      <c r="B129" s="1">
+    </row>
+    <row r="159" spans="1:6">
+      <c r="A159" s="18">
+        <v>158</v>
+      </c>
+      <c r="B159" s="12">
         <v>46237</v>
       </c>
-      <c r="C129" s="7" t="s">
+      <c r="C159" s="18" t="s">
         <v>321</v>
       </c>
-      <c r="D129" s="8" t="s">
+      <c r="D159" s="21" t="s">
         <v>279</v>
       </c>
-      <c r="E129" s="3" t="s">
+      <c r="E159" s="17" t="s">
         <v>194</v>
       </c>
-      <c r="F129" s="2" t="s">
+      <c r="F159" s="14" t="s">
         <v>322</v>
       </c>
-      <c r="G129" s="7"/>
-    </row>
-    <row r="130" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A130" s="7"/>
-      <c r="B130" s="7"/>
-      <c r="C130" s="7"/>
-      <c r="D130" s="7"/>
-      <c r="E130" s="7"/>
-      <c r="F130" s="7"/>
-      <c r="G130" s="7"/>
+    </row>
+    <row r="160" spans="1:6">
+      <c r="F160" s="6"/>
     </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B109:F159">
+    <sortCondition ref="B109:B159"/>
+  </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/민원데이터.xlsx
+++ b/민원데이터.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\바탕화면\박현식\박현식 개인\코딩\민원관리 대시보드\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A5BBD4C-881A-4750-887F-765317F7E607}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{896D9126-1544-4D2F-81EC-A7BCAD390C10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-345" yWindow="1470" windowWidth="29100" windowHeight="13620" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="285" yWindow="1905" windowWidth="29100" windowHeight="13815" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="708" uniqueCount="382">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="952" uniqueCount="483">
   <si>
     <t>민원번호</t>
   </si>
@@ -1372,6 +1372,726 @@
   </si>
   <si>
     <t>울산 중구 다운동 779-6</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>병영성 북문지 주변(동동 216-1, 동동 830-17 일원) 도로패임 보수 요청</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>병영2동 주민센터 앞 삼일공원(서동 60-8 일원) 주차장 조성 사업 진행 현황</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>병영 휴쉼터 옆 공터(서동 253, 서동 254-2 일원) 주차장 바닥 보강</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>울산중구청-(주)이노뎁 계약정보 이력 일체</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>병영1동 태양빌라 옥상 불법건축물 제거 시 누수 발생 우려로 방수 시공이 필요한 상황임. 보조금 지원 가능 여부 확인 요청</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>새치삼거리 대광사 앞 인도 철제 시설물 제거 요청(구 버스정류장 의자 이용 시설)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>복산물놀이장 시설물에 묶여 있는 불필요한 케이블타이 제거 및 주변 시설 점검</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>우정공원물놀이장 앞 방치 쓰레기 수거 및 주변 환경정비</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>성안물놀이장 진입로 중 족구장 사이 구간 담배꽁초 및 쓰레기 수거</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>함월구민운동장 노후·부식된 나무 벤치 점검 후 수리 또는 교체</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>함월구민운동장 노후 운동기구 점검 후 수리 또는 교체</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>함월구민운동장 공연장 스탠드 세로면 탈락 석재 수리·보강 및 주변 석재 점검</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>함월구민운동장 고장 앰프 점검 후 수리 또는 교체</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>함월구민운동장 고장 먼지털이기 점검 및 수리·보수</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>동천자전거문화센터 바닥면 보수 시 노후·파손된 나무데크 전체 수리·보강</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>동천자전거문화센터 외부 방치 자전거 및 각종 자재 확인·정리</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>동천자전거문화센터 옆 제초작업 및 주변 환경정비</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>동천야외물놀이장 위 외솔큰길 인도 보도블록 점검 및 보수</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>성안물놀이장 물바구니 폭포 주변 바닥 탄성포장 구간 확대·보수 검토</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>학성동 가구삼거리~학성교 구간 도로 가로수 가지 처짐 발생으로 전지 요청</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>성안동823-10(정안정) 맞은편 나뭇가지 부러져 인도 보행 방해/위험 우려로 정비 요청</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>병영4길~병영로 진입 좌회전시 불법주정차로 인한 시야 방해 발생. 사고 위험 감소를 위한 반사경 설치 요청</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>동동 675번지 휴게쉼터 계단 옆 펜스 유격 발생(피스 헐거움)으로 넘어짐 사고 우려.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>병영성8길 53~장군신당 앞 삼거리 구역 내 맨홀 주변 도로 파손으로 소음 및 먼지 발생.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>서동 148-1번지 주차장 일원 도로 파손부 표시의 목적(보수 예정 등) 확인 요청</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>병영8길 30-4 주택 앞 음식물 쓰레기 배출로 악취 발생</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>병영성 동문지 및 산전 일원 잔디 식재 공사 관련 공사 시행 보조자로부터 부실공사 의혹 제기</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>성안동 833-1 싱크홀 보수 요청</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>현대홈마트 앞에서 내황공원 방향 골목 방범용 CCTV 설치를 2027년 대상지 심의에 반영 검토</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>반구1동 새마을금고 인근 골목 입구 자전거 옆 용도 불명 시설물·적치물의 소유·필요 여부 확인 후 수거·정비</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>반구정11길 6 인근에서 시장 안쪽 방향을 촬영하는 방범용 CCTV 설치를 2027년 대상지 심의에 반영 검토</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>반구정11길 6 인근 골목 모서리 방치 물품의 소유·관리 여부를 확인하고 불필요한 적치물 정리</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>반구2동 구교1길 1·신울산전문정비공업사 주변 오토바이·차량·카라반 상시 주차·적치 건의 도로구역·주정차 위반 여부 확인</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>신울산전문정비공업사 맞은편·구교1길 1 인근 방치 폐타이어·쓰레기 수거·정비</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>병영성4길 48 현대빌라 앞 인도 연석 도로부 돌출로 차량 접촉사고 빈번함. 제거 요청</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>황방산 등산로 입구(맨발걷기길 앞) 에어건 설치 요청</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>▲성안생활체육공원 테니스장 이용시간 제한 해제 및 객관적 소음 측정 요구 ▲출입문 임의 폐쇄에 따른 소극행정 지적 ▲대체 구장 제시안의 실효성 문제 제기 등</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>B-04 재개발 추진 과정의 적정성 문제제기</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>동천강변 가로등 인근 날씨정보 안내시설물의 벗겨진 도장면 재도색</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>동천강변 가로등 35번 인근 교량 아래 나무데크의 파손·들뜸 점검, 고정용 볼트 재체결 및 파손부위 보수</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>동천강변 가로등 35~37번 인근 고사목의 안전상 위험을 확인하고 제거 또는 정비</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>동천강 내 수중펌프·모터 관련 공사의 공사명·시행부서·작업내용·설치대수·고장원인·수리·교체내역·비용·점검주기 파악</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>청각장애인이 무인 공영주차장 이용 시 정산기 및 차단기 오류 발생했을 때 난감한 상황 발생. 이에 청각장애인을 위한 주차기계 시스템 개선 요청</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>병영성지하차도 내부 중앙분리대 부착 반사판이 먼지, 분진으로 인해 반사 기능 상실함. 교체 요청</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>강북로 도로 밀림 현상</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>용연암 버스정류소(정류소번호 73001) 전광판이 점등되지 않는 날이 자주 발생하므로 작동 상태와 고장 원인을 점검하고 정상 운영되도록 수리·정비</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>성안체육공원 테니스장 이용시간 제한 해제 등에 대한 민원 답변 처리 지연으로 답변 촉구</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>내황공원 정자의 페인트가 전반적으로 벗겨진 상태로, 현장 점검 후 정자 도색</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>내황공원 내 파고라의 부식·훼손된 바닥재를 교체하고 천장 도색</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>도화공원 내 보안등 5번·6번이 장기간 점등되지 않고 있어 작동 상태를 점검하고 신속히 수리·교체</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>반구시장</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>내</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>남자화장실의</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>대변기</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>소변기가</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>각각</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>개만</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>설치돼</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>있어</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>유휴</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>공간을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>활용한</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>대변기</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>소변기</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>추가</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>설치</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>검토</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>구교쉼터 파고라의 시공·관리 상태를 재점검하고 미흡한 부분 보수</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>반구사거리 일원의 노후·파손된 보도블록을 점검하고 필요한 구간 보수·재포장</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">성안동 1404번지 일원 농로공사현장에 우천에 의한 토사 유실 발생으로 붕괴 우려
+- 공사 기간 및 준공시 기존 울타리 재설치 이행 약속 여부 확인 </t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>태화강국가정원 위치한 '내오산로 2-7' 가로등 장기 미점등 점검 요망</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>이전 답변에 대한 불만 및 현장 확인을 통한 의견 청취 희망.
+6월 간담회 당시 중구청, 도시관리공단 측의 갑질 행위 및 '유곡테니스장'에 대한 오안내 주장</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>복산동 하림유통 앞 거주자우선주차구역(4-75-1) 배정 탈락에 따른 사유와 재신청 요구(010-3569-2000)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>남외3길 남외초, 남외중 일원 노후 보도블럭 정비 및 교체 요청</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>학성동 436-11 필지(구역전족발 등 상가) 용도변경을 위한 부설주차장 마련안에 대한 회신 불만 및 현장 방문 요구
+(교통과) 부설주차장 임대 방식 조성 불가, 건물 소유주가 취득한 부지에 설치시에만 검토 가능함 회신</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>계변로 48 (버스정류장 11506) 인근 보도블럭 위 잡초제거 요청</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>동천1길 69(서동) 한라하얏트 아파트 뒤편길 가로등 미점등 수리 요청</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>검토중</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>처리불가</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>의회누리집</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>울산 중구 동동 216-1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>울산 중구 서동 60-8</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>울산 중구 서동 253</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>울산 중구 동동 242</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>울산 중구 학산동 66-20</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>울산 중구 복산동 707</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>울산 중구 우정동 444</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>울산 중구 성안동 918-1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>울산 중구 남외동 634-1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>울산 중구 남외동 964</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>울산 중구 학성동 207-1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>울산 중구 성안동 823-10</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>울산 중구 남외동 271</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>울산 중구 서동 155-19</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>울산 중구 서동 148-1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>울산 중구 동동 642</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>울산 중구 동동 388</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>울산 중구 반구동 804-6</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>울산 중구 반구동 594-23</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>울산 중구 반구동 254</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>울산 중구 남외동 9-1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>울산 중구 장현동 469</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>울산 중구 성안동 900-6</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>울산 중구 북정동 58-6</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>울산 중구 동동 55-4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>울산 중구 강북로</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>울산 중구 반구동 644-85</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>울산 중구 복산동 205-1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>울산 중구 반구동 801</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>울산 중구 반구동 51-12</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>울산 중구 반구동 799</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>울산 중구 성안동 1404</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>울산 중구 태화동 343</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>울산 중구 복산동 418-19</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>울산 중구 남외동 518</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>울산 중구 학성동 414</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>울산 중구 서동 42-2</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1379,7 +2099,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6">
+  <fonts count="9">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1421,6 +2141,27 @@
       <family val="3"/>
       <charset val="129"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -1444,43 +2185,35 @@
   </cellStyleXfs>
   <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -1488,21 +2221,29 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1806,7 +2547,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H160"/>
+  <dimension ref="A1:H220"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="2" max="2" width="11.125" bestFit="1" customWidth="1"/>
@@ -1815,3651 +2556,5127 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
-      <c r="A1" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="3" t="s">
         <v>185</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="3" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:8">
-      <c r="A2">
+      <c r="A2" s="3">
         <v>1</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F2" t="s">
+      <c r="F2" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="G2">
+      <c r="G2" s="3">
         <v>35.580469557483802</v>
       </c>
-      <c r="H2">
+      <c r="H2" s="3">
         <v>129.334708123821</v>
       </c>
     </row>
     <row r="3" spans="1:8">
-      <c r="A3">
+      <c r="A3" s="3">
         <v>2</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="E3" t="s">
+      <c r="E3" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="F3" t="s">
+      <c r="F3" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="G3">
+      <c r="G3" s="3">
         <v>35.557218587790402</v>
       </c>
-      <c r="H3">
+      <c r="H3" s="3">
         <v>129.34914011636599</v>
       </c>
     </row>
     <row r="4" spans="1:8">
-      <c r="A4">
+      <c r="A4" s="3">
         <v>3</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D4" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="E4" t="s">
+      <c r="E4" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="F4" t="s">
+      <c r="F4" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="G4">
+      <c r="G4" s="3">
         <v>35.5713260857693</v>
       </c>
-      <c r="H4">
+      <c r="H4" s="3">
         <v>129.341655674116</v>
       </c>
     </row>
     <row r="5" spans="1:8">
-      <c r="A5">
+      <c r="A5" s="3">
         <v>4</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D5" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="E5" t="s">
+      <c r="E5" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="F5" s="6" t="s">
+      <c r="F5" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="G5">
+      <c r="G5" s="3">
         <v>35.577922593177099</v>
       </c>
-      <c r="H5">
+      <c r="H5" s="3">
         <v>129.348784402462</v>
       </c>
     </row>
     <row r="6" spans="1:8">
-      <c r="A6">
+      <c r="A6" s="3">
         <v>5</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C6" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="D6" t="s">
+      <c r="D6" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="E6" t="s">
+      <c r="E6" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F6" s="6" t="s">
+      <c r="F6" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="G6">
+      <c r="G6" s="3">
         <v>35.555464871860003</v>
       </c>
-      <c r="H6">
+      <c r="H6" s="3">
         <v>129.328386461436</v>
       </c>
     </row>
     <row r="7" spans="1:8">
-      <c r="A7">
+      <c r="A7" s="3">
         <v>6</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C7" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="D7" t="s">
+      <c r="D7" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="E7" t="s">
+      <c r="E7" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F7" s="6" t="s">
+      <c r="F7" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="G7">
+      <c r="G7" s="3">
         <v>35.590617968339103</v>
       </c>
-      <c r="H7">
+      <c r="H7" s="3">
         <v>129.293406307109</v>
       </c>
     </row>
     <row r="8" spans="1:8">
-      <c r="A8">
+      <c r="A8" s="3">
         <v>7</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C8" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="D8" t="s">
+      <c r="D8" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="E8" t="s">
+      <c r="E8" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F8" s="6" t="s">
+      <c r="F8" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="G8">
+      <c r="G8" s="3">
         <v>35.556862661251103</v>
       </c>
-      <c r="H8">
+      <c r="H8" s="3">
         <v>129.321138541696</v>
       </c>
     </row>
     <row r="9" spans="1:8">
-      <c r="A9">
+      <c r="A9" s="3">
         <v>8</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C9" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="D9" t="s">
+      <c r="D9" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="E9" t="s">
+      <c r="E9" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F9" s="6" t="s">
+      <c r="F9" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="G9">
+      <c r="G9" s="3">
         <v>35.557005249299998</v>
       </c>
-      <c r="H9">
+      <c r="H9" s="3">
         <v>129.336443953188</v>
       </c>
     </row>
     <row r="10" spans="1:8">
-      <c r="A10">
+      <c r="A10" s="3">
         <v>9</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="C10" t="s">
+      <c r="C10" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="D10" t="s">
+      <c r="D10" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="E10" t="s">
+      <c r="E10" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="F10" s="6" t="s">
+      <c r="F10" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="G10">
+      <c r="G10" s="3">
         <v>35.563824811119602</v>
       </c>
-      <c r="H10">
+      <c r="H10" s="3">
         <v>129.35126645610401</v>
       </c>
     </row>
     <row r="11" spans="1:8">
-      <c r="A11">
+      <c r="A11" s="3">
         <v>10</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B11" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="C11" t="s">
+      <c r="C11" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="D11" t="s">
+      <c r="D11" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="E11" t="s">
+      <c r="E11" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="F11" s="6" t="s">
+      <c r="F11" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="G11">
+      <c r="G11" s="3">
         <v>35.595422914415401</v>
       </c>
-      <c r="H11">
+      <c r="H11" s="3">
         <v>129.34604022411801</v>
       </c>
     </row>
     <row r="12" spans="1:8">
-      <c r="A12">
+      <c r="A12" s="3">
         <v>11</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B12" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="C12" t="s">
+      <c r="C12" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="D12" t="s">
+      <c r="D12" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="E12" t="s">
+      <c r="E12" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="F12" s="6" t="s">
+      <c r="F12" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="G12">
+      <c r="G12" s="3">
         <v>35.577184699448203</v>
       </c>
-      <c r="H12">
+      <c r="H12" s="3">
         <v>129.34512228457299</v>
       </c>
     </row>
     <row r="13" spans="1:8">
-      <c r="A13">
+      <c r="A13" s="3">
         <v>12</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B13" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="C13" t="s">
+      <c r="C13" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="D13" t="s">
+      <c r="D13" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="E13" t="s">
+      <c r="E13" s="3" t="s">
         <v>186</v>
       </c>
-      <c r="F13" s="6" t="s">
+      <c r="F13" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="G13">
+      <c r="G13" s="3">
         <v>35.568898288977401</v>
       </c>
-      <c r="H13">
+      <c r="H13" s="3">
         <v>129.265769674285</v>
       </c>
     </row>
     <row r="14" spans="1:8">
-      <c r="A14">
+      <c r="A14" s="3">
         <v>13</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B14" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="C14" t="s">
+      <c r="C14" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="D14" t="s">
+      <c r="D14" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="E14" t="s">
+      <c r="E14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F14" s="6" t="s">
+      <c r="F14" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="G14">
+      <c r="G14" s="3">
         <v>35.563133174512203</v>
       </c>
-      <c r="H14">
+      <c r="H14" s="3">
         <v>129.328832230009</v>
       </c>
     </row>
     <row r="15" spans="1:8">
-      <c r="A15">
+      <c r="A15" s="3">
         <v>14</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B15" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="C15" t="s">
+      <c r="C15" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="D15" t="s">
+      <c r="D15" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="E15" t="s">
+      <c r="E15" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F15" s="6" t="s">
+      <c r="F15" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="G15">
+      <c r="G15" s="3">
         <v>35.564948907444297</v>
       </c>
-      <c r="H15">
+      <c r="H15" s="3">
         <v>129.32766567982</v>
       </c>
     </row>
     <row r="16" spans="1:8">
-      <c r="A16">
+      <c r="A16" s="3">
         <v>15</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B16" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="C16" t="s">
+      <c r="C16" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="D16" t="s">
+      <c r="D16" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="E16" t="s">
+      <c r="E16" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F16" s="6" t="s">
+      <c r="F16" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="G16">
+      <c r="G16" s="3">
         <v>35.566499953091601</v>
       </c>
-      <c r="H16">
+      <c r="H16" s="3">
         <v>129.32605295352801</v>
       </c>
     </row>
     <row r="17" spans="1:8">
-      <c r="A17">
+      <c r="A17" s="3">
         <v>16</v>
       </c>
-      <c r="B17" t="s">
+      <c r="B17" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="C17" t="s">
+      <c r="C17" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="D17" t="s">
+      <c r="D17" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="E17" t="s">
+      <c r="E17" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F17" s="6" t="s">
+      <c r="F17" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="G17">
+      <c r="G17" s="3">
         <v>35.564673848122197</v>
       </c>
-      <c r="H17">
+      <c r="H17" s="3">
         <v>129.32736074607899</v>
       </c>
     </row>
     <row r="18" spans="1:8">
-      <c r="A18">
+      <c r="A18" s="3">
         <v>17</v>
       </c>
-      <c r="B18" t="s">
+      <c r="B18" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="C18" t="s">
+      <c r="C18" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="D18" t="s">
+      <c r="D18" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="E18" t="s">
+      <c r="E18" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F18" s="6" t="s">
+      <c r="F18" s="4" t="s">
         <v>187</v>
       </c>
-      <c r="G18">
+      <c r="G18" s="3">
         <v>35.557967985714299</v>
       </c>
-      <c r="H18">
+      <c r="H18" s="3">
         <v>129.327571456708</v>
       </c>
     </row>
     <row r="19" spans="1:8">
-      <c r="A19">
+      <c r="A19" s="3">
         <v>18</v>
       </c>
-      <c r="B19" t="s">
+      <c r="B19" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="C19" t="s">
+      <c r="C19" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="D19" t="s">
+      <c r="D19" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="E19" t="s">
+      <c r="E19" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="F19" s="6" t="s">
+      <c r="F19" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="G19">
+      <c r="G19" s="3">
         <v>35.565149045041302</v>
       </c>
-      <c r="H19">
+      <c r="H19" s="3">
         <v>129.26688519197299</v>
       </c>
     </row>
     <row r="20" spans="1:8">
-      <c r="A20">
+      <c r="A20" s="3">
         <v>19</v>
       </c>
-      <c r="B20" t="s">
+      <c r="B20" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="C20" t="s">
+      <c r="C20" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="D20" t="s">
+      <c r="D20" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="E20" t="s">
+      <c r="E20" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="F20" s="6" t="s">
+      <c r="F20" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="G20">
+      <c r="G20" s="3">
         <v>35.562542384548003</v>
       </c>
-      <c r="H20">
+      <c r="H20" s="3">
         <v>129.29811305216501</v>
       </c>
     </row>
     <row r="21" spans="1:8">
-      <c r="A21">
+      <c r="A21" s="3">
         <v>20</v>
       </c>
-      <c r="B21" t="s">
+      <c r="B21" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="C21" t="s">
+      <c r="C21" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="D21" t="s">
+      <c r="D21" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="E21" t="s">
+      <c r="E21" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="F21" s="6" t="s">
+      <c r="F21" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="G21">
+      <c r="G21" s="3">
         <v>35.562542384548003</v>
       </c>
-      <c r="H21">
+      <c r="H21" s="3">
         <v>129.29811305216501</v>
       </c>
     </row>
     <row r="22" spans="1:8">
-      <c r="A22">
+      <c r="A22" s="3">
         <v>21</v>
       </c>
-      <c r="B22" t="s">
+      <c r="B22" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="C22" t="s">
+      <c r="C22" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="D22" t="s">
+      <c r="D22" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="E22" t="s">
+      <c r="E22" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="F22" s="6" t="s">
+      <c r="F22" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="G22">
+      <c r="G22" s="3">
         <v>35.561698862410097</v>
       </c>
-      <c r="H22">
+      <c r="H22" s="3">
         <v>129.300962239363</v>
       </c>
     </row>
     <row r="23" spans="1:8">
-      <c r="A23">
+      <c r="A23" s="3">
         <v>22</v>
       </c>
-      <c r="B23" t="s">
+      <c r="B23" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="C23" t="s">
+      <c r="C23" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="D23" t="s">
+      <c r="D23" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="E23" t="s">
+      <c r="E23" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="F23" s="6" t="s">
+      <c r="F23" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="G23">
+      <c r="G23" s="3">
         <v>35.562256372045802</v>
       </c>
-      <c r="H23">
+      <c r="H23" s="3">
         <v>129.30058825465301</v>
       </c>
     </row>
     <row r="24" spans="1:8">
-      <c r="A24">
+      <c r="A24" s="3">
         <v>23</v>
       </c>
-      <c r="B24" t="s">
+      <c r="B24" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="C24" t="s">
+      <c r="C24" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="D24" t="s">
+      <c r="D24" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="E24" t="s">
+      <c r="E24" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="F24" s="6" t="s">
+      <c r="F24" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="G24">
+      <c r="G24" s="3">
         <v>35.562256372045802</v>
       </c>
-      <c r="H24">
+      <c r="H24" s="3">
         <v>129.30058825465301</v>
       </c>
     </row>
     <row r="25" spans="1:8">
-      <c r="A25">
+      <c r="A25" s="3">
         <v>24</v>
       </c>
-      <c r="B25" t="s">
+      <c r="B25" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="C25" t="s">
+      <c r="C25" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="D25" t="s">
+      <c r="D25" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="E25" t="s">
+      <c r="E25" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F25" s="6" t="s">
+      <c r="F25" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="G25">
+      <c r="G25" s="3">
         <v>35.554163272103402</v>
       </c>
-      <c r="H25">
+      <c r="H25" s="3">
         <v>129.32200364813099</v>
       </c>
     </row>
     <row r="26" spans="1:8">
-      <c r="A26">
+      <c r="A26" s="3">
         <v>25</v>
       </c>
-      <c r="B26" t="s">
+      <c r="B26" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="C26" t="s">
+      <c r="C26" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="D26" t="s">
+      <c r="D26" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="E26" t="s">
+      <c r="E26" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F26" s="6" t="s">
+      <c r="F26" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="G26">
+      <c r="G26" s="3">
         <v>35.571759323509703</v>
       </c>
-      <c r="H26">
+      <c r="H26" s="3">
         <v>129.32531570361701</v>
       </c>
     </row>
     <row r="27" spans="1:8">
-      <c r="A27">
+      <c r="A27" s="3">
         <v>26</v>
       </c>
-      <c r="B27" t="s">
+      <c r="B27" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="C27" t="s">
+      <c r="C27" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="D27" t="s">
+      <c r="D27" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="E27" t="s">
+      <c r="E27" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F27" s="6" t="s">
+      <c r="F27" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="G27">
+      <c r="G27" s="3">
         <v>35.553725834135101</v>
       </c>
-      <c r="H27">
+      <c r="H27" s="3">
         <v>129.31827211577701</v>
       </c>
     </row>
     <row r="28" spans="1:8">
-      <c r="A28">
+      <c r="A28" s="3">
         <v>27</v>
       </c>
-      <c r="B28" t="s">
+      <c r="B28" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="C28" t="s">
+      <c r="C28" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="D28" t="s">
+      <c r="D28" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="E28" t="s">
+      <c r="E28" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="F28" s="6" t="s">
+      <c r="F28" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="G28">
+      <c r="G28" s="3">
         <v>35.558515772422702</v>
       </c>
-      <c r="H28">
+      <c r="H28" s="3">
         <v>129.3211136704</v>
       </c>
     </row>
     <row r="29" spans="1:8">
-      <c r="A29">
+      <c r="A29" s="3">
         <v>28</v>
       </c>
-      <c r="B29" t="s">
+      <c r="B29" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="C29" t="s">
+      <c r="C29" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="D29" t="s">
+      <c r="D29" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="E29" t="s">
+      <c r="E29" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="F29" s="6" t="s">
+      <c r="F29" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="G29">
+      <c r="G29" s="3">
         <v>35.578164038624699</v>
       </c>
-      <c r="H29">
+      <c r="H29" s="3">
         <v>129.28046149747701</v>
       </c>
     </row>
     <row r="30" spans="1:8">
-      <c r="A30">
+      <c r="A30" s="3">
         <v>29</v>
       </c>
-      <c r="B30" t="s">
+      <c r="B30" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="C30" t="s">
+      <c r="C30" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="D30" t="s">
+      <c r="D30" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="E30" t="s">
+      <c r="E30" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F30" s="6" t="s">
+      <c r="F30" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="G30">
+      <c r="G30" s="3">
         <v>35.557702701320402</v>
       </c>
-      <c r="H30">
+      <c r="H30" s="3">
         <v>129.34220700976999</v>
       </c>
     </row>
     <row r="31" spans="1:8">
-      <c r="A31">
+      <c r="A31" s="3">
         <v>30</v>
       </c>
-      <c r="B31" t="s">
+      <c r="B31" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="C31" t="s">
+      <c r="C31" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="D31" t="s">
+      <c r="D31" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="E31" t="s">
+      <c r="E31" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F31" s="6" t="s">
+      <c r="F31" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="G31">
+      <c r="G31" s="3">
         <v>35.575763456244403</v>
       </c>
-      <c r="H31">
+      <c r="H31" s="3">
         <v>129.308375901956</v>
       </c>
     </row>
     <row r="32" spans="1:8">
-      <c r="A32">
+      <c r="A32" s="3">
         <v>31</v>
       </c>
-      <c r="B32" t="s">
+      <c r="B32" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="C32" t="s">
+      <c r="C32" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="D32" t="s">
+      <c r="D32" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="E32" t="s">
+      <c r="E32" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="F32" s="6" t="s">
+      <c r="F32" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="G32">
+      <c r="G32" s="3">
         <v>35.5566680715689</v>
       </c>
-      <c r="H32">
+      <c r="H32" s="3">
         <v>129.279177893774</v>
       </c>
     </row>
     <row r="33" spans="1:8">
-      <c r="A33">
+      <c r="A33" s="3">
         <v>32</v>
       </c>
-      <c r="B33" t="s">
+      <c r="B33" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="C33" t="s">
+      <c r="C33" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="D33" t="s">
+      <c r="D33" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="E33" t="s">
+      <c r="E33" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F33" s="6" t="s">
+      <c r="F33" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="G33">
+      <c r="G33" s="3">
         <v>35.573423169238197</v>
       </c>
-      <c r="H33">
+      <c r="H33" s="3">
         <v>129.31901602761101</v>
       </c>
     </row>
     <row r="34" spans="1:8">
-      <c r="A34">
+      <c r="A34" s="3">
         <v>33</v>
       </c>
-      <c r="B34" t="s">
+      <c r="B34" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="C34" t="s">
+      <c r="C34" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="D34" t="s">
+      <c r="D34" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="E34" t="s">
+      <c r="E34" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="F34" s="6" t="s">
+      <c r="F34" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="G34">
+      <c r="G34" s="3">
         <v>35.5775826180368</v>
       </c>
-      <c r="H34">
+      <c r="H34" s="3">
         <v>129.346181351555</v>
       </c>
     </row>
     <row r="35" spans="1:8">
-      <c r="A35">
+      <c r="A35" s="3">
         <v>34</v>
       </c>
-      <c r="B35" t="s">
+      <c r="B35" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="C35" t="s">
+      <c r="C35" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="D35" t="s">
+      <c r="D35" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="E35" t="s">
+      <c r="E35" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F35" s="6" t="s">
+      <c r="F35" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="G35">
+      <c r="G35" s="3">
         <v>35.576716410896601</v>
       </c>
-      <c r="H35">
+      <c r="H35" s="3">
         <v>129.32388107690801</v>
       </c>
     </row>
     <row r="36" spans="1:8">
-      <c r="A36">
+      <c r="A36" s="3">
         <v>35</v>
       </c>
-      <c r="B36" t="s">
+      <c r="B36" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="C36" t="s">
+      <c r="C36" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="D36" t="s">
+      <c r="D36" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="E36" t="s">
+      <c r="E36" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F36" s="6" t="s">
+      <c r="F36" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="G36">
+      <c r="G36" s="3">
         <v>35.5582326437437</v>
       </c>
-      <c r="H36">
+      <c r="H36" s="3">
         <v>129.33754632059299</v>
       </c>
     </row>
     <row r="37" spans="1:8">
-      <c r="A37">
+      <c r="A37" s="3">
         <v>36</v>
       </c>
-      <c r="B37" t="s">
+      <c r="B37" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="C37" t="s">
+      <c r="C37" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="D37" t="s">
+      <c r="D37" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="E37" t="s">
+      <c r="E37" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F37" s="6" t="s">
+      <c r="F37" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="G37">
+      <c r="G37" s="3">
         <v>35.5582326437437</v>
       </c>
-      <c r="H37">
+      <c r="H37" s="3">
         <v>129.33754632059299</v>
       </c>
     </row>
     <row r="38" spans="1:8">
-      <c r="A38">
+      <c r="A38" s="3">
         <v>37</v>
       </c>
-      <c r="B38" t="s">
+      <c r="B38" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="C38" t="s">
+      <c r="C38" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="D38" t="s">
+      <c r="D38" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="E38" t="s">
+      <c r="E38" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F38" s="6" t="s">
+      <c r="F38" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="G38">
+      <c r="G38" s="3">
         <v>35.5666608429161</v>
       </c>
-      <c r="H38">
+      <c r="H38" s="3">
         <v>129.32938991855301</v>
       </c>
     </row>
     <row r="39" spans="1:8">
-      <c r="A39">
+      <c r="A39" s="3">
         <v>38</v>
       </c>
-      <c r="B39" t="s">
+      <c r="B39" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="C39" t="s">
+      <c r="C39" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="D39" t="s">
+      <c r="D39" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="E39" t="s">
+      <c r="E39" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="F39" s="6" t="s">
+      <c r="F39" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="G39">
+      <c r="G39" s="3">
         <v>35.554869652407199</v>
       </c>
-      <c r="H39">
+      <c r="H39" s="3">
         <v>129.30858345615701</v>
       </c>
     </row>
     <row r="40" spans="1:8">
-      <c r="A40">
+      <c r="A40" s="3">
         <v>39</v>
       </c>
-      <c r="B40" t="s">
+      <c r="B40" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="C40" t="s">
+      <c r="C40" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="D40" t="s">
+      <c r="D40" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="E40" t="s">
+      <c r="E40" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F40" s="6" t="s">
+      <c r="F40" s="4" t="s">
         <v>188</v>
       </c>
-      <c r="G40">
+      <c r="G40" s="3">
         <v>35.5720641715236</v>
       </c>
-      <c r="H40">
+      <c r="H40" s="3">
         <v>129.32189922619699</v>
       </c>
     </row>
     <row r="41" spans="1:8">
-      <c r="A41">
+      <c r="A41" s="3">
         <v>40</v>
       </c>
-      <c r="B41" t="s">
+      <c r="B41" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="C41" t="s">
+      <c r="C41" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="D41" t="s">
+      <c r="D41" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="E41" t="s">
+      <c r="E41" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F41" s="6" t="s">
+      <c r="F41" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="G41">
+      <c r="G41" s="3">
         <v>35.5720641715236</v>
       </c>
-      <c r="H41">
+      <c r="H41" s="3">
         <v>129.32189922619699</v>
       </c>
     </row>
     <row r="42" spans="1:8">
-      <c r="A42">
+      <c r="A42" s="3">
         <v>41</v>
       </c>
-      <c r="B42" t="s">
+      <c r="B42" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="C42" t="s">
+      <c r="C42" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="D42" t="s">
+      <c r="D42" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="E42" t="s">
+      <c r="E42" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F42" s="6" t="s">
+      <c r="F42" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="G42">
+      <c r="G42" s="3">
         <v>35.556520932882101</v>
       </c>
-      <c r="H42">
+      <c r="H42" s="3">
         <v>129.31846356317999</v>
       </c>
     </row>
     <row r="43" spans="1:8">
-      <c r="A43">
+      <c r="A43" s="3">
         <v>42</v>
       </c>
-      <c r="B43" t="s">
+      <c r="B43" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="C43" t="s">
+      <c r="C43" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="D43" t="s">
+      <c r="D43" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="E43" t="s">
+      <c r="E43" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F43" s="6" t="s">
+      <c r="F43" s="4" t="s">
         <v>11</v>
       </c>
+      <c r="G43" s="3"/>
+      <c r="H43" s="3"/>
     </row>
     <row r="44" spans="1:8">
-      <c r="A44">
+      <c r="A44" s="3">
         <v>43</v>
       </c>
-      <c r="B44" t="s">
+      <c r="B44" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="C44" t="s">
+      <c r="C44" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="D44" t="s">
+      <c r="D44" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="E44" t="s">
+      <c r="E44" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F44" s="6" t="s">
+      <c r="F44" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="G44">
+      <c r="G44" s="3">
         <v>35.5740791279623</v>
       </c>
-      <c r="H44">
+      <c r="H44" s="3">
         <v>129.31021759453901</v>
       </c>
     </row>
     <row r="45" spans="1:8">
-      <c r="A45">
+      <c r="A45" s="3">
         <v>44</v>
       </c>
-      <c r="B45" t="s">
+      <c r="B45" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="C45" t="s">
+      <c r="C45" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="D45" t="s">
+      <c r="D45" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="E45" t="s">
+      <c r="E45" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="F45" s="6" t="s">
+      <c r="F45" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="G45">
+      <c r="G45" s="3">
         <v>35.554869652407199</v>
       </c>
-      <c r="H45">
+      <c r="H45" s="3">
         <v>129.30858345615701</v>
       </c>
     </row>
     <row r="46" spans="1:8">
-      <c r="A46">
+      <c r="A46" s="3">
         <v>45</v>
       </c>
-      <c r="B46" t="s">
+      <c r="B46" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="C46" t="s">
+      <c r="C46" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="D46" t="s">
+      <c r="D46" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="E46" t="s">
+      <c r="E46" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F46" s="6" t="s">
+      <c r="F46" s="4" t="s">
         <v>187</v>
       </c>
-      <c r="G46">
+      <c r="G46" s="3">
         <v>35.557219330149202</v>
       </c>
-      <c r="H46">
+      <c r="H46" s="3">
         <v>129.334901038727</v>
       </c>
     </row>
     <row r="47" spans="1:8">
-      <c r="A47">
+      <c r="A47" s="3">
         <v>46</v>
       </c>
-      <c r="B47" t="s">
+      <c r="B47" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="C47" t="s">
+      <c r="C47" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="D47" t="s">
+      <c r="D47" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="E47" t="s">
+      <c r="E47" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F47" s="6" t="s">
+      <c r="F47" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="G47">
+      <c r="G47" s="3">
         <v>35.581462324241897</v>
       </c>
-      <c r="H47">
+      <c r="H47" s="3">
         <v>129.32268218764199</v>
       </c>
     </row>
     <row r="48" spans="1:8">
-      <c r="A48">
+      <c r="A48" s="3">
         <v>47</v>
       </c>
-      <c r="B48" t="s">
+      <c r="B48" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="C48" t="s">
+      <c r="C48" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="D48" t="s">
+      <c r="D48" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="E48" t="s">
+      <c r="E48" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="F48" s="6" t="s">
+      <c r="F48" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="G48">
+      <c r="G48" s="3">
         <v>35.555482477365103</v>
       </c>
-      <c r="H48">
+      <c r="H48" s="3">
         <v>129.32704582909801</v>
       </c>
     </row>
     <row r="49" spans="1:8">
-      <c r="A49">
+      <c r="A49" s="3">
         <v>48</v>
       </c>
-      <c r="B49" t="s">
+      <c r="B49" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="C49" t="s">
+      <c r="C49" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="D49" t="s">
+      <c r="D49" s="3" t="s">
         <v>138</v>
       </c>
-      <c r="E49" t="s">
+      <c r="E49" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F49" s="6" t="s">
+      <c r="F49" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="G49">
+      <c r="G49" s="3">
         <v>35.562287031924903</v>
       </c>
-      <c r="H49">
+      <c r="H49" s="3">
         <v>129.32991157348201</v>
       </c>
     </row>
     <row r="50" spans="1:8">
-      <c r="A50">
+      <c r="A50" s="3">
         <v>49</v>
       </c>
-      <c r="B50" t="s">
+      <c r="B50" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="C50" t="s">
+      <c r="C50" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="D50" t="s">
+      <c r="D50" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="E50" t="s">
+      <c r="E50" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="F50" s="6" t="s">
+      <c r="F50" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="G50">
+      <c r="G50" s="3">
         <v>35.553408829687001</v>
       </c>
-      <c r="H50">
+      <c r="H50" s="3">
         <v>129.30194271522601</v>
       </c>
     </row>
     <row r="51" spans="1:8">
-      <c r="A51">
+      <c r="A51" s="3">
         <v>50</v>
       </c>
-      <c r="B51" t="s">
+      <c r="B51" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="C51" t="s">
+      <c r="C51" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="D51" t="s">
+      <c r="D51" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="E51" t="s">
+      <c r="E51" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F51" s="6" t="s">
+      <c r="F51" s="4" t="s">
         <v>187</v>
       </c>
-      <c r="G51">
+      <c r="G51" s="3">
         <v>35.562228786253897</v>
       </c>
-      <c r="H51">
+      <c r="H51" s="3">
         <v>129.31749376133601</v>
       </c>
     </row>
     <row r="52" spans="1:8">
-      <c r="A52">
+      <c r="A52" s="3">
         <v>51</v>
       </c>
-      <c r="B52" t="s">
+      <c r="B52" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="C52" t="s">
+      <c r="C52" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="D52" t="s">
+      <c r="D52" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="E52" t="s">
+      <c r="E52" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F52" s="6" t="s">
+      <c r="F52" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="G52">
+      <c r="G52" s="3">
         <v>35.562228786253897</v>
       </c>
-      <c r="H52">
+      <c r="H52" s="3">
         <v>129.31749376133601</v>
       </c>
     </row>
     <row r="53" spans="1:8">
-      <c r="A53">
+      <c r="A53" s="3">
         <v>52</v>
       </c>
-      <c r="B53" t="s">
+      <c r="B53" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="C53" t="s">
+      <c r="C53" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="D53" t="s">
+      <c r="D53" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="E53" t="s">
+      <c r="E53" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F53" s="6" t="s">
+      <c r="F53" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="G53">
+      <c r="G53" s="3">
         <v>35.555836455695498</v>
       </c>
-      <c r="H53">
+      <c r="H53" s="3">
         <v>129.337495790666</v>
       </c>
     </row>
     <row r="54" spans="1:8">
-      <c r="A54">
+      <c r="A54" s="3">
         <v>53</v>
       </c>
-      <c r="B54" t="s">
+      <c r="B54" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="C54" t="s">
+      <c r="C54" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="D54" t="s">
+      <c r="D54" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="E54" t="s">
+      <c r="E54" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F54" s="6" t="s">
+      <c r="F54" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="G54">
+      <c r="G54" s="3">
         <v>35.5666608429161</v>
       </c>
-      <c r="H54">
+      <c r="H54" s="3">
         <v>129.32938991855301</v>
       </c>
     </row>
     <row r="55" spans="1:8">
-      <c r="A55">
+      <c r="A55" s="3">
         <v>54</v>
       </c>
-      <c r="B55" t="s">
+      <c r="B55" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="C55" t="s">
+      <c r="C55" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="D55" t="s">
+      <c r="D55" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="E55" t="s">
+      <c r="E55" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F55" s="6" t="s">
+      <c r="F55" s="4" t="s">
         <v>188</v>
       </c>
-      <c r="G55">
+      <c r="G55" s="3">
         <v>35.558800966055898</v>
       </c>
-      <c r="H55">
+      <c r="H55" s="3">
         <v>129.33276957269501</v>
       </c>
     </row>
     <row r="56" spans="1:8">
-      <c r="A56">
+      <c r="A56" s="3">
         <v>55</v>
       </c>
-      <c r="B56" t="s">
+      <c r="B56" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="C56" t="s">
+      <c r="C56" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="D56" t="s">
+      <c r="D56" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="E56" t="s">
+      <c r="E56" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="F56" s="6" t="s">
+      <c r="F56" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="G56">
+      <c r="G56" s="3">
         <v>35.555639784408001</v>
       </c>
-      <c r="H56">
+      <c r="H56" s="3">
         <v>129.34719219842799</v>
       </c>
     </row>
     <row r="57" spans="1:8">
-      <c r="A57">
+      <c r="A57" s="3">
         <v>56</v>
       </c>
-      <c r="B57" t="s">
+      <c r="B57" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="C57" t="s">
+      <c r="C57" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="D57" t="s">
+      <c r="D57" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="E57" t="s">
+      <c r="E57" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="F57" s="6" t="s">
+      <c r="F57" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="G57">
+      <c r="G57" s="3">
         <v>35.5700202952994</v>
       </c>
-      <c r="H57">
+      <c r="H57" s="3">
         <v>129.337436690766</v>
       </c>
     </row>
     <row r="58" spans="1:8">
-      <c r="A58">
+      <c r="A58" s="3">
         <v>57</v>
       </c>
-      <c r="B58" t="s">
+      <c r="B58" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="C58" t="s">
+      <c r="C58" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="D58" t="s">
+      <c r="D58" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="E58" t="s">
+      <c r="E58" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="F58" s="6" t="s">
+      <c r="F58" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="G58">
+      <c r="G58" s="3">
         <v>35.556341521778499</v>
       </c>
-      <c r="H58">
+      <c r="H58" s="3">
         <v>129.30959998798701</v>
       </c>
     </row>
     <row r="59" spans="1:8">
-      <c r="A59">
+      <c r="A59" s="3">
         <v>58</v>
       </c>
-      <c r="B59" t="s">
+      <c r="B59" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="C59" t="s">
+      <c r="C59" s="3" t="s">
         <v>161</v>
       </c>
-      <c r="D59" t="s">
+      <c r="D59" s="3" t="s">
         <v>201</v>
       </c>
-      <c r="E59" t="s">
+      <c r="E59" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="F59" s="6" t="s">
+      <c r="F59" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="G59">
+      <c r="G59" s="3">
         <v>35.557052889907403</v>
       </c>
-      <c r="H59">
+      <c r="H59" s="3">
         <v>129.34773887451399</v>
       </c>
     </row>
     <row r="60" spans="1:8">
-      <c r="A60">
+      <c r="A60" s="3">
         <v>59</v>
       </c>
-      <c r="B60" t="s">
+      <c r="B60" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="C60" t="s">
+      <c r="C60" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="D60" t="s">
+      <c r="D60" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="E60" t="s">
+      <c r="E60" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F60" s="6" t="s">
+      <c r="F60" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="G60">
+      <c r="G60" s="3">
         <v>35.556366031864698</v>
       </c>
-      <c r="H60">
+      <c r="H60" s="3">
         <v>129.32796607151101</v>
       </c>
     </row>
     <row r="61" spans="1:8">
-      <c r="A61">
+      <c r="A61" s="3">
         <v>60</v>
       </c>
-      <c r="B61" t="s">
+      <c r="B61" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="C61" t="s">
+      <c r="C61" s="3" t="s">
         <v>165</v>
       </c>
-      <c r="D61" t="s">
+      <c r="D61" s="3" t="s">
         <v>166</v>
       </c>
-      <c r="E61" t="s">
+      <c r="E61" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F61" s="6" t="s">
+      <c r="F61" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="G61">
+      <c r="G61" s="3">
         <v>35.558083481622702</v>
       </c>
-      <c r="H61">
+      <c r="H61" s="3">
         <v>129.32761912511799</v>
       </c>
     </row>
     <row r="62" spans="1:8">
-      <c r="A62">
+      <c r="A62" s="3">
         <v>61</v>
       </c>
-      <c r="B62" t="s">
+      <c r="B62" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="C62" t="s">
+      <c r="C62" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="D62" t="s">
+      <c r="D62" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="E62" t="s">
+      <c r="E62" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F62" s="6" t="s">
+      <c r="F62" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="G62">
+      <c r="G62" s="3">
         <v>35.555203248603398</v>
       </c>
-      <c r="H62">
+      <c r="H62" s="3">
         <v>129.33454593378599</v>
       </c>
     </row>
     <row r="63" spans="1:8">
-      <c r="A63">
+      <c r="A63" s="3">
         <v>62</v>
       </c>
-      <c r="B63" t="s">
+      <c r="B63" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="C63" t="s">
+      <c r="C63" s="3" t="s">
         <v>169</v>
       </c>
-      <c r="D63" t="s">
+      <c r="D63" s="3" t="s">
         <v>170</v>
       </c>
-      <c r="E63" t="s">
+      <c r="E63" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F63" s="6" t="s">
+      <c r="F63" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="G63">
+      <c r="G63" s="3">
         <v>35.557554542102103</v>
       </c>
-      <c r="H63">
+      <c r="H63" s="3">
         <v>129.33141894784401</v>
       </c>
     </row>
     <row r="64" spans="1:8">
-      <c r="A64">
+      <c r="A64" s="3">
         <v>63</v>
       </c>
-      <c r="B64" t="s">
+      <c r="B64" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="C64" t="s">
+      <c r="C64" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="D64" t="s">
+      <c r="D64" s="3" t="s">
         <v>173</v>
       </c>
-      <c r="E64" t="s">
+      <c r="E64" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="F64" s="6" t="s">
+      <c r="F64" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="G64">
+      <c r="G64" s="3">
         <v>35.576364760900098</v>
       </c>
-      <c r="H64">
+      <c r="H64" s="3">
         <v>129.33133707067299</v>
       </c>
     </row>
     <row r="65" spans="1:8">
-      <c r="A65">
+      <c r="A65" s="3">
         <v>64</v>
       </c>
-      <c r="B65" t="s">
+      <c r="B65" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="C65" t="s">
+      <c r="C65" s="3" t="s">
         <v>174</v>
       </c>
-      <c r="D65" t="s">
+      <c r="D65" s="3" t="s">
         <v>175</v>
       </c>
-      <c r="E65" t="s">
+      <c r="E65" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="F65" s="6" t="s">
+      <c r="F65" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="G65">
+      <c r="G65" s="3">
         <v>35.558510277147398</v>
       </c>
-      <c r="H65">
+      <c r="H65" s="3">
         <v>129.34715485530299</v>
       </c>
     </row>
     <row r="66" spans="1:8">
-      <c r="A66">
+      <c r="A66" s="3">
         <v>65</v>
       </c>
-      <c r="B66" t="s">
+      <c r="B66" s="3" t="s">
         <v>176</v>
       </c>
-      <c r="C66" t="s">
+      <c r="C66" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="D66" t="s">
+      <c r="D66" s="3" t="s">
         <v>178</v>
       </c>
-      <c r="E66" t="s">
+      <c r="E66" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F66" s="6" t="s">
+      <c r="F66" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="G66">
+      <c r="G66" s="3">
         <v>35.554274741918398</v>
       </c>
-      <c r="H66">
+      <c r="H66" s="3">
         <v>129.33926986466699</v>
       </c>
     </row>
     <row r="67" spans="1:8">
-      <c r="A67">
+      <c r="A67" s="3">
         <v>66</v>
       </c>
-      <c r="B67" t="s">
+      <c r="B67" s="3" t="s">
         <v>176</v>
       </c>
-      <c r="C67" t="s">
+      <c r="C67" s="3" t="s">
         <v>165</v>
       </c>
-      <c r="D67" t="s">
+      <c r="D67" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="E67" t="s">
+      <c r="E67" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F67" s="6" t="s">
+      <c r="F67" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="G67">
+      <c r="G67" s="3">
         <v>35.558083481622702</v>
       </c>
-      <c r="H67">
+      <c r="H67" s="3">
         <v>129.32761912511799</v>
       </c>
     </row>
     <row r="68" spans="1:8">
-      <c r="A68">
+      <c r="A68" s="3">
         <v>67</v>
       </c>
-      <c r="B68" t="s">
+      <c r="B68" s="3" t="s">
         <v>176</v>
       </c>
-      <c r="C68" t="s">
+      <c r="C68" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="D68" t="s">
+      <c r="D68" s="3" t="s">
         <v>181</v>
       </c>
-      <c r="E68" t="s">
+      <c r="E68" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F68" s="6" t="s">
+      <c r="F68" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="G68">
+      <c r="G68" s="3">
         <v>35.575956108387999</v>
       </c>
-      <c r="H68">
+      <c r="H68" s="3">
         <v>129.309630937603</v>
       </c>
     </row>
     <row r="69" spans="1:8">
-      <c r="A69">
+      <c r="A69" s="3">
         <v>68</v>
       </c>
-      <c r="B69" t="s">
+      <c r="B69" s="3" t="s">
         <v>182</v>
       </c>
-      <c r="C69" t="s">
+      <c r="C69" s="3" t="s">
         <v>183</v>
       </c>
-      <c r="D69" t="s">
+      <c r="D69" s="3" t="s">
         <v>184</v>
       </c>
-      <c r="E69" t="s">
+      <c r="E69" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="F69" s="6" t="s">
+      <c r="F69" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="G69">
+      <c r="G69" s="3">
         <v>35.579577253452101</v>
       </c>
-      <c r="H69">
+      <c r="H69" s="3">
         <v>129.31561270768299</v>
       </c>
     </row>
     <row r="70" spans="1:8">
-      <c r="A70">
+      <c r="A70" s="3">
         <v>69</v>
       </c>
-      <c r="B70" s="1">
+      <c r="B70" s="5">
         <v>46146</v>
       </c>
-      <c r="C70" t="s">
+      <c r="C70" s="3" t="s">
         <v>225</v>
       </c>
-      <c r="D70" s="4" t="s">
+      <c r="D70" s="6" t="s">
         <v>210</v>
       </c>
-      <c r="E70" s="3" t="s">
+      <c r="E70" s="7" t="s">
         <v>194</v>
       </c>
-      <c r="F70" s="4" t="s">
+      <c r="F70" s="6" t="s">
         <v>196</v>
       </c>
+      <c r="G70" s="3"/>
+      <c r="H70" s="3"/>
     </row>
     <row r="71" spans="1:8">
-      <c r="A71">
+      <c r="A71" s="3">
         <v>70</v>
       </c>
-      <c r="B71" s="1">
+      <c r="B71" s="5">
         <v>46149</v>
       </c>
-      <c r="C71" t="s">
+      <c r="C71" s="3" t="s">
         <v>224</v>
       </c>
-      <c r="D71" s="2" t="s">
+      <c r="D71" s="8" t="s">
         <v>211</v>
       </c>
-      <c r="E71" s="3" t="s">
+      <c r="E71" s="7" t="s">
         <v>206</v>
       </c>
-      <c r="F71" s="4" t="s">
+      <c r="F71" s="6" t="s">
         <v>196</v>
       </c>
+      <c r="G71" s="3"/>
+      <c r="H71" s="3"/>
     </row>
     <row r="72" spans="1:8">
-      <c r="A72">
+      <c r="A72" s="3">
         <v>71</v>
       </c>
-      <c r="B72" s="1">
+      <c r="B72" s="5">
         <v>46153</v>
       </c>
-      <c r="C72" t="s">
+      <c r="C72" s="3" t="s">
         <v>226</v>
       </c>
-      <c r="D72" s="4" t="s">
+      <c r="D72" s="6" t="s">
         <v>213</v>
       </c>
-      <c r="E72" s="3" t="s">
+      <c r="E72" s="7" t="s">
         <v>194</v>
       </c>
-      <c r="F72" s="4" t="s">
+      <c r="F72" s="6" t="s">
         <v>196</v>
       </c>
+      <c r="G72" s="3"/>
+      <c r="H72" s="3"/>
     </row>
     <row r="73" spans="1:8">
-      <c r="A73">
+      <c r="A73" s="3">
         <v>72</v>
       </c>
-      <c r="B73" s="1">
+      <c r="B73" s="5">
         <v>46153</v>
       </c>
-      <c r="C73" t="s">
+      <c r="C73" s="3" t="s">
         <v>228</v>
       </c>
-      <c r="D73" s="5" t="s">
+      <c r="D73" s="9" t="s">
         <v>227</v>
       </c>
-      <c r="E73" s="3" t="s">
+      <c r="E73" s="7" t="s">
         <v>194</v>
       </c>
-      <c r="F73" s="4" t="s">
+      <c r="F73" s="6" t="s">
         <v>196</v>
       </c>
+      <c r="G73" s="3"/>
+      <c r="H73" s="3"/>
     </row>
     <row r="74" spans="1:8">
-      <c r="A74">
+      <c r="A74" s="3">
         <v>73</v>
       </c>
-      <c r="B74" s="1">
+      <c r="B74" s="5">
         <v>46153</v>
       </c>
-      <c r="C74" t="s">
+      <c r="C74" s="3" t="s">
         <v>229</v>
       </c>
-      <c r="D74" s="5" t="s">
+      <c r="D74" s="9" t="s">
         <v>222</v>
       </c>
-      <c r="E74" s="3" t="s">
+      <c r="E74" s="7" t="s">
         <v>204</v>
       </c>
-      <c r="F74" s="4" t="s">
+      <c r="F74" s="6" t="s">
         <v>187</v>
       </c>
+      <c r="G74" s="3"/>
+      <c r="H74" s="3"/>
     </row>
     <row r="75" spans="1:8">
-      <c r="A75">
+      <c r="A75" s="3">
         <v>74</v>
       </c>
-      <c r="B75" s="1">
+      <c r="B75" s="5">
         <v>46153</v>
       </c>
-      <c r="C75" t="s">
+      <c r="C75" s="3" t="s">
         <v>230</v>
       </c>
-      <c r="D75" s="5" t="s">
+      <c r="D75" s="9" t="s">
         <v>214</v>
       </c>
-      <c r="E75" s="3" t="s">
+      <c r="E75" s="7" t="s">
         <v>208</v>
       </c>
-      <c r="F75" s="4" t="s">
+      <c r="F75" s="6" t="s">
         <v>196</v>
       </c>
+      <c r="G75" s="3"/>
+      <c r="H75" s="3"/>
     </row>
     <row r="76" spans="1:8">
-      <c r="A76">
+      <c r="A76" s="3">
         <v>75</v>
       </c>
-      <c r="B76" s="1">
+      <c r="B76" s="5">
         <v>46155</v>
       </c>
-      <c r="C76" t="s">
+      <c r="C76" s="3" t="s">
         <v>231</v>
       </c>
-      <c r="D76" s="4" t="s">
+      <c r="D76" s="6" t="s">
         <v>215</v>
       </c>
-      <c r="E76" s="3" t="s">
+      <c r="E76" s="7" t="s">
         <v>194</v>
       </c>
-      <c r="F76" s="4" t="s">
+      <c r="F76" s="6" t="s">
         <v>196</v>
       </c>
+      <c r="G76" s="3"/>
+      <c r="H76" s="3"/>
     </row>
     <row r="77" spans="1:8">
-      <c r="A77">
+      <c r="A77" s="3">
         <v>76</v>
       </c>
-      <c r="B77" s="1">
+      <c r="B77" s="5">
         <v>46160</v>
       </c>
-      <c r="C77" t="s">
+      <c r="C77" s="3" t="s">
         <v>200</v>
       </c>
-      <c r="D77" s="4" t="s">
+      <c r="D77" s="6" t="s">
         <v>189</v>
       </c>
-      <c r="E77" s="3" t="s">
+      <c r="E77" s="7" t="s">
         <v>194</v>
       </c>
-      <c r="F77" s="4" t="s">
+      <c r="F77" s="6" t="s">
         <v>196</v>
       </c>
+      <c r="G77" s="3"/>
+      <c r="H77" s="3"/>
     </row>
     <row r="78" spans="1:8">
-      <c r="A78">
+      <c r="A78" s="3">
         <v>77</v>
       </c>
-      <c r="B78" s="1">
+      <c r="B78" s="5">
         <v>46160</v>
       </c>
-      <c r="C78" t="s">
+      <c r="C78" s="3" t="s">
         <v>232</v>
       </c>
-      <c r="D78" s="4" t="s">
+      <c r="D78" s="6" t="s">
         <v>190</v>
       </c>
-      <c r="E78" s="3" t="s">
+      <c r="E78" s="7" t="s">
         <v>194</v>
       </c>
-      <c r="F78" s="4" t="s">
+      <c r="F78" s="6" t="s">
         <v>196</v>
       </c>
+      <c r="G78" s="3"/>
+      <c r="H78" s="3"/>
     </row>
     <row r="79" spans="1:8">
-      <c r="A79">
+      <c r="A79" s="3">
         <v>78</v>
       </c>
-      <c r="B79" s="1">
+      <c r="B79" s="5">
         <v>46161</v>
       </c>
-      <c r="C79" t="s">
+      <c r="C79" s="3" t="s">
         <v>223</v>
       </c>
-      <c r="D79" s="4" t="s">
+      <c r="D79" s="6" t="s">
         <v>212</v>
       </c>
-      <c r="E79" s="3" t="s">
+      <c r="E79" s="7" t="s">
         <v>207</v>
       </c>
-      <c r="F79" s="4" t="s">
+      <c r="F79" s="6" t="s">
         <v>221</v>
       </c>
+      <c r="G79" s="3"/>
+      <c r="H79" s="3"/>
     </row>
     <row r="80" spans="1:8">
-      <c r="A80">
+      <c r="A80" s="3">
         <v>79</v>
       </c>
-      <c r="B80" s="1">
+      <c r="B80" s="5">
         <v>46164</v>
       </c>
-      <c r="C80" t="s">
+      <c r="C80" s="3" t="s">
         <v>202</v>
       </c>
-      <c r="D80" s="4" t="s">
+      <c r="D80" s="6" t="s">
         <v>191</v>
       </c>
-      <c r="E80" s="3" t="s">
+      <c r="E80" s="7" t="s">
         <v>195</v>
       </c>
-      <c r="F80" s="4" t="s">
+      <c r="F80" s="6" t="s">
         <v>196</v>
       </c>
-    </row>
-    <row r="81" spans="1:7">
-      <c r="A81" s="7">
+      <c r="G80" s="3"/>
+      <c r="H80" s="3"/>
+    </row>
+    <row r="81" spans="1:8">
+      <c r="A81" s="2">
         <v>80</v>
       </c>
-      <c r="B81" s="1">
+      <c r="B81" s="5">
         <v>46164</v>
       </c>
-      <c r="C81" s="7" t="s">
+      <c r="C81" s="2" t="s">
         <v>199</v>
       </c>
-      <c r="D81" s="4" t="s">
+      <c r="D81" s="6" t="s">
         <v>192</v>
       </c>
-      <c r="E81" s="3" t="s">
+      <c r="E81" s="7" t="s">
         <v>195</v>
       </c>
-      <c r="F81" s="4" t="s">
+      <c r="F81" s="6" t="s">
         <v>236</v>
       </c>
-      <c r="G81" s="7"/>
-    </row>
-    <row r="82" spans="1:7">
-      <c r="A82" s="7">
+      <c r="G81" s="2"/>
+      <c r="H81" s="3"/>
+    </row>
+    <row r="82" spans="1:8">
+      <c r="A82" s="2">
         <v>81</v>
       </c>
-      <c r="B82" s="1">
+      <c r="B82" s="5">
         <v>46168</v>
       </c>
-      <c r="C82" s="7" t="s">
+      <c r="C82" s="2" t="s">
         <v>198</v>
       </c>
-      <c r="D82" s="4" t="s">
+      <c r="D82" s="6" t="s">
         <v>193</v>
       </c>
-      <c r="E82" s="3" t="s">
+      <c r="E82" s="7" t="s">
         <v>194</v>
       </c>
-      <c r="F82" s="4" t="s">
+      <c r="F82" s="6" t="s">
         <v>196</v>
       </c>
-      <c r="G82" s="7"/>
-    </row>
-    <row r="83" spans="1:7">
-      <c r="A83" s="7">
+      <c r="G82" s="2"/>
+      <c r="H82" s="3"/>
+    </row>
+    <row r="83" spans="1:8">
+      <c r="A83" s="2">
         <v>82</v>
       </c>
-      <c r="B83" s="1">
+      <c r="B83" s="5">
         <v>46168</v>
       </c>
-      <c r="C83" s="7" t="s">
+      <c r="C83" s="2" t="s">
         <v>197</v>
       </c>
-      <c r="D83" s="4" t="s">
+      <c r="D83" s="6" t="s">
         <v>216</v>
       </c>
-      <c r="E83" s="3" t="s">
+      <c r="E83" s="7" t="s">
         <v>194</v>
       </c>
-      <c r="F83" s="4" t="s">
+      <c r="F83" s="6" t="s">
         <v>196</v>
       </c>
-      <c r="G83" s="7"/>
-    </row>
-    <row r="84" spans="1:7">
-      <c r="A84" s="7">
+      <c r="G83" s="2"/>
+      <c r="H83" s="3"/>
+    </row>
+    <row r="84" spans="1:8">
+      <c r="A84" s="2">
         <v>83</v>
       </c>
-      <c r="B84" s="1">
+      <c r="B84" s="5">
         <v>46169</v>
       </c>
-      <c r="C84" s="7" t="s">
+      <c r="C84" s="2" t="s">
         <v>203</v>
       </c>
-      <c r="D84" s="4" t="s">
+      <c r="D84" s="6" t="s">
         <v>217</v>
       </c>
-      <c r="E84" s="3" t="s">
+      <c r="E84" s="7" t="s">
         <v>194</v>
       </c>
-      <c r="F84" s="4" t="s">
+      <c r="F84" s="6" t="s">
         <v>196</v>
       </c>
-      <c r="G84" s="7"/>
-    </row>
-    <row r="85" spans="1:7">
-      <c r="A85" s="7">
+      <c r="G84" s="2"/>
+      <c r="H84" s="3"/>
+    </row>
+    <row r="85" spans="1:8">
+      <c r="A85" s="2">
         <v>84</v>
       </c>
-      <c r="B85" s="1">
+      <c r="B85" s="5">
         <v>46170</v>
       </c>
-      <c r="C85" s="7" t="s">
+      <c r="C85" s="2" t="s">
         <v>233</v>
       </c>
-      <c r="D85" s="4" t="s">
+      <c r="D85" s="6" t="s">
         <v>218</v>
       </c>
-      <c r="E85" s="3" t="s">
+      <c r="E85" s="7" t="s">
         <v>209</v>
       </c>
-      <c r="F85" s="4" t="s">
+      <c r="F85" s="6" t="s">
         <v>196</v>
       </c>
-      <c r="G85" s="7"/>
-    </row>
-    <row r="86" spans="1:7">
-      <c r="A86" s="7">
+      <c r="G85" s="2"/>
+      <c r="H85" s="3"/>
+    </row>
+    <row r="86" spans="1:8">
+      <c r="A86" s="2">
         <v>85</v>
       </c>
-      <c r="B86" s="1">
+      <c r="B86" s="5">
         <v>46171</v>
       </c>
-      <c r="C86" s="7" t="s">
+      <c r="C86" s="2" t="s">
         <v>234</v>
       </c>
-      <c r="D86" s="4" t="s">
+      <c r="D86" s="6" t="s">
         <v>219</v>
       </c>
-      <c r="E86" s="3" t="s">
+      <c r="E86" s="7" t="s">
         <v>194</v>
       </c>
-      <c r="F86" s="4" t="s">
+      <c r="F86" s="6" t="s">
         <v>196</v>
       </c>
-      <c r="G86" s="7"/>
-    </row>
-    <row r="87" spans="1:7">
-      <c r="A87" s="7">
+      <c r="G86" s="2"/>
+      <c r="H86" s="3"/>
+    </row>
+    <row r="87" spans="1:8">
+      <c r="A87" s="2">
         <v>86</v>
       </c>
-      <c r="B87" s="1">
+      <c r="B87" s="5">
         <v>46171</v>
       </c>
-      <c r="C87" s="7" t="s">
+      <c r="C87" s="2" t="s">
         <v>235</v>
       </c>
-      <c r="D87" s="4" t="s">
+      <c r="D87" s="6" t="s">
         <v>220</v>
       </c>
-      <c r="E87" s="3" t="s">
+      <c r="E87" s="7" t="s">
         <v>194</v>
       </c>
-      <c r="F87" s="4" t="s">
+      <c r="F87" s="6" t="s">
         <v>196</v>
       </c>
-      <c r="G87" s="7"/>
-    </row>
-    <row r="88" spans="1:7">
-      <c r="A88" s="7">
+      <c r="G87" s="2"/>
+      <c r="H87" s="3"/>
+    </row>
+    <row r="88" spans="1:8">
+      <c r="A88" s="2">
         <v>87</v>
       </c>
-      <c r="B88" s="1">
+      <c r="B88" s="5">
         <v>46181</v>
       </c>
-      <c r="C88" s="7" t="s">
+      <c r="C88" s="2" t="s">
         <v>280</v>
       </c>
-      <c r="D88" s="4" t="s">
+      <c r="D88" s="6" t="s">
         <v>240</v>
       </c>
-      <c r="E88" s="3" t="s">
+      <c r="E88" s="7" t="s">
         <v>208</v>
       </c>
-      <c r="F88" s="4" t="s">
+      <c r="F88" s="6" t="s">
         <v>196</v>
       </c>
-      <c r="G88" s="7"/>
-    </row>
-    <row r="89" spans="1:7" ht="33">
-      <c r="A89" s="7">
+      <c r="G88" s="2"/>
+      <c r="H88" s="3"/>
+    </row>
+    <row r="89" spans="1:8" ht="33">
+      <c r="A89" s="2">
         <v>88</v>
       </c>
-      <c r="B89" s="1">
+      <c r="B89" s="5">
         <v>46182</v>
       </c>
-      <c r="C89" s="7" t="s">
+      <c r="C89" s="2" t="s">
         <v>281</v>
       </c>
-      <c r="D89" s="8" t="s">
+      <c r="D89" s="10" t="s">
         <v>241</v>
       </c>
-      <c r="E89" s="3" t="s">
+      <c r="E89" s="7" t="s">
         <v>208</v>
       </c>
-      <c r="F89" s="4" t="s">
+      <c r="F89" s="6" t="s">
         <v>196</v>
       </c>
-      <c r="G89" s="7"/>
-    </row>
-    <row r="90" spans="1:7">
-      <c r="A90" s="7">
+      <c r="G89" s="2"/>
+      <c r="H89" s="3"/>
+    </row>
+    <row r="90" spans="1:8">
+      <c r="A90" s="2">
         <v>89</v>
       </c>
-      <c r="B90" s="1">
+      <c r="B90" s="5">
         <v>46184</v>
       </c>
-      <c r="C90" s="9" t="s">
+      <c r="C90" s="11" t="s">
         <v>282</v>
       </c>
-      <c r="D90" s="2" t="s">
+      <c r="D90" s="8" t="s">
         <v>242</v>
       </c>
-      <c r="E90" s="3" t="s">
+      <c r="E90" s="7" t="s">
         <v>194</v>
       </c>
-      <c r="F90" s="4" t="s">
+      <c r="F90" s="6" t="s">
         <v>196</v>
       </c>
-      <c r="G90" s="7"/>
-    </row>
-    <row r="91" spans="1:7">
-      <c r="A91" s="7">
+      <c r="G90" s="2"/>
+      <c r="H90" s="3"/>
+    </row>
+    <row r="91" spans="1:8">
+      <c r="A91" s="2">
         <v>90</v>
       </c>
-      <c r="B91" s="1">
+      <c r="B91" s="5">
         <v>46185</v>
       </c>
-      <c r="C91" s="7" t="s">
+      <c r="C91" s="2" t="s">
         <v>283</v>
       </c>
-      <c r="D91" s="2" t="s">
+      <c r="D91" s="8" t="s">
         <v>243</v>
       </c>
-      <c r="E91" s="3" t="s">
+      <c r="E91" s="7" t="s">
         <v>194</v>
       </c>
-      <c r="F91" s="4" t="s">
+      <c r="F91" s="6" t="s">
         <v>196</v>
       </c>
-      <c r="G91" s="7"/>
-    </row>
-    <row r="92" spans="1:7">
-      <c r="A92" s="7">
+      <c r="G91" s="2"/>
+      <c r="H91" s="3"/>
+    </row>
+    <row r="92" spans="1:8">
+      <c r="A92" s="2">
         <v>91</v>
       </c>
-      <c r="B92" s="1">
+      <c r="B92" s="5">
         <v>46188</v>
       </c>
-      <c r="C92" s="7" t="s">
+      <c r="C92" s="2" t="s">
         <v>284</v>
       </c>
-      <c r="D92" s="2" t="s">
+      <c r="D92" s="8" t="s">
         <v>244</v>
       </c>
-      <c r="E92" s="3" t="s">
+      <c r="E92" s="7" t="s">
         <v>194</v>
       </c>
-      <c r="F92" s="4" t="s">
+      <c r="F92" s="6" t="s">
         <v>196</v>
       </c>
-      <c r="G92" s="7"/>
-    </row>
-    <row r="93" spans="1:7">
-      <c r="A93" s="7">
+      <c r="G92" s="2"/>
+      <c r="H92" s="3"/>
+    </row>
+    <row r="93" spans="1:8">
+      <c r="A93" s="2">
         <v>92</v>
       </c>
-      <c r="B93" s="1">
+      <c r="B93" s="5">
         <v>46188</v>
       </c>
-      <c r="C93" s="9" t="s">
+      <c r="C93" s="11" t="s">
         <v>285</v>
       </c>
-      <c r="D93" s="2" t="s">
+      <c r="D93" s="8" t="s">
         <v>245</v>
       </c>
-      <c r="E93" s="3" t="s">
+      <c r="E93" s="7" t="s">
         <v>194</v>
       </c>
-      <c r="F93" s="4" t="s">
+      <c r="F93" s="6" t="s">
         <v>239</v>
       </c>
-      <c r="G93" s="7"/>
-    </row>
-    <row r="94" spans="1:7">
-      <c r="A94" s="7">
+      <c r="G93" s="2"/>
+      <c r="H93" s="3"/>
+    </row>
+    <row r="94" spans="1:8">
+      <c r="A94" s="2">
         <v>93</v>
       </c>
-      <c r="B94" s="1">
+      <c r="B94" s="5">
         <v>46188</v>
       </c>
-      <c r="C94" s="7" t="s">
+      <c r="C94" s="2" t="s">
         <v>286</v>
       </c>
-      <c r="D94" s="2" t="s">
+      <c r="D94" s="8" t="s">
         <v>246</v>
       </c>
-      <c r="E94" s="3" t="s">
+      <c r="E94" s="7" t="s">
         <v>194</v>
       </c>
-      <c r="F94" s="4" t="s">
+      <c r="F94" s="6" t="s">
         <v>196</v>
       </c>
-      <c r="G94" s="7"/>
-    </row>
-    <row r="95" spans="1:7">
-      <c r="A95" s="7">
+      <c r="G94" s="2"/>
+      <c r="H94" s="3"/>
+    </row>
+    <row r="95" spans="1:8">
+      <c r="A95" s="2">
         <v>94</v>
       </c>
-      <c r="B95" s="1">
+      <c r="B95" s="5">
         <v>46188</v>
       </c>
-      <c r="C95" s="7" t="s">
+      <c r="C95" s="2" t="s">
         <v>287</v>
       </c>
-      <c r="D95" s="2" t="s">
+      <c r="D95" s="8" t="s">
         <v>247</v>
       </c>
-      <c r="E95" s="3" t="s">
+      <c r="E95" s="7" t="s">
         <v>194</v>
       </c>
-      <c r="F95" s="4" t="s">
+      <c r="F95" s="6" t="s">
         <v>221</v>
       </c>
-      <c r="G95" s="7"/>
-    </row>
-    <row r="96" spans="1:7">
-      <c r="A96" s="7">
+      <c r="G95" s="2"/>
+      <c r="H95" s="3"/>
+    </row>
+    <row r="96" spans="1:8">
+      <c r="A96" s="2">
         <v>95</v>
       </c>
-      <c r="B96" s="1">
+      <c r="B96" s="5">
         <v>46188</v>
       </c>
-      <c r="C96" s="7" t="s">
+      <c r="C96" s="2" t="s">
         <v>288</v>
       </c>
-      <c r="D96" s="2" t="s">
+      <c r="D96" s="8" t="s">
         <v>248</v>
       </c>
-      <c r="E96" s="3" t="s">
+      <c r="E96" s="7" t="s">
         <v>194</v>
       </c>
-      <c r="F96" s="4" t="s">
+      <c r="F96" s="6" t="s">
         <v>323</v>
       </c>
-      <c r="G96" s="7"/>
-    </row>
-    <row r="97" spans="1:7" ht="33">
-      <c r="A97" s="7">
+      <c r="G96" s="2"/>
+      <c r="H96" s="3"/>
+    </row>
+    <row r="97" spans="1:8" ht="33">
+      <c r="A97" s="2">
         <v>96</v>
       </c>
-      <c r="B97" s="1">
+      <c r="B97" s="5">
         <v>46188</v>
       </c>
-      <c r="C97" s="7" t="s">
+      <c r="C97" s="2" t="s">
         <v>289</v>
       </c>
-      <c r="D97" s="8" t="s">
+      <c r="D97" s="10" t="s">
         <v>249</v>
       </c>
-      <c r="E97" s="3" t="s">
+      <c r="E97" s="7" t="s">
         <v>194</v>
       </c>
-      <c r="F97" s="4" t="s">
+      <c r="F97" s="6" t="s">
         <v>236</v>
       </c>
-      <c r="G97" s="7"/>
-    </row>
-    <row r="98" spans="1:7">
-      <c r="A98" s="7">
+      <c r="G97" s="2"/>
+      <c r="H97" s="3"/>
+    </row>
+    <row r="98" spans="1:8">
+      <c r="A98" s="2">
         <v>97</v>
       </c>
-      <c r="B98" s="1">
+      <c r="B98" s="5">
         <v>46188</v>
       </c>
-      <c r="C98" s="7" t="s">
+      <c r="C98" s="2" t="s">
         <v>290</v>
       </c>
-      <c r="D98" s="2" t="s">
+      <c r="D98" s="8" t="s">
         <v>250</v>
       </c>
-      <c r="E98" s="3" t="s">
+      <c r="E98" s="7" t="s">
         <v>194</v>
       </c>
-      <c r="F98" s="4" t="s">
+      <c r="F98" s="6" t="s">
         <v>221</v>
       </c>
-      <c r="G98" s="7"/>
-    </row>
-    <row r="99" spans="1:7">
-      <c r="A99" s="7">
+      <c r="G98" s="2"/>
+      <c r="H98" s="3"/>
+    </row>
+    <row r="99" spans="1:8">
+      <c r="A99" s="2">
         <v>98</v>
       </c>
-      <c r="B99" s="1">
+      <c r="B99" s="5">
         <v>46190</v>
       </c>
-      <c r="C99" s="7" t="s">
+      <c r="C99" s="2" t="s">
         <v>291</v>
       </c>
-      <c r="D99" s="4" t="s">
+      <c r="D99" s="6" t="s">
         <v>251</v>
       </c>
-      <c r="E99" s="3" t="s">
+      <c r="E99" s="7" t="s">
         <v>237</v>
       </c>
-      <c r="F99" s="4" t="s">
+      <c r="F99" s="6" t="s">
         <v>322</v>
       </c>
-      <c r="G99" s="7"/>
-    </row>
-    <row r="100" spans="1:7">
-      <c r="A100" s="7">
+      <c r="G99" s="2"/>
+      <c r="H99" s="3"/>
+    </row>
+    <row r="100" spans="1:8">
+      <c r="A100" s="2">
         <v>99</v>
       </c>
-      <c r="B100" s="1">
+      <c r="B100" s="5">
         <v>46190</v>
       </c>
-      <c r="C100" s="7" t="s">
+      <c r="C100" s="2" t="s">
         <v>292</v>
       </c>
-      <c r="D100" s="4" t="s">
+      <c r="D100" s="6" t="s">
         <v>252</v>
       </c>
-      <c r="E100" s="3" t="s">
+      <c r="E100" s="7" t="s">
         <v>209</v>
       </c>
-      <c r="F100" s="4" t="s">
+      <c r="F100" s="6" t="s">
         <v>239</v>
       </c>
-      <c r="G100" s="7"/>
-    </row>
-    <row r="101" spans="1:7">
-      <c r="A101" s="7">
+      <c r="G100" s="2"/>
+      <c r="H100" s="3"/>
+    </row>
+    <row r="101" spans="1:8">
+      <c r="A101" s="2">
         <v>100</v>
       </c>
-      <c r="B101" s="1">
+      <c r="B101" s="5">
         <v>46191</v>
       </c>
-      <c r="C101" s="7" t="s">
+      <c r="C101" s="2" t="s">
         <v>293</v>
       </c>
-      <c r="D101" s="2" t="s">
+      <c r="D101" s="8" t="s">
         <v>253</v>
       </c>
-      <c r="E101" s="3" t="s">
+      <c r="E101" s="7" t="s">
         <v>194</v>
       </c>
-      <c r="F101" s="4" t="s">
+      <c r="F101" s="6" t="s">
         <v>196</v>
       </c>
-      <c r="G101" s="7"/>
-    </row>
-    <row r="102" spans="1:7">
-      <c r="A102" s="7">
+      <c r="G101" s="2"/>
+      <c r="H101" s="3"/>
+    </row>
+    <row r="102" spans="1:8">
+      <c r="A102" s="2">
         <v>101</v>
       </c>
-      <c r="B102" s="1">
+      <c r="B102" s="5">
         <v>46195</v>
       </c>
-      <c r="C102" s="7" t="s">
+      <c r="C102" s="2" t="s">
         <v>294</v>
       </c>
-      <c r="D102" s="2" t="s">
+      <c r="D102" s="8" t="s">
         <v>254</v>
       </c>
-      <c r="E102" s="3" t="s">
+      <c r="E102" s="7" t="s">
         <v>194</v>
       </c>
-      <c r="F102" s="4" t="s">
+      <c r="F102" s="6" t="s">
         <v>196</v>
       </c>
-      <c r="G102" s="7"/>
-    </row>
-    <row r="103" spans="1:7">
-      <c r="A103" s="7">
+      <c r="G102" s="2"/>
+      <c r="H102" s="3"/>
+    </row>
+    <row r="103" spans="1:8">
+      <c r="A103" s="2">
         <v>102</v>
       </c>
-      <c r="B103" s="1">
+      <c r="B103" s="5">
         <v>46195</v>
       </c>
-      <c r="C103" s="7" t="s">
+      <c r="C103" s="2" t="s">
         <v>295</v>
       </c>
-      <c r="D103" s="2" t="s">
+      <c r="D103" s="8" t="s">
         <v>255</v>
       </c>
-      <c r="E103" s="3" t="s">
+      <c r="E103" s="7" t="s">
         <v>194</v>
       </c>
-      <c r="F103" s="4" t="s">
+      <c r="F103" s="6" t="s">
         <v>196</v>
       </c>
-      <c r="G103" s="7"/>
-    </row>
-    <row r="104" spans="1:7">
-      <c r="A104" s="7">
+      <c r="G103" s="2"/>
+      <c r="H103" s="3"/>
+    </row>
+    <row r="104" spans="1:8">
+      <c r="A104" s="2">
         <v>103</v>
       </c>
-      <c r="B104" s="1">
+      <c r="B104" s="5">
         <v>46196</v>
       </c>
-      <c r="C104" s="7" t="s">
+      <c r="C104" s="2" t="s">
         <v>298</v>
       </c>
-      <c r="D104" s="4" t="s">
+      <c r="D104" s="6" t="s">
         <v>256</v>
       </c>
-      <c r="E104" s="3" t="s">
+      <c r="E104" s="7" t="s">
         <v>237</v>
       </c>
-      <c r="F104" s="4" t="s">
+      <c r="F104" s="6" t="s">
         <v>196</v>
       </c>
-      <c r="G104" s="7"/>
-    </row>
-    <row r="105" spans="1:7">
-      <c r="A105" s="7">
+      <c r="G104" s="2"/>
+      <c r="H104" s="3"/>
+    </row>
+    <row r="105" spans="1:8">
+      <c r="A105" s="2">
         <v>104</v>
       </c>
-      <c r="B105" s="1">
+      <c r="B105" s="5">
         <v>46197</v>
       </c>
-      <c r="C105" s="7" t="s">
+      <c r="C105" s="2" t="s">
         <v>296</v>
       </c>
-      <c r="D105" s="2" t="s">
+      <c r="D105" s="8" t="s">
         <v>257</v>
       </c>
-      <c r="E105" s="3" t="s">
+      <c r="E105" s="7" t="s">
         <v>194</v>
       </c>
-      <c r="F105" s="4" t="s">
+      <c r="F105" s="6" t="s">
         <v>196</v>
       </c>
-      <c r="G105" s="7"/>
-    </row>
-    <row r="106" spans="1:7">
-      <c r="A106" s="7">
+      <c r="G105" s="2"/>
+      <c r="H105" s="3"/>
+    </row>
+    <row r="106" spans="1:8">
+      <c r="A106" s="2">
         <v>105</v>
       </c>
-      <c r="B106" s="1">
+      <c r="B106" s="5">
         <v>46197</v>
       </c>
-      <c r="C106" s="7" t="s">
+      <c r="C106" s="2" t="s">
         <v>297</v>
       </c>
-      <c r="D106" s="2" t="s">
+      <c r="D106" s="8" t="s">
         <v>258</v>
       </c>
-      <c r="E106" s="3" t="s">
+      <c r="E106" s="7" t="s">
         <v>194</v>
       </c>
-      <c r="F106" s="4" t="s">
+      <c r="F106" s="6" t="s">
         <v>196</v>
       </c>
-      <c r="G106" s="7"/>
-    </row>
-    <row r="107" spans="1:7">
-      <c r="A107" s="7">
+      <c r="G106" s="2"/>
+      <c r="H106" s="3"/>
+    </row>
+    <row r="107" spans="1:8">
+      <c r="A107" s="2">
         <v>106</v>
       </c>
-      <c r="B107" s="1">
+      <c r="B107" s="5">
         <v>46198</v>
       </c>
-      <c r="C107" s="7" t="s">
+      <c r="C107" s="2" t="s">
         <v>299</v>
       </c>
-      <c r="D107" s="2" t="s">
+      <c r="D107" s="8" t="s">
         <v>259</v>
       </c>
-      <c r="E107" s="3" t="s">
+      <c r="E107" s="7" t="s">
         <v>194</v>
       </c>
-      <c r="F107" s="4" t="s">
+      <c r="F107" s="6" t="s">
         <v>196</v>
       </c>
-      <c r="G107" s="7"/>
-    </row>
-    <row r="108" spans="1:7">
-      <c r="A108" s="7">
+      <c r="G107" s="2"/>
+      <c r="H107" s="3"/>
+    </row>
+    <row r="108" spans="1:8">
+      <c r="A108" s="2">
         <v>107</v>
       </c>
-      <c r="B108" s="1">
+      <c r="B108" s="5">
         <v>46198</v>
       </c>
-      <c r="C108" s="7" t="s">
+      <c r="C108" s="2" t="s">
         <v>300</v>
       </c>
-      <c r="D108" s="4" t="s">
+      <c r="D108" s="6" t="s">
         <v>260</v>
       </c>
-      <c r="E108" s="3" t="s">
+      <c r="E108" s="7" t="s">
         <v>237</v>
       </c>
-      <c r="F108" s="4" t="s">
+      <c r="F108" s="6" t="s">
         <v>221</v>
       </c>
-      <c r="G108" s="7"/>
-    </row>
-    <row r="109" spans="1:7">
-      <c r="A109" s="7">
+      <c r="G108" s="2"/>
+      <c r="H108" s="3"/>
+    </row>
+    <row r="109" spans="1:8">
+      <c r="A109" s="2">
         <v>108</v>
       </c>
-      <c r="B109" s="1">
+      <c r="B109" s="5">
         <v>46204</v>
       </c>
-      <c r="C109" s="7" t="s">
+      <c r="C109" s="2" t="s">
         <v>301</v>
       </c>
-      <c r="D109" s="2" t="s">
+      <c r="D109" s="8" t="s">
         <v>261</v>
       </c>
-      <c r="E109" s="3" t="s">
+      <c r="E109" s="7" t="s">
         <v>194</v>
       </c>
-      <c r="F109" s="4" t="s">
+      <c r="F109" s="6" t="s">
         <v>196</v>
       </c>
-      <c r="G109" s="7"/>
-    </row>
-    <row r="110" spans="1:7">
-      <c r="A110" s="7">
+      <c r="G109" s="2"/>
+      <c r="H109" s="3"/>
+    </row>
+    <row r="110" spans="1:8">
+      <c r="A110" s="2">
         <v>109</v>
       </c>
-      <c r="B110" s="1">
+      <c r="B110" s="5">
         <v>46206</v>
       </c>
-      <c r="C110" s="7" t="s">
+      <c r="C110" s="2" t="s">
         <v>229</v>
       </c>
-      <c r="D110" s="2" t="s">
+      <c r="D110" s="8" t="s">
         <v>262</v>
       </c>
-      <c r="E110" s="3" t="s">
+      <c r="E110" s="7" t="s">
         <v>194</v>
       </c>
-      <c r="F110" s="4" t="s">
+      <c r="F110" s="6" t="s">
         <v>221</v>
       </c>
-      <c r="G110" s="7"/>
-    </row>
-    <row r="111" spans="1:7">
-      <c r="A111" s="7">
+      <c r="G110" s="2"/>
+      <c r="H110" s="3"/>
+    </row>
+    <row r="111" spans="1:8">
+      <c r="A111" s="2">
         <v>110</v>
       </c>
-      <c r="B111" s="11">
+      <c r="B111" s="12">
         <v>46206</v>
       </c>
-      <c r="C111" s="9" t="s">
+      <c r="C111" s="11" t="s">
         <v>358</v>
       </c>
-      <c r="D111" s="13" t="s">
+      <c r="D111" s="9" t="s">
         <v>328</v>
       </c>
-      <c r="E111" s="17" t="s">
+      <c r="E111" s="7" t="s">
         <v>208</v>
       </c>
-      <c r="F111" s="14" t="s">
+      <c r="F111" s="6" t="s">
         <v>221</v>
       </c>
-      <c r="G111" s="7"/>
-    </row>
-    <row r="112" spans="1:7">
-      <c r="A112" s="7">
+      <c r="G111" s="2"/>
+      <c r="H111" s="3"/>
+    </row>
+    <row r="112" spans="1:8">
+      <c r="A112" s="2">
         <v>111</v>
       </c>
-      <c r="B112" s="1">
+      <c r="B112" s="5">
         <v>46211</v>
       </c>
-      <c r="C112" s="7" t="s">
+      <c r="C112" s="2" t="s">
         <v>309</v>
       </c>
-      <c r="D112" s="2" t="s">
+      <c r="D112" s="8" t="s">
         <v>263</v>
       </c>
-      <c r="E112" s="3" t="s">
+      <c r="E112" s="7" t="s">
         <v>238</v>
       </c>
-      <c r="F112" s="4" t="s">
+      <c r="F112" s="6" t="s">
         <v>196</v>
       </c>
-      <c r="G112" s="7"/>
-    </row>
-    <row r="113" spans="1:7">
-      <c r="A113" s="7">
+      <c r="G112" s="2"/>
+      <c r="H112" s="3"/>
+    </row>
+    <row r="113" spans="1:8">
+      <c r="A113" s="2">
         <v>112</v>
       </c>
-      <c r="B113" s="1">
+      <c r="B113" s="5">
         <v>46211</v>
       </c>
-      <c r="C113" s="7" t="s">
+      <c r="C113" s="2" t="s">
         <v>303</v>
       </c>
-      <c r="D113" s="2" t="s">
+      <c r="D113" s="8" t="s">
         <v>264</v>
       </c>
-      <c r="E113" s="3" t="s">
+      <c r="E113" s="7" t="s">
         <v>238</v>
       </c>
-      <c r="F113" s="4" t="s">
+      <c r="F113" s="6" t="s">
         <v>196</v>
       </c>
-      <c r="G113" s="7"/>
-    </row>
-    <row r="114" spans="1:7">
-      <c r="A114" s="7">
+      <c r="G113" s="2"/>
+      <c r="H113" s="3"/>
+    </row>
+    <row r="114" spans="1:8">
+      <c r="A114" s="2">
         <v>113</v>
       </c>
-      <c r="B114" s="1">
+      <c r="B114" s="5">
         <v>46211</v>
       </c>
-      <c r="C114" s="7" t="s">
+      <c r="C114" s="2" t="s">
         <v>304</v>
       </c>
-      <c r="D114" s="2" t="s">
+      <c r="D114" s="8" t="s">
         <v>265</v>
       </c>
-      <c r="E114" s="3" t="s">
+      <c r="E114" s="7" t="s">
         <v>238</v>
       </c>
-      <c r="F114" s="4" t="s">
+      <c r="F114" s="6" t="s">
         <v>221</v>
       </c>
-      <c r="G114" s="7"/>
-    </row>
-    <row r="115" spans="1:7">
-      <c r="A115" s="7">
+      <c r="G114" s="2"/>
+      <c r="H114" s="3"/>
+    </row>
+    <row r="115" spans="1:8">
+      <c r="A115" s="2">
         <v>114</v>
       </c>
-      <c r="B115" s="1">
+      <c r="B115" s="5">
         <v>46211</v>
       </c>
-      <c r="C115" s="7" t="s">
+      <c r="C115" s="2" t="s">
         <v>200</v>
       </c>
-      <c r="D115" s="2" t="s">
+      <c r="D115" s="8" t="s">
         <v>266</v>
       </c>
-      <c r="E115" s="3" t="s">
+      <c r="E115" s="7" t="s">
         <v>194</v>
       </c>
-      <c r="F115" s="4" t="s">
+      <c r="F115" s="6" t="s">
         <v>196</v>
       </c>
-      <c r="G115" s="7"/>
-    </row>
-    <row r="116" spans="1:7" ht="33">
-      <c r="A116" s="7">
+      <c r="G115" s="2"/>
+      <c r="H115" s="3"/>
+    </row>
+    <row r="116" spans="1:8" ht="33">
+      <c r="A116" s="2">
         <v>115</v>
       </c>
-      <c r="B116" s="11">
+      <c r="B116" s="12">
         <v>46213</v>
       </c>
-      <c r="C116" s="10" t="s">
+      <c r="C116" s="2" t="s">
         <v>359</v>
       </c>
-      <c r="D116" s="15" t="s">
+      <c r="D116" s="13" t="s">
         <v>329</v>
       </c>
-      <c r="E116" s="17" t="s">
+      <c r="E116" s="7" t="s">
         <v>324</v>
       </c>
-      <c r="F116" s="14" t="s">
+      <c r="F116" s="6" t="s">
         <v>236</v>
       </c>
-      <c r="G116" s="7"/>
-    </row>
-    <row r="117" spans="1:7" ht="33">
-      <c r="A117" s="7">
+      <c r="G116" s="2"/>
+      <c r="H116" s="3"/>
+    </row>
+    <row r="117" spans="1:8" ht="33">
+      <c r="A117" s="2">
         <v>116</v>
       </c>
-      <c r="B117" s="1">
+      <c r="B117" s="5">
         <v>46216</v>
       </c>
-      <c r="C117" s="7" t="s">
+      <c r="C117" s="2" t="s">
         <v>305</v>
       </c>
-      <c r="D117" s="8" t="s">
+      <c r="D117" s="10" t="s">
         <v>267</v>
       </c>
-      <c r="E117" s="3" t="s">
+      <c r="E117" s="7" t="s">
         <v>194</v>
       </c>
-      <c r="F117" s="4" t="s">
+      <c r="F117" s="6" t="s">
         <v>221</v>
       </c>
-      <c r="G117" s="7"/>
-    </row>
-    <row r="118" spans="1:7">
-      <c r="A118" s="7">
+      <c r="G117" s="2"/>
+      <c r="H117" s="3"/>
+    </row>
+    <row r="118" spans="1:8">
+      <c r="A118" s="2">
         <v>117</v>
       </c>
-      <c r="B118" s="1">
+      <c r="B118" s="5">
         <v>46216</v>
       </c>
-      <c r="C118" s="7" t="s">
+      <c r="C118" s="2" t="s">
         <v>306</v>
       </c>
-      <c r="D118" s="2" t="s">
+      <c r="D118" s="8" t="s">
         <v>268</v>
       </c>
-      <c r="E118" s="3" t="s">
+      <c r="E118" s="7" t="s">
         <v>194</v>
       </c>
-      <c r="F118" s="4" t="s">
+      <c r="F118" s="6" t="s">
         <v>196</v>
       </c>
-      <c r="G118" s="7"/>
-    </row>
-    <row r="119" spans="1:7">
-      <c r="A119" s="7">
+      <c r="G118" s="2"/>
+      <c r="H118" s="3"/>
+    </row>
+    <row r="119" spans="1:8">
+      <c r="A119" s="2">
         <v>118</v>
       </c>
-      <c r="B119" s="11">
+      <c r="B119" s="12">
         <v>46216</v>
       </c>
-      <c r="C119" s="10" t="s">
+      <c r="C119" s="2" t="s">
         <v>360</v>
       </c>
-      <c r="D119" s="14" t="s">
+      <c r="D119" s="6" t="s">
         <v>330</v>
       </c>
-      <c r="E119" s="17" t="s">
+      <c r="E119" s="7" t="s">
+        <v>445</v>
+      </c>
+      <c r="F119" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="G119" s="2"/>
+      <c r="H119" s="3"/>
+    </row>
+    <row r="120" spans="1:8">
+      <c r="A120" s="2">
+        <v>119</v>
+      </c>
+      <c r="B120" s="12">
+        <v>46218</v>
+      </c>
+      <c r="C120" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="D120" s="14" t="s">
+        <v>331</v>
+      </c>
+      <c r="E120" s="7" t="s">
+        <v>237</v>
+      </c>
+      <c r="F120" s="6" t="s">
+        <v>236</v>
+      </c>
+      <c r="G120" s="2"/>
+      <c r="H120" s="3"/>
+    </row>
+    <row r="121" spans="1:8">
+      <c r="A121" s="2">
+        <v>120</v>
+      </c>
+      <c r="B121" s="12">
+        <v>46223</v>
+      </c>
+      <c r="C121" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="D121" s="6" t="s">
+        <v>332</v>
+      </c>
+      <c r="E121" s="7" t="s">
+        <v>237</v>
+      </c>
+      <c r="F121" s="6" t="s">
+        <v>236</v>
+      </c>
+      <c r="G121" s="2"/>
+      <c r="H121" s="3"/>
+    </row>
+    <row r="122" spans="1:8">
+      <c r="A122" s="2">
+        <v>121</v>
+      </c>
+      <c r="B122" s="5">
+        <v>46223</v>
+      </c>
+      <c r="C122" s="2" t="s">
+        <v>362</v>
+      </c>
+      <c r="D122" s="6" t="s">
+        <v>333</v>
+      </c>
+      <c r="E122" s="7" t="s">
+        <v>325</v>
+      </c>
+      <c r="F122" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="G122" s="2"/>
+      <c r="H122" s="3"/>
+    </row>
+    <row r="123" spans="1:8">
+      <c r="A123" s="2">
+        <v>122</v>
+      </c>
+      <c r="B123" s="5">
+        <v>46223</v>
+      </c>
+      <c r="C123" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="D123" s="6" t="s">
+        <v>334</v>
+      </c>
+      <c r="E123" s="7" t="s">
+        <v>325</v>
+      </c>
+      <c r="F123" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="G123" s="2"/>
+      <c r="H123" s="3"/>
+    </row>
+    <row r="124" spans="1:8">
+      <c r="A124" s="2">
+        <v>123</v>
+      </c>
+      <c r="B124" s="5">
+        <v>46223</v>
+      </c>
+      <c r="C124" s="2" t="s">
+        <v>364</v>
+      </c>
+      <c r="D124" s="6" t="s">
+        <v>335</v>
+      </c>
+      <c r="E124" s="7" t="s">
+        <v>325</v>
+      </c>
+      <c r="F124" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="G124" s="2"/>
+      <c r="H124" s="3"/>
+    </row>
+    <row r="125" spans="1:8">
+      <c r="A125" s="2">
+        <v>124</v>
+      </c>
+      <c r="B125" s="5">
+        <v>46223</v>
+      </c>
+      <c r="C125" s="2" t="s">
+        <v>365</v>
+      </c>
+      <c r="D125" s="6" t="s">
+        <v>336</v>
+      </c>
+      <c r="E125" s="7" t="s">
+        <v>325</v>
+      </c>
+      <c r="F125" s="6" t="s">
+        <v>236</v>
+      </c>
+      <c r="G125" s="2"/>
+      <c r="H125" s="3"/>
+    </row>
+    <row r="126" spans="1:8">
+      <c r="A126" s="2">
+        <v>125</v>
+      </c>
+      <c r="B126" s="5">
+        <v>46223</v>
+      </c>
+      <c r="C126" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="D126" s="6" t="s">
+        <v>337</v>
+      </c>
+      <c r="E126" s="7" t="s">
+        <v>325</v>
+      </c>
+      <c r="F126" s="6" t="s">
+        <v>221</v>
+      </c>
+      <c r="G126" s="2"/>
+      <c r="H126" s="3"/>
+    </row>
+    <row r="127" spans="1:8">
+      <c r="A127" s="2">
+        <v>126</v>
+      </c>
+      <c r="B127" s="5">
+        <v>46223</v>
+      </c>
+      <c r="C127" s="2" t="s">
+        <v>367</v>
+      </c>
+      <c r="D127" s="6" t="s">
+        <v>338</v>
+      </c>
+      <c r="E127" s="7" t="s">
+        <v>325</v>
+      </c>
+      <c r="F127" s="6" t="s">
+        <v>236</v>
+      </c>
+      <c r="G127" s="2"/>
+      <c r="H127" s="3"/>
+    </row>
+    <row r="128" spans="1:8">
+      <c r="A128" s="2">
+        <v>127</v>
+      </c>
+      <c r="B128" s="5">
+        <v>46223</v>
+      </c>
+      <c r="C128" s="2" t="s">
+        <v>368</v>
+      </c>
+      <c r="D128" s="6" t="s">
+        <v>339</v>
+      </c>
+      <c r="E128" s="7" t="s">
+        <v>325</v>
+      </c>
+      <c r="F128" s="6" t="s">
+        <v>236</v>
+      </c>
+      <c r="G128" s="2"/>
+      <c r="H128" s="3"/>
+    </row>
+    <row r="129" spans="1:8">
+      <c r="A129" s="2">
+        <v>128</v>
+      </c>
+      <c r="B129" s="5">
+        <v>46223</v>
+      </c>
+      <c r="C129" s="2" t="s">
+        <v>369</v>
+      </c>
+      <c r="D129" s="6" t="s">
+        <v>340</v>
+      </c>
+      <c r="E129" s="7" t="s">
+        <v>325</v>
+      </c>
+      <c r="F129" s="6" t="s">
+        <v>236</v>
+      </c>
+      <c r="G129" s="2"/>
+      <c r="H129" s="3"/>
+    </row>
+    <row r="130" spans="1:8">
+      <c r="A130" s="2">
+        <v>129</v>
+      </c>
+      <c r="B130" s="5">
+        <v>46223</v>
+      </c>
+      <c r="C130" s="2" t="s">
+        <v>370</v>
+      </c>
+      <c r="D130" s="6" t="s">
+        <v>341</v>
+      </c>
+      <c r="E130" s="7" t="s">
+        <v>325</v>
+      </c>
+      <c r="F130" s="6" t="s">
+        <v>236</v>
+      </c>
+      <c r="G130" s="2"/>
+      <c r="H130" s="3"/>
+    </row>
+    <row r="131" spans="1:8">
+      <c r="A131" s="2">
+        <v>130</v>
+      </c>
+      <c r="B131" s="5">
+        <v>46223</v>
+      </c>
+      <c r="C131" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="D131" s="6" t="s">
+        <v>342</v>
+      </c>
+      <c r="E131" s="7" t="s">
+        <v>325</v>
+      </c>
+      <c r="F131" s="6" t="s">
+        <v>236</v>
+      </c>
+      <c r="G131" s="3"/>
+      <c r="H131" s="3"/>
+    </row>
+    <row r="132" spans="1:8">
+      <c r="A132" s="2">
+        <v>131</v>
+      </c>
+      <c r="B132" s="5">
+        <v>46223</v>
+      </c>
+      <c r="C132" s="2" t="s">
+        <v>372</v>
+      </c>
+      <c r="D132" s="6" t="s">
+        <v>343</v>
+      </c>
+      <c r="E132" s="7" t="s">
+        <v>325</v>
+      </c>
+      <c r="F132" s="6" t="s">
+        <v>236</v>
+      </c>
+      <c r="G132" s="3"/>
+      <c r="H132" s="3"/>
+    </row>
+    <row r="133" spans="1:8">
+      <c r="A133" s="2">
+        <v>132</v>
+      </c>
+      <c r="B133" s="5">
+        <v>46224</v>
+      </c>
+      <c r="C133" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="D133" s="8" t="s">
+        <v>269</v>
+      </c>
+      <c r="E133" s="7" t="s">
+        <v>238</v>
+      </c>
+      <c r="F133" s="6" t="s">
+        <v>221</v>
+      </c>
+      <c r="G133" s="3"/>
+      <c r="H133" s="3"/>
+    </row>
+    <row r="134" spans="1:8">
+      <c r="A134" s="2">
+        <v>133</v>
+      </c>
+      <c r="B134" s="5">
+        <v>46225</v>
+      </c>
+      <c r="C134" s="11" t="s">
+        <v>308</v>
+      </c>
+      <c r="D134" s="8" t="s">
+        <v>270</v>
+      </c>
+      <c r="E134" s="7" t="s">
+        <v>238</v>
+      </c>
+      <c r="F134" s="6" t="s">
+        <v>323</v>
+      </c>
+      <c r="G134" s="3"/>
+      <c r="H134" s="3"/>
+    </row>
+    <row r="135" spans="1:8">
+      <c r="A135" s="2">
+        <v>134</v>
+      </c>
+      <c r="B135" s="5">
+        <v>46225</v>
+      </c>
+      <c r="C135" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="D135" s="10" t="s">
+        <v>271</v>
+      </c>
+      <c r="E135" s="7" t="s">
+        <v>238</v>
+      </c>
+      <c r="F135" s="6" t="s">
+        <v>323</v>
+      </c>
+      <c r="G135" s="3"/>
+      <c r="H135" s="3"/>
+    </row>
+    <row r="136" spans="1:8">
+      <c r="A136" s="2">
+        <v>135</v>
+      </c>
+      <c r="B136" s="12">
+        <v>46225</v>
+      </c>
+      <c r="C136" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="D136" s="6" t="s">
+        <v>344</v>
+      </c>
+      <c r="E136" s="7" t="s">
+        <v>326</v>
+      </c>
+      <c r="F136" s="6" t="s">
+        <v>221</v>
+      </c>
+      <c r="G136" s="3"/>
+      <c r="H136" s="3"/>
+    </row>
+    <row r="137" spans="1:8">
+      <c r="A137" s="2">
+        <v>136</v>
+      </c>
+      <c r="B137" s="5">
+        <v>46225</v>
+      </c>
+      <c r="C137" s="2" t="s">
+        <v>374</v>
+      </c>
+      <c r="D137" s="6" t="s">
+        <v>345</v>
+      </c>
+      <c r="E137" s="7" t="s">
+        <v>325</v>
+      </c>
+      <c r="F137" s="6" t="s">
+        <v>236</v>
+      </c>
+      <c r="G137" s="3"/>
+      <c r="H137" s="3"/>
+    </row>
+    <row r="138" spans="1:8">
+      <c r="A138" s="2">
+        <v>137</v>
+      </c>
+      <c r="B138" s="5">
+        <v>46225</v>
+      </c>
+      <c r="C138" s="2" t="s">
+        <v>364</v>
+      </c>
+      <c r="D138" s="6" t="s">
+        <v>346</v>
+      </c>
+      <c r="E138" s="7" t="s">
+        <v>325</v>
+      </c>
+      <c r="F138" s="6" t="s">
+        <v>236</v>
+      </c>
+      <c r="G138" s="3"/>
+      <c r="H138" s="3"/>
+    </row>
+    <row r="139" spans="1:8">
+      <c r="A139" s="2">
+        <v>138</v>
+      </c>
+      <c r="B139" s="5">
+        <v>46225</v>
+      </c>
+      <c r="C139" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="D139" s="6" t="s">
+        <v>347</v>
+      </c>
+      <c r="E139" s="7" t="s">
+        <v>325</v>
+      </c>
+      <c r="F139" s="6" t="s">
+        <v>236</v>
+      </c>
+      <c r="G139" s="3"/>
+      <c r="H139" s="3"/>
+    </row>
+    <row r="140" spans="1:8">
+      <c r="A140" s="2">
+        <v>139</v>
+      </c>
+      <c r="B140" s="5">
+        <v>46225</v>
+      </c>
+      <c r="C140" s="2" t="s">
+        <v>376</v>
+      </c>
+      <c r="D140" s="6" t="s">
+        <v>348</v>
+      </c>
+      <c r="E140" s="7" t="s">
+        <v>325</v>
+      </c>
+      <c r="F140" s="6" t="s">
+        <v>236</v>
+      </c>
+      <c r="G140" s="3"/>
+      <c r="H140" s="3"/>
+    </row>
+    <row r="141" spans="1:8">
+      <c r="A141" s="2">
+        <v>140</v>
+      </c>
+      <c r="B141" s="5">
+        <v>46225</v>
+      </c>
+      <c r="C141" s="2" t="s">
+        <v>377</v>
+      </c>
+      <c r="D141" s="6" t="s">
+        <v>349</v>
+      </c>
+      <c r="E141" s="7" t="s">
+        <v>325</v>
+      </c>
+      <c r="F141" s="6" t="s">
+        <v>236</v>
+      </c>
+      <c r="G141" s="3"/>
+      <c r="H141" s="3"/>
+    </row>
+    <row r="142" spans="1:8">
+      <c r="A142" s="2">
+        <v>141</v>
+      </c>
+      <c r="B142" s="5">
+        <v>46225</v>
+      </c>
+      <c r="C142" s="2" t="s">
+        <v>378</v>
+      </c>
+      <c r="D142" s="6" t="s">
+        <v>350</v>
+      </c>
+      <c r="E142" s="7" t="s">
+        <v>325</v>
+      </c>
+      <c r="F142" s="6" t="s">
+        <v>236</v>
+      </c>
+      <c r="G142" s="3"/>
+      <c r="H142" s="3"/>
+    </row>
+    <row r="143" spans="1:8">
+      <c r="A143" s="2">
+        <v>142</v>
+      </c>
+      <c r="B143" s="5">
+        <v>46225</v>
+      </c>
+      <c r="C143" s="2" t="s">
+        <v>378</v>
+      </c>
+      <c r="D143" s="6" t="s">
+        <v>351</v>
+      </c>
+      <c r="E143" s="7" t="s">
+        <v>325</v>
+      </c>
+      <c r="F143" s="6" t="s">
+        <v>236</v>
+      </c>
+      <c r="G143" s="3"/>
+      <c r="H143" s="3"/>
+    </row>
+    <row r="144" spans="1:8">
+      <c r="A144" s="2">
+        <v>143</v>
+      </c>
+      <c r="B144" s="5">
+        <v>46225</v>
+      </c>
+      <c r="C144" s="2" t="s">
+        <v>378</v>
+      </c>
+      <c r="D144" s="15" t="s">
+        <v>352</v>
+      </c>
+      <c r="E144" s="7" t="s">
+        <v>325</v>
+      </c>
+      <c r="F144" s="6" t="s">
+        <v>236</v>
+      </c>
+      <c r="G144" s="3"/>
+      <c r="H144" s="3"/>
+    </row>
+    <row r="145" spans="1:8">
+      <c r="A145" s="2">
+        <v>144</v>
+      </c>
+      <c r="B145" s="5">
+        <v>46225</v>
+      </c>
+      <c r="C145" s="2" t="s">
+        <v>379</v>
+      </c>
+      <c r="D145" s="15" t="s">
+        <v>353</v>
+      </c>
+      <c r="E145" s="7" t="s">
+        <v>325</v>
+      </c>
+      <c r="F145" s="6" t="s">
+        <v>236</v>
+      </c>
+      <c r="G145" s="3"/>
+      <c r="H145" s="3"/>
+    </row>
+    <row r="146" spans="1:8">
+      <c r="A146" s="2">
+        <v>145</v>
+      </c>
+      <c r="B146" s="5">
+        <v>46225</v>
+      </c>
+      <c r="C146" s="2" t="s">
+        <v>380</v>
+      </c>
+      <c r="D146" s="15" t="s">
+        <v>354</v>
+      </c>
+      <c r="E146" s="7" t="s">
+        <v>325</v>
+      </c>
+      <c r="F146" s="6" t="s">
+        <v>236</v>
+      </c>
+      <c r="G146" s="3"/>
+      <c r="H146" s="3"/>
+    </row>
+    <row r="147" spans="1:8">
+      <c r="A147" s="2">
+        <v>146</v>
+      </c>
+      <c r="B147" s="5">
+        <v>46225</v>
+      </c>
+      <c r="C147" s="2" t="s">
+        <v>364</v>
+      </c>
+      <c r="D147" s="6" t="s">
+        <v>355</v>
+      </c>
+      <c r="E147" s="7" t="s">
+        <v>325</v>
+      </c>
+      <c r="F147" s="6" t="s">
+        <v>236</v>
+      </c>
+      <c r="G147" s="3"/>
+      <c r="H147" s="3"/>
+    </row>
+    <row r="148" spans="1:8" ht="49.5">
+      <c r="A148" s="2">
+        <v>147</v>
+      </c>
+      <c r="B148" s="5">
+        <v>46226</v>
+      </c>
+      <c r="C148" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="D148" s="10" t="s">
+        <v>272</v>
+      </c>
+      <c r="E148" s="7" t="s">
+        <v>238</v>
+      </c>
+      <c r="F148" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="G148" s="3"/>
+      <c r="H148" s="3"/>
+    </row>
+    <row r="149" spans="1:8" ht="33">
+      <c r="A149" s="2">
+        <v>148</v>
+      </c>
+      <c r="B149" s="5">
+        <v>46226</v>
+      </c>
+      <c r="C149" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="D149" s="10" t="s">
+        <v>273</v>
+      </c>
+      <c r="E149" s="7" t="s">
+        <v>238</v>
+      </c>
+      <c r="F149" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="G149" s="3"/>
+      <c r="H149" s="3"/>
+    </row>
+    <row r="150" spans="1:8">
+      <c r="A150" s="2">
+        <v>149</v>
+      </c>
+      <c r="B150" s="5">
+        <v>46226</v>
+      </c>
+      <c r="C150" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="D150" s="10" t="s">
+        <v>274</v>
+      </c>
+      <c r="E150" s="7" t="s">
+        <v>194</v>
+      </c>
+      <c r="F150" s="6" t="s">
+        <v>221</v>
+      </c>
+      <c r="G150" s="3"/>
+      <c r="H150" s="3"/>
+    </row>
+    <row r="151" spans="1:8">
+      <c r="A151" s="2">
+        <v>150</v>
+      </c>
+      <c r="B151" s="12">
+        <v>46226</v>
+      </c>
+      <c r="C151" s="2" t="s">
+        <v>381</v>
+      </c>
+      <c r="D151" s="6" t="s">
+        <v>356</v>
+      </c>
+      <c r="E151" s="7" t="s">
+        <v>237</v>
+      </c>
+      <c r="F151" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="G151" s="3"/>
+      <c r="H151" s="3"/>
+    </row>
+    <row r="152" spans="1:8">
+      <c r="A152" s="2">
+        <v>151</v>
+      </c>
+      <c r="B152" s="5">
+        <v>46230</v>
+      </c>
+      <c r="C152" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="D152" s="10" t="s">
+        <v>275</v>
+      </c>
+      <c r="E152" s="7" t="s">
+        <v>238</v>
+      </c>
+      <c r="F152" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="G152" s="3"/>
+      <c r="H152" s="3"/>
+    </row>
+    <row r="153" spans="1:8">
+      <c r="A153" s="2">
+        <v>152</v>
+      </c>
+      <c r="B153" s="5">
+        <v>46230</v>
+      </c>
+      <c r="C153" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="D153" s="10" t="s">
+        <v>316</v>
+      </c>
+      <c r="E153" s="7" t="s">
+        <v>194</v>
+      </c>
+      <c r="F153" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="G153" s="3"/>
+      <c r="H153" s="3"/>
+    </row>
+    <row r="154" spans="1:8">
+      <c r="A154" s="2">
+        <v>153</v>
+      </c>
+      <c r="B154" s="5">
+        <v>46230</v>
+      </c>
+      <c r="C154" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="D154" s="10" t="s">
+        <v>317</v>
+      </c>
+      <c r="E154" s="7" t="s">
+        <v>194</v>
+      </c>
+      <c r="F154" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="G154" s="3"/>
+      <c r="H154" s="3"/>
+    </row>
+    <row r="155" spans="1:8">
+      <c r="A155" s="2">
+        <v>154</v>
+      </c>
+      <c r="B155" s="5">
+        <v>46234</v>
+      </c>
+      <c r="C155" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="D155" s="10" t="s">
+        <v>276</v>
+      </c>
+      <c r="E155" s="7" t="s">
+        <v>238</v>
+      </c>
+      <c r="F155" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="G155" s="3"/>
+      <c r="H155" s="3"/>
+    </row>
+    <row r="156" spans="1:8" ht="33">
+      <c r="A156" s="2">
+        <v>155</v>
+      </c>
+      <c r="B156" s="5">
+        <v>46234</v>
+      </c>
+      <c r="C156" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="D156" s="10" t="s">
+        <v>277</v>
+      </c>
+      <c r="E156" s="7" t="s">
+        <v>238</v>
+      </c>
+      <c r="F156" s="6" t="s">
+        <v>236</v>
+      </c>
+      <c r="G156" s="3"/>
+      <c r="H156" s="3"/>
+    </row>
+    <row r="157" spans="1:8">
+      <c r="A157" s="2">
+        <v>156</v>
+      </c>
+      <c r="B157" s="12">
+        <v>46234</v>
+      </c>
+      <c r="C157" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="D157" s="6" t="s">
+        <v>357</v>
+      </c>
+      <c r="E157" s="7" t="s">
+        <v>327</v>
+      </c>
+      <c r="F157" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="G157" s="3"/>
+      <c r="H157" s="3"/>
+    </row>
+    <row r="158" spans="1:8">
+      <c r="A158" s="2">
+        <v>157</v>
+      </c>
+      <c r="B158" s="16">
+        <v>46237</v>
+      </c>
+      <c r="C158" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="D158" s="17" t="s">
+        <v>278</v>
+      </c>
+      <c r="E158" s="18" t="s">
+        <v>194</v>
+      </c>
+      <c r="F158" s="19" t="s">
+        <v>196</v>
+      </c>
+      <c r="G158" s="3"/>
+      <c r="H158" s="3"/>
+    </row>
+    <row r="159" spans="1:8">
+      <c r="A159" s="2">
+        <v>158</v>
+      </c>
+      <c r="B159" s="16">
+        <v>46237</v>
+      </c>
+      <c r="C159" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="D159" s="17" t="s">
+        <v>279</v>
+      </c>
+      <c r="E159" s="18" t="s">
+        <v>194</v>
+      </c>
+      <c r="F159" s="18" t="s">
+        <v>323</v>
+      </c>
+      <c r="G159" s="3"/>
+      <c r="H159" s="3"/>
+    </row>
+    <row r="160" spans="1:8">
+      <c r="A160" s="2">
+        <v>159</v>
+      </c>
+      <c r="B160" s="16">
+        <v>46238</v>
+      </c>
+      <c r="C160" s="1" t="s">
+        <v>446</v>
+      </c>
+      <c r="D160" s="20" t="s">
+        <v>382</v>
+      </c>
+      <c r="E160" s="18" t="s">
+        <v>324</v>
+      </c>
+      <c r="F160" s="18" t="s">
+        <v>443</v>
+      </c>
+      <c r="G160" s="3"/>
+      <c r="H160" s="3"/>
+    </row>
+    <row r="161" spans="1:8">
+      <c r="A161" s="2">
+        <v>160</v>
+      </c>
+      <c r="B161" s="16">
+        <v>46238</v>
+      </c>
+      <c r="C161" s="1" t="s">
+        <v>447</v>
+      </c>
+      <c r="D161" s="20" t="s">
+        <v>383</v>
+      </c>
+      <c r="E161" s="18" t="s">
+        <v>324</v>
+      </c>
+      <c r="F161" s="18" t="s">
+        <v>443</v>
+      </c>
+      <c r="G161" s="3"/>
+      <c r="H161" s="3"/>
+    </row>
+    <row r="162" spans="1:8">
+      <c r="A162" s="2">
+        <v>161</v>
+      </c>
+      <c r="B162" s="16">
+        <v>46238</v>
+      </c>
+      <c r="C162" s="1" t="s">
+        <v>448</v>
+      </c>
+      <c r="D162" s="20" t="s">
+        <v>384</v>
+      </c>
+      <c r="E162" s="18" t="s">
+        <v>324</v>
+      </c>
+      <c r="F162" s="18" t="s">
+        <v>443</v>
+      </c>
+      <c r="G162" s="3"/>
+      <c r="H162" s="3"/>
+    </row>
+    <row r="163" spans="1:8">
+      <c r="A163" s="2">
+        <v>162</v>
+      </c>
+      <c r="B163" s="21">
+        <v>46238</v>
+      </c>
+      <c r="C163" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="D163" s="20" t="s">
+        <v>385</v>
+      </c>
+      <c r="E163" s="18" t="s">
+        <v>194</v>
+      </c>
+      <c r="F163" s="18" t="s">
+        <v>196</v>
+      </c>
+      <c r="G163" s="3"/>
+      <c r="H163" s="3"/>
+    </row>
+    <row r="164" spans="1:8">
+      <c r="A164" s="2">
+        <v>163</v>
+      </c>
+      <c r="B164" s="16">
+        <v>46239</v>
+      </c>
+      <c r="C164" s="1" t="s">
+        <v>449</v>
+      </c>
+      <c r="D164" s="20" t="s">
+        <v>386</v>
+      </c>
+      <c r="E164" s="18" t="s">
+        <v>324</v>
+      </c>
+      <c r="F164" s="18" t="s">
+        <v>221</v>
+      </c>
+      <c r="G164" s="3"/>
+      <c r="H164" s="3"/>
+    </row>
+    <row r="165" spans="1:8">
+      <c r="A165" s="2">
+        <v>164</v>
+      </c>
+      <c r="B165" s="21">
+        <v>46239</v>
+      </c>
+      <c r="C165" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="D165" s="20" t="s">
+        <v>387</v>
+      </c>
+      <c r="E165" s="18" t="s">
+        <v>194</v>
+      </c>
+      <c r="F165" s="18" t="s">
+        <v>236</v>
+      </c>
+      <c r="G165" s="3"/>
+      <c r="H165" s="3"/>
+    </row>
+    <row r="166" spans="1:8">
+      <c r="A166" s="2">
+        <v>165</v>
+      </c>
+      <c r="B166" s="16">
+        <v>46239</v>
+      </c>
+      <c r="C166" s="1" t="s">
+        <v>451</v>
+      </c>
+      <c r="D166" s="20" t="s">
+        <v>388</v>
+      </c>
+      <c r="E166" s="18" t="s">
+        <v>325</v>
+      </c>
+      <c r="F166" s="18" t="s">
+        <v>196</v>
+      </c>
+      <c r="G166" s="3"/>
+      <c r="H166" s="3"/>
+    </row>
+    <row r="167" spans="1:8">
+      <c r="A167" s="2">
+        <v>166</v>
+      </c>
+      <c r="B167" s="16">
+        <v>46239</v>
+      </c>
+      <c r="C167" s="1" t="s">
+        <v>452</v>
+      </c>
+      <c r="D167" s="20" t="s">
+        <v>389</v>
+      </c>
+      <c r="E167" s="18" t="s">
+        <v>325</v>
+      </c>
+      <c r="F167" s="18" t="s">
+        <v>196</v>
+      </c>
+      <c r="G167" s="3"/>
+      <c r="H167" s="3"/>
+    </row>
+    <row r="168" spans="1:8">
+      <c r="A168" s="2">
+        <v>167</v>
+      </c>
+      <c r="B168" s="16">
+        <v>46239</v>
+      </c>
+      <c r="C168" s="1" t="s">
+        <v>453</v>
+      </c>
+      <c r="D168" s="20" t="s">
+        <v>390</v>
+      </c>
+      <c r="E168" s="18" t="s">
+        <v>325</v>
+      </c>
+      <c r="F168" s="18" t="s">
+        <v>196</v>
+      </c>
+      <c r="G168" s="3"/>
+      <c r="H168" s="3"/>
+    </row>
+    <row r="169" spans="1:8">
+      <c r="A169" s="2">
+        <v>168</v>
+      </c>
+      <c r="B169" s="16">
+        <v>46239</v>
+      </c>
+      <c r="C169" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="D169" s="20" t="s">
+        <v>391</v>
+      </c>
+      <c r="E169" s="18" t="s">
+        <v>325</v>
+      </c>
+      <c r="F169" s="18" t="s">
+        <v>443</v>
+      </c>
+      <c r="G169" s="3"/>
+      <c r="H169" s="3"/>
+    </row>
+    <row r="170" spans="1:8">
+      <c r="A170" s="2">
+        <v>169</v>
+      </c>
+      <c r="B170" s="16">
+        <v>46239</v>
+      </c>
+      <c r="C170" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="D170" s="20" t="s">
+        <v>392</v>
+      </c>
+      <c r="E170" s="18" t="s">
+        <v>325</v>
+      </c>
+      <c r="F170" s="18" t="s">
+        <v>443</v>
+      </c>
+      <c r="G170" s="3"/>
+      <c r="H170" s="3"/>
+    </row>
+    <row r="171" spans="1:8">
+      <c r="A171" s="2">
+        <v>170</v>
+      </c>
+      <c r="B171" s="16">
+        <v>46239</v>
+      </c>
+      <c r="C171" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="D171" s="20" t="s">
+        <v>393</v>
+      </c>
+      <c r="E171" s="18" t="s">
+        <v>325</v>
+      </c>
+      <c r="F171" s="18" t="s">
+        <v>443</v>
+      </c>
+      <c r="G171" s="3"/>
+      <c r="H171" s="3"/>
+    </row>
+    <row r="172" spans="1:8">
+      <c r="A172" s="2">
+        <v>171</v>
+      </c>
+      <c r="B172" s="16">
+        <v>46239</v>
+      </c>
+      <c r="C172" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="D172" s="20" t="s">
+        <v>394</v>
+      </c>
+      <c r="E172" s="18" t="s">
+        <v>325</v>
+      </c>
+      <c r="F172" s="18" t="s">
+        <v>443</v>
+      </c>
+      <c r="G172" s="3"/>
+      <c r="H172" s="3"/>
+    </row>
+    <row r="173" spans="1:8">
+      <c r="A173" s="2">
+        <v>172</v>
+      </c>
+      <c r="B173" s="16">
+        <v>46239</v>
+      </c>
+      <c r="C173" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="D173" s="20" t="s">
+        <v>395</v>
+      </c>
+      <c r="E173" s="18" t="s">
+        <v>325</v>
+      </c>
+      <c r="F173" s="18" t="s">
+        <v>443</v>
+      </c>
+      <c r="G173" s="3"/>
+      <c r="H173" s="3"/>
+    </row>
+    <row r="174" spans="1:8">
+      <c r="A174" s="2">
+        <v>173</v>
+      </c>
+      <c r="B174" s="16">
+        <v>46239</v>
+      </c>
+      <c r="C174" s="1" t="s">
+        <v>454</v>
+      </c>
+      <c r="D174" s="20" t="s">
+        <v>396</v>
+      </c>
+      <c r="E174" s="18" t="s">
+        <v>325</v>
+      </c>
+      <c r="F174" s="18" t="s">
+        <v>443</v>
+      </c>
+      <c r="G174" s="3"/>
+      <c r="H174" s="3"/>
+    </row>
+    <row r="175" spans="1:8">
+      <c r="A175" s="2">
+        <v>174</v>
+      </c>
+      <c r="B175" s="16">
+        <v>46239</v>
+      </c>
+      <c r="C175" s="1" t="s">
+        <v>454</v>
+      </c>
+      <c r="D175" s="20" t="s">
+        <v>397</v>
+      </c>
+      <c r="E175" s="18" t="s">
+        <v>325</v>
+      </c>
+      <c r="F175" s="18" t="s">
+        <v>443</v>
+      </c>
+      <c r="G175" s="3"/>
+      <c r="H175" s="3"/>
+    </row>
+    <row r="176" spans="1:8">
+      <c r="A176" s="2">
+        <v>175</v>
+      </c>
+      <c r="B176" s="16">
+        <v>46239</v>
+      </c>
+      <c r="C176" s="1" t="s">
+        <v>454</v>
+      </c>
+      <c r="D176" s="20" t="s">
+        <v>398</v>
+      </c>
+      <c r="E176" s="18" t="s">
+        <v>325</v>
+      </c>
+      <c r="F176" s="18" t="s">
+        <v>443</v>
+      </c>
+      <c r="G176" s="3"/>
+      <c r="H176" s="3"/>
+    </row>
+    <row r="177" spans="1:8">
+      <c r="A177" s="2">
+        <v>176</v>
+      </c>
+      <c r="B177" s="16">
+        <v>46239</v>
+      </c>
+      <c r="C177" s="1" t="s">
+        <v>455</v>
+      </c>
+      <c r="D177" s="20" t="s">
+        <v>399</v>
+      </c>
+      <c r="E177" s="18" t="s">
+        <v>325</v>
+      </c>
+      <c r="F177" s="18" t="s">
+        <v>443</v>
+      </c>
+      <c r="G177" s="3"/>
+      <c r="H177" s="3"/>
+    </row>
+    <row r="178" spans="1:8">
+      <c r="A178" s="2">
+        <v>177</v>
+      </c>
+      <c r="B178" s="16">
+        <v>46239</v>
+      </c>
+      <c r="C178" s="1" t="s">
+        <v>453</v>
+      </c>
+      <c r="D178" s="20" t="s">
+        <v>400</v>
+      </c>
+      <c r="E178" s="18" t="s">
+        <v>325</v>
+      </c>
+      <c r="F178" s="18" t="s">
+        <v>323</v>
+      </c>
+      <c r="G178" s="3"/>
+      <c r="H178" s="3"/>
+    </row>
+    <row r="179" spans="1:8">
+      <c r="A179" s="2">
+        <v>178</v>
+      </c>
+      <c r="B179" s="21">
+        <v>46240</v>
+      </c>
+      <c r="C179" s="1" t="s">
+        <v>456</v>
+      </c>
+      <c r="D179" s="20" t="s">
+        <v>401</v>
+      </c>
+      <c r="E179" s="18" t="s">
+        <v>194</v>
+      </c>
+      <c r="F179" s="18" t="s">
+        <v>236</v>
+      </c>
+      <c r="G179" s="3"/>
+      <c r="H179" s="3"/>
+    </row>
+    <row r="180" spans="1:8">
+      <c r="A180" s="2">
+        <v>179</v>
+      </c>
+      <c r="B180" s="21">
+        <v>46244</v>
+      </c>
+      <c r="C180" s="1" t="s">
+        <v>457</v>
+      </c>
+      <c r="D180" s="20" t="s">
+        <v>402</v>
+      </c>
+      <c r="E180" s="18" t="s">
+        <v>194</v>
+      </c>
+      <c r="F180" s="18" t="s">
+        <v>196</v>
+      </c>
+      <c r="G180" s="3"/>
+      <c r="H180" s="3"/>
+    </row>
+    <row r="181" spans="1:8">
+      <c r="A181" s="2">
+        <v>180</v>
+      </c>
+      <c r="B181" s="21">
+        <v>46244</v>
+      </c>
+      <c r="C181" s="1" t="s">
+        <v>458</v>
+      </c>
+      <c r="D181" s="20" t="s">
+        <v>403</v>
+      </c>
+      <c r="E181" s="18" t="s">
+        <v>238</v>
+      </c>
+      <c r="F181" s="18" t="s">
+        <v>196</v>
+      </c>
+      <c r="G181" s="3"/>
+      <c r="H181" s="3"/>
+    </row>
+    <row r="182" spans="1:8">
+      <c r="A182" s="2">
+        <v>181</v>
+      </c>
+      <c r="B182" s="21">
+        <v>46244</v>
+      </c>
+      <c r="C182" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="D182" s="20" t="s">
+        <v>404</v>
+      </c>
+      <c r="E182" s="18" t="s">
+        <v>238</v>
+      </c>
+      <c r="F182" s="18" t="s">
+        <v>236</v>
+      </c>
+      <c r="G182" s="3"/>
+      <c r="H182" s="3"/>
+    </row>
+    <row r="183" spans="1:8">
+      <c r="A183" s="2">
+        <v>182</v>
+      </c>
+      <c r="B183" s="21">
+        <v>46244</v>
+      </c>
+      <c r="C183" s="1" t="s">
+        <v>459</v>
+      </c>
+      <c r="D183" s="20" t="s">
+        <v>405</v>
+      </c>
+      <c r="E183" s="18" t="s">
+        <v>238</v>
+      </c>
+      <c r="F183" s="18" t="s">
+        <v>196</v>
+      </c>
+      <c r="G183" s="3"/>
+      <c r="H183" s="3"/>
+    </row>
+    <row r="184" spans="1:8">
+      <c r="A184" s="2">
+        <v>183</v>
+      </c>
+      <c r="B184" s="21">
+        <v>46244</v>
+      </c>
+      <c r="C184" s="1" t="s">
+        <v>460</v>
+      </c>
+      <c r="D184" s="20" t="s">
+        <v>406</v>
+      </c>
+      <c r="E184" s="18" t="s">
+        <v>238</v>
+      </c>
+      <c r="F184" s="18" t="s">
+        <v>196</v>
+      </c>
+      <c r="G184" s="3"/>
+      <c r="H184" s="3"/>
+    </row>
+    <row r="185" spans="1:8">
+      <c r="A185" s="2">
+        <v>184</v>
+      </c>
+      <c r="B185" s="21">
+        <v>46244</v>
+      </c>
+      <c r="C185" s="1" t="s">
+        <v>461</v>
+      </c>
+      <c r="D185" s="20" t="s">
+        <v>407</v>
+      </c>
+      <c r="E185" s="18" t="s">
+        <v>238</v>
+      </c>
+      <c r="F185" s="18" t="s">
+        <v>196</v>
+      </c>
+      <c r="G185" s="3"/>
+      <c r="H185" s="3"/>
+    </row>
+    <row r="186" spans="1:8">
+      <c r="A186" s="2">
+        <v>185</v>
+      </c>
+      <c r="B186" s="21">
+        <v>46244</v>
+      </c>
+      <c r="C186" s="22" t="s">
+        <v>462</v>
+      </c>
+      <c r="D186" s="20" t="s">
+        <v>408</v>
+      </c>
+      <c r="E186" s="18" t="s">
+        <v>238</v>
+      </c>
+      <c r="F186" s="18" t="s">
+        <v>196</v>
+      </c>
+      <c r="G186" s="3"/>
+      <c r="H186" s="3"/>
+    </row>
+    <row r="187" spans="1:8">
+      <c r="A187" s="2">
+        <v>186</v>
+      </c>
+      <c r="B187" s="16">
+        <v>46244</v>
+      </c>
+      <c r="C187" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="D187" s="17" t="s">
+        <v>409</v>
+      </c>
+      <c r="E187" s="18" t="s">
+        <v>327</v>
+      </c>
+      <c r="F187" s="18" t="s">
+        <v>196</v>
+      </c>
+      <c r="G187" s="3"/>
+      <c r="H187" s="3"/>
+    </row>
+    <row r="188" spans="1:8">
+      <c r="A188" s="2">
+        <v>187</v>
+      </c>
+      <c r="B188" s="16">
+        <v>46244</v>
+      </c>
+      <c r="C188" s="1" t="s">
+        <v>463</v>
+      </c>
+      <c r="D188" s="20" t="s">
+        <v>410</v>
+      </c>
+      <c r="E188" s="18" t="s">
+        <v>325</v>
+      </c>
+      <c r="F188" s="18" t="s">
+        <v>443</v>
+      </c>
+      <c r="G188" s="3"/>
+      <c r="H188" s="3"/>
+    </row>
+    <row r="189" spans="1:8">
+      <c r="A189" s="2">
+        <v>188</v>
+      </c>
+      <c r="B189" s="16">
+        <v>46244</v>
+      </c>
+      <c r="C189" s="1" t="s">
+        <v>464</v>
+      </c>
+      <c r="D189" s="20" t="s">
+        <v>411</v>
+      </c>
+      <c r="E189" s="18" t="s">
+        <v>325</v>
+      </c>
+      <c r="F189" s="18" t="s">
+        <v>443</v>
+      </c>
+      <c r="G189" s="3"/>
+      <c r="H189" s="3"/>
+    </row>
+    <row r="190" spans="1:8">
+      <c r="A190" s="2">
+        <v>189</v>
+      </c>
+      <c r="B190" s="16">
+        <v>46244</v>
+      </c>
+      <c r="C190" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="D190" s="20" t="s">
+        <v>412</v>
+      </c>
+      <c r="E190" s="18" t="s">
+        <v>325</v>
+      </c>
+      <c r="F190" s="18" t="s">
+        <v>444</v>
+      </c>
+      <c r="G190" s="3"/>
+      <c r="H190" s="3"/>
+    </row>
+    <row r="191" spans="1:8">
+      <c r="A191" s="2">
+        <v>190</v>
+      </c>
+      <c r="B191" s="16">
+        <v>46244</v>
+      </c>
+      <c r="C191" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="D191" s="20" t="s">
+        <v>413</v>
+      </c>
+      <c r="E191" s="18" t="s">
+        <v>325</v>
+      </c>
+      <c r="F191" s="18" t="s">
+        <v>196</v>
+      </c>
+      <c r="G191" s="3"/>
+      <c r="H191" s="3"/>
+    </row>
+    <row r="192" spans="1:8">
+      <c r="A192" s="2">
+        <v>191</v>
+      </c>
+      <c r="B192" s="16">
+        <v>46244</v>
+      </c>
+      <c r="C192" s="1" t="s">
+        <v>465</v>
+      </c>
+      <c r="D192" s="20" t="s">
+        <v>414</v>
+      </c>
+      <c r="E192" s="18" t="s">
+        <v>325</v>
+      </c>
+      <c r="F192" s="18" t="s">
+        <v>443</v>
+      </c>
+      <c r="G192" s="3"/>
+      <c r="H192" s="3"/>
+    </row>
+    <row r="193" spans="1:8">
+      <c r="A193" s="2">
+        <v>192</v>
+      </c>
+      <c r="B193" s="16">
+        <v>46244</v>
+      </c>
+      <c r="C193" s="1" t="s">
+        <v>465</v>
+      </c>
+      <c r="D193" s="20" t="s">
+        <v>415</v>
+      </c>
+      <c r="E193" s="18" t="s">
+        <v>325</v>
+      </c>
+      <c r="F193" s="18" t="s">
+        <v>196</v>
+      </c>
+      <c r="G193" s="3"/>
+      <c r="H193" s="3"/>
+    </row>
+    <row r="194" spans="1:8">
+      <c r="A194" s="2">
+        <v>193</v>
+      </c>
+      <c r="B194" s="21">
+        <v>46245</v>
+      </c>
+      <c r="C194" s="1" t="s">
+        <v>466</v>
+      </c>
+      <c r="D194" s="20" t="s">
+        <v>416</v>
+      </c>
+      <c r="E194" s="18" t="s">
+        <v>238</v>
+      </c>
+      <c r="F194" s="18" t="s">
+        <v>236</v>
+      </c>
+      <c r="G194" s="3"/>
+      <c r="H194" s="3"/>
+    </row>
+    <row r="195" spans="1:8">
+      <c r="A195" s="2">
+        <v>194</v>
+      </c>
+      <c r="B195" s="21">
+        <v>46246</v>
+      </c>
+      <c r="C195" s="1" t="s">
+        <v>467</v>
+      </c>
+      <c r="D195" s="20" t="s">
+        <v>417</v>
+      </c>
+      <c r="E195" s="18" t="s">
+        <v>238</v>
+      </c>
+      <c r="F195" s="18" t="s">
+        <v>221</v>
+      </c>
+      <c r="G195" s="3"/>
+      <c r="H195" s="3"/>
+    </row>
+    <row r="196" spans="1:8" ht="33">
+      <c r="A196" s="2">
+        <v>195</v>
+      </c>
+      <c r="B196" s="21">
+        <v>46247</v>
+      </c>
+      <c r="C196" s="1" t="s">
+        <v>468</v>
+      </c>
+      <c r="D196" s="20" t="s">
+        <v>418</v>
+      </c>
+      <c r="E196" s="18" t="s">
+        <v>445</v>
+      </c>
+      <c r="F196" s="18" t="s">
+        <v>196</v>
+      </c>
+      <c r="G196" s="3"/>
+      <c r="H196" s="3"/>
+    </row>
+    <row r="197" spans="1:8">
+      <c r="A197" s="2">
+        <v>196</v>
+      </c>
+      <c r="B197" s="16">
+        <v>46247</v>
+      </c>
+      <c r="C197" s="1" t="s">
+        <v>469</v>
+      </c>
+      <c r="D197" s="20" t="s">
+        <v>419</v>
+      </c>
+      <c r="E197" s="18" t="s">
+        <v>327</v>
+      </c>
+      <c r="F197" s="18" t="s">
+        <v>221</v>
+      </c>
+      <c r="G197" s="3"/>
+      <c r="H197" s="3"/>
+    </row>
+    <row r="198" spans="1:8">
+      <c r="A198" s="2">
+        <v>197</v>
+      </c>
+      <c r="B198" s="16">
+        <v>46247</v>
+      </c>
+      <c r="C198" s="1" t="s">
+        <v>455</v>
+      </c>
+      <c r="D198" s="20" t="s">
+        <v>420</v>
+      </c>
+      <c r="E198" s="18" t="s">
+        <v>325</v>
+      </c>
+      <c r="F198" s="18" t="s">
+        <v>443</v>
+      </c>
+      <c r="G198" s="3"/>
+      <c r="H198" s="3"/>
+    </row>
+    <row r="199" spans="1:8">
+      <c r="A199" s="2">
+        <v>198</v>
+      </c>
+      <c r="B199" s="16">
+        <v>46247</v>
+      </c>
+      <c r="C199" s="1" t="s">
+        <v>455</v>
+      </c>
+      <c r="D199" s="20" t="s">
+        <v>421</v>
+      </c>
+      <c r="E199" s="18" t="s">
+        <v>325</v>
+      </c>
+      <c r="F199" s="18" t="s">
+        <v>443</v>
+      </c>
+      <c r="G199" s="3"/>
+      <c r="H199" s="3"/>
+    </row>
+    <row r="200" spans="1:8">
+      <c r="A200" s="2">
+        <v>199</v>
+      </c>
+      <c r="B200" s="16">
+        <v>46247</v>
+      </c>
+      <c r="C200" s="1" t="s">
+        <v>455</v>
+      </c>
+      <c r="D200" s="20" t="s">
+        <v>422</v>
+      </c>
+      <c r="E200" s="18" t="s">
+        <v>325</v>
+      </c>
+      <c r="F200" s="18" t="s">
+        <v>443</v>
+      </c>
+      <c r="G200" s="3"/>
+      <c r="H200" s="3"/>
+    </row>
+    <row r="201" spans="1:8">
+      <c r="A201" s="2">
+        <v>200</v>
+      </c>
+      <c r="B201" s="16">
+        <v>46247</v>
+      </c>
+      <c r="C201" s="1" t="s">
+        <v>455</v>
+      </c>
+      <c r="D201" s="20" t="s">
+        <v>423</v>
+      </c>
+      <c r="E201" s="18" t="s">
+        <v>325</v>
+      </c>
+      <c r="F201" s="18" t="s">
+        <v>443</v>
+      </c>
+      <c r="G201" s="3"/>
+      <c r="H201" s="3"/>
+    </row>
+    <row r="202" spans="1:8">
+      <c r="A202" s="2">
+        <v>201</v>
+      </c>
+      <c r="B202" s="16">
+        <v>46248</v>
+      </c>
+      <c r="C202" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="D202" s="20" t="s">
+        <v>424</v>
+      </c>
+      <c r="E202" s="18" t="s">
+        <v>326</v>
+      </c>
+      <c r="F202" s="18" t="s">
+        <v>443</v>
+      </c>
+      <c r="G202" s="3"/>
+      <c r="H202" s="3"/>
+    </row>
+    <row r="203" spans="1:8">
+      <c r="A203" s="2">
+        <v>202</v>
+      </c>
+      <c r="B203" s="21">
+        <v>46248</v>
+      </c>
+      <c r="C203" s="1" t="s">
+        <v>470</v>
+      </c>
+      <c r="D203" s="20" t="s">
+        <v>425</v>
+      </c>
+      <c r="E203" s="18" t="s">
+        <v>238</v>
+      </c>
+      <c r="F203" s="18" t="s">
+        <v>236</v>
+      </c>
+      <c r="G203" s="3"/>
+      <c r="H203" s="3"/>
+    </row>
+    <row r="204" spans="1:8">
+      <c r="A204" s="2">
+        <v>203</v>
+      </c>
+      <c r="B204" s="16">
+        <v>46248</v>
+      </c>
+      <c r="C204" s="1" t="s">
+        <v>471</v>
+      </c>
+      <c r="D204" s="20" t="s">
+        <v>426</v>
+      </c>
+      <c r="E204" s="18" t="s">
+        <v>327</v>
+      </c>
+      <c r="F204" s="18" t="s">
+        <v>196</v>
+      </c>
+      <c r="G204" s="3"/>
+      <c r="H204" s="3"/>
+    </row>
+    <row r="205" spans="1:8">
+      <c r="A205" s="2">
+        <v>204</v>
+      </c>
+      <c r="B205" s="16">
+        <v>46248</v>
+      </c>
+      <c r="C205" s="1" t="s">
+        <v>472</v>
+      </c>
+      <c r="D205" s="20" t="s">
+        <v>427</v>
+      </c>
+      <c r="E205" s="18" t="s">
+        <v>325</v>
+      </c>
+      <c r="F205" s="18" t="s">
+        <v>196</v>
+      </c>
+      <c r="G205" s="3"/>
+      <c r="H205" s="3"/>
+    </row>
+    <row r="206" spans="1:8" ht="33">
+      <c r="A206" s="2">
+        <v>205</v>
+      </c>
+      <c r="B206" s="21">
+        <v>46254</v>
+      </c>
+      <c r="C206" s="1" t="s">
+        <v>468</v>
+      </c>
+      <c r="D206" s="20" t="s">
+        <v>428</v>
+      </c>
+      <c r="E206" s="18" t="s">
+        <v>445</v>
+      </c>
+      <c r="F206" s="18" t="s">
+        <v>196</v>
+      </c>
+      <c r="G206" s="3"/>
+      <c r="H206" s="3"/>
+    </row>
+    <row r="207" spans="1:8">
+      <c r="A207" s="2">
         <v>206</v>
       </c>
-      <c r="F119" s="14" t="s">
+      <c r="B207" s="16">
+        <v>46254</v>
+      </c>
+      <c r="C207" s="1" t="s">
+        <v>372</v>
+      </c>
+      <c r="D207" s="20" t="s">
+        <v>429</v>
+      </c>
+      <c r="E207" s="18" t="s">
+        <v>325</v>
+      </c>
+      <c r="F207" s="18" t="s">
+        <v>443</v>
+      </c>
+      <c r="G207" s="3"/>
+      <c r="H207" s="3"/>
+    </row>
+    <row r="208" spans="1:8">
+      <c r="A208" s="2">
+        <v>207</v>
+      </c>
+      <c r="B208" s="16">
+        <v>46254</v>
+      </c>
+      <c r="C208" s="1" t="s">
+        <v>372</v>
+      </c>
+      <c r="D208" s="20" t="s">
+        <v>430</v>
+      </c>
+      <c r="E208" s="18" t="s">
+        <v>325</v>
+      </c>
+      <c r="F208" s="18" t="s">
+        <v>443</v>
+      </c>
+      <c r="G208" s="3"/>
+      <c r="H208" s="3"/>
+    </row>
+    <row r="209" spans="1:8">
+      <c r="A209" s="2">
+        <v>208</v>
+      </c>
+      <c r="B209" s="16">
+        <v>46254</v>
+      </c>
+      <c r="C209" s="1" t="s">
+        <v>473</v>
+      </c>
+      <c r="D209" s="20" t="s">
+        <v>431</v>
+      </c>
+      <c r="E209" s="18" t="s">
+        <v>325</v>
+      </c>
+      <c r="F209" s="18" t="s">
+        <v>443</v>
+      </c>
+      <c r="G209" s="3"/>
+      <c r="H209" s="3"/>
+    </row>
+    <row r="210" spans="1:8">
+      <c r="A210" s="2">
+        <v>209</v>
+      </c>
+      <c r="B210" s="16">
+        <v>46254</v>
+      </c>
+      <c r="C210" s="1" t="s">
+        <v>474</v>
+      </c>
+      <c r="D210" s="20" t="s">
+        <v>432</v>
+      </c>
+      <c r="E210" s="18" t="s">
+        <v>325</v>
+      </c>
+      <c r="F210" s="18" t="s">
+        <v>443</v>
+      </c>
+      <c r="G210" s="3"/>
+      <c r="H210" s="3"/>
+    </row>
+    <row r="211" spans="1:8">
+      <c r="A211" s="2">
+        <v>210</v>
+      </c>
+      <c r="B211" s="16">
+        <v>46254</v>
+      </c>
+      <c r="C211" s="1" t="s">
+        <v>475</v>
+      </c>
+      <c r="D211" s="20" t="s">
+        <v>433</v>
+      </c>
+      <c r="E211" s="18" t="s">
+        <v>325</v>
+      </c>
+      <c r="F211" s="18" t="s">
+        <v>443</v>
+      </c>
+      <c r="G211" s="3"/>
+      <c r="H211" s="3"/>
+    </row>
+    <row r="212" spans="1:8">
+      <c r="A212" s="2">
+        <v>211</v>
+      </c>
+      <c r="B212" s="16">
+        <v>46254</v>
+      </c>
+      <c r="C212" s="1" t="s">
+        <v>476</v>
+      </c>
+      <c r="D212" s="20" t="s">
+        <v>434</v>
+      </c>
+      <c r="E212" s="18" t="s">
+        <v>325</v>
+      </c>
+      <c r="F212" s="18" t="s">
+        <v>443</v>
+      </c>
+      <c r="G212" s="3"/>
+      <c r="H212" s="3"/>
+    </row>
+    <row r="213" spans="1:8" ht="33">
+      <c r="A213" s="2">
+        <v>212</v>
+      </c>
+      <c r="B213" s="21">
+        <v>46255</v>
+      </c>
+      <c r="C213" s="1" t="s">
+        <v>477</v>
+      </c>
+      <c r="D213" s="20" t="s">
+        <v>435</v>
+      </c>
+      <c r="E213" s="18" t="s">
+        <v>194</v>
+      </c>
+      <c r="F213" s="18" t="s">
         <v>196</v>
       </c>
-      <c r="G119" s="7"/>
-    </row>
-    <row r="120" spans="1:7">
-      <c r="A120" s="7">
-        <v>119</v>
-      </c>
-      <c r="B120" s="11">
-        <v>46218</v>
-      </c>
-      <c r="C120" s="10" t="s">
-        <v>300</v>
-      </c>
-      <c r="D120" s="16" t="s">
-        <v>331</v>
-      </c>
-      <c r="E120" s="17" t="s">
-        <v>237</v>
-      </c>
-      <c r="F120" s="14" t="s">
+      <c r="G213" s="3"/>
+      <c r="H213" s="3"/>
+    </row>
+    <row r="214" spans="1:8">
+      <c r="A214" s="2">
+        <v>213</v>
+      </c>
+      <c r="B214" s="21">
+        <v>46255</v>
+      </c>
+      <c r="C214" s="1" t="s">
+        <v>478</v>
+      </c>
+      <c r="D214" s="20" t="s">
+        <v>436</v>
+      </c>
+      <c r="E214" s="18" t="s">
+        <v>194</v>
+      </c>
+      <c r="F214" s="18" t="s">
+        <v>196</v>
+      </c>
+      <c r="G214" s="3"/>
+      <c r="H214" s="3"/>
+    </row>
+    <row r="215" spans="1:8" ht="33">
+      <c r="A215" s="2">
+        <v>214</v>
+      </c>
+      <c r="B215" s="21">
+        <v>46258</v>
+      </c>
+      <c r="C215" s="1" t="s">
+        <v>468</v>
+      </c>
+      <c r="D215" s="20" t="s">
+        <v>437</v>
+      </c>
+      <c r="E215" s="18" t="s">
+        <v>445</v>
+      </c>
+      <c r="F215" s="18" t="s">
+        <v>196</v>
+      </c>
+      <c r="G215" s="3"/>
+      <c r="H215" s="3"/>
+    </row>
+    <row r="216" spans="1:8">
+      <c r="A216" s="2">
+        <v>215</v>
+      </c>
+      <c r="B216" s="21">
+        <v>46259</v>
+      </c>
+      <c r="C216" s="1" t="s">
+        <v>479</v>
+      </c>
+      <c r="D216" s="20" t="s">
+        <v>438</v>
+      </c>
+      <c r="E216" s="18" t="s">
+        <v>194</v>
+      </c>
+      <c r="F216" s="18" t="s">
+        <v>196</v>
+      </c>
+      <c r="G216" s="3"/>
+      <c r="H216" s="3"/>
+    </row>
+    <row r="217" spans="1:8" ht="33">
+      <c r="A217" s="2">
+        <v>216</v>
+      </c>
+      <c r="B217" s="21">
+        <v>46259</v>
+      </c>
+      <c r="C217" s="1" t="s">
+        <v>480</v>
+      </c>
+      <c r="D217" s="20" t="s">
+        <v>439</v>
+      </c>
+      <c r="E217" s="18" t="s">
+        <v>445</v>
+      </c>
+      <c r="F217" s="18" t="s">
+        <v>196</v>
+      </c>
+      <c r="G217" s="3"/>
+      <c r="H217" s="3"/>
+    </row>
+    <row r="218" spans="1:8" ht="33">
+      <c r="A218" s="2">
+        <v>217</v>
+      </c>
+      <c r="B218" s="21">
+        <v>46261</v>
+      </c>
+      <c r="C218" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="D218" s="20" t="s">
+        <v>440</v>
+      </c>
+      <c r="E218" s="18" t="s">
+        <v>194</v>
+      </c>
+      <c r="F218" s="18" t="s">
+        <v>196</v>
+      </c>
+      <c r="G218" s="3"/>
+      <c r="H218" s="3"/>
+    </row>
+    <row r="219" spans="1:8">
+      <c r="A219" s="2">
+        <v>218</v>
+      </c>
+      <c r="B219" s="16">
+        <v>46261</v>
+      </c>
+      <c r="C219" s="1" t="s">
+        <v>481</v>
+      </c>
+      <c r="D219" s="20" t="s">
+        <v>441</v>
+      </c>
+      <c r="E219" s="18" t="s">
+        <v>327</v>
+      </c>
+      <c r="F219" s="18" t="s">
         <v>236</v>
       </c>
-      <c r="G120" s="7"/>
-    </row>
-    <row r="121" spans="1:7">
-      <c r="A121" s="7">
-        <v>120</v>
-      </c>
-      <c r="B121" s="11">
-        <v>46223</v>
-      </c>
-      <c r="C121" s="10" t="s">
-        <v>361</v>
-      </c>
-      <c r="D121" s="14" t="s">
-        <v>332</v>
-      </c>
-      <c r="E121" s="17" t="s">
-        <v>237</v>
-      </c>
-      <c r="F121" s="14" t="s">
-        <v>236</v>
-      </c>
-      <c r="G121" s="7"/>
-    </row>
-    <row r="122" spans="1:7">
-      <c r="A122" s="7">
-        <v>121</v>
-      </c>
-      <c r="B122" s="12">
-        <v>46223</v>
-      </c>
-      <c r="C122" s="10" t="s">
-        <v>362</v>
-      </c>
-      <c r="D122" s="14" t="s">
-        <v>333</v>
-      </c>
-      <c r="E122" s="17" t="s">
-        <v>325</v>
-      </c>
-      <c r="F122" s="14" t="s">
+      <c r="G219" s="3"/>
+      <c r="H219" s="3"/>
+    </row>
+    <row r="220" spans="1:8">
+      <c r="A220" s="2">
+        <v>219</v>
+      </c>
+      <c r="B220" s="21">
+        <v>46265</v>
+      </c>
+      <c r="C220" s="1" t="s">
+        <v>482</v>
+      </c>
+      <c r="D220" s="20" t="s">
+        <v>442</v>
+      </c>
+      <c r="E220" s="18" t="s">
+        <v>238</v>
+      </c>
+      <c r="F220" s="18" t="s">
         <v>196</v>
       </c>
-      <c r="G122" s="7"/>
-    </row>
-    <row r="123" spans="1:7">
-      <c r="A123" s="7">
-        <v>122</v>
-      </c>
-      <c r="B123" s="12">
-        <v>46223</v>
-      </c>
-      <c r="C123" s="10" t="s">
-        <v>363</v>
-      </c>
-      <c r="D123" s="14" t="s">
-        <v>334</v>
-      </c>
-      <c r="E123" s="17" t="s">
-        <v>325</v>
-      </c>
-      <c r="F123" s="14" t="s">
-        <v>196</v>
-      </c>
-      <c r="G123" s="7"/>
-    </row>
-    <row r="124" spans="1:7">
-      <c r="A124" s="7">
-        <v>123</v>
-      </c>
-      <c r="B124" s="12">
-        <v>46223</v>
-      </c>
-      <c r="C124" s="10" t="s">
-        <v>364</v>
-      </c>
-      <c r="D124" s="14" t="s">
-        <v>335</v>
-      </c>
-      <c r="E124" s="17" t="s">
-        <v>325</v>
-      </c>
-      <c r="F124" s="14" t="s">
-        <v>196</v>
-      </c>
-      <c r="G124" s="7"/>
-    </row>
-    <row r="125" spans="1:7">
-      <c r="A125" s="18">
-        <v>124</v>
-      </c>
-      <c r="B125" s="12">
-        <v>46223</v>
-      </c>
-      <c r="C125" s="10" t="s">
-        <v>365</v>
-      </c>
-      <c r="D125" s="14" t="s">
-        <v>336</v>
-      </c>
-      <c r="E125" s="17" t="s">
-        <v>325</v>
-      </c>
-      <c r="F125" s="14" t="s">
-        <v>236</v>
-      </c>
-      <c r="G125" s="7"/>
-    </row>
-    <row r="126" spans="1:7">
-      <c r="A126" s="18">
-        <v>125</v>
-      </c>
-      <c r="B126" s="12">
-        <v>46223</v>
-      </c>
-      <c r="C126" s="10" t="s">
-        <v>366</v>
-      </c>
-      <c r="D126" s="14" t="s">
-        <v>337</v>
-      </c>
-      <c r="E126" s="17" t="s">
-        <v>325</v>
-      </c>
-      <c r="F126" s="14" t="s">
-        <v>221</v>
-      </c>
-      <c r="G126" s="7"/>
-    </row>
-    <row r="127" spans="1:7">
-      <c r="A127" s="18">
-        <v>126</v>
-      </c>
-      <c r="B127" s="12">
-        <v>46223</v>
-      </c>
-      <c r="C127" s="10" t="s">
-        <v>367</v>
-      </c>
-      <c r="D127" s="14" t="s">
-        <v>338</v>
-      </c>
-      <c r="E127" s="17" t="s">
-        <v>325</v>
-      </c>
-      <c r="F127" s="14" t="s">
-        <v>236</v>
-      </c>
-      <c r="G127" s="7"/>
-    </row>
-    <row r="128" spans="1:7">
-      <c r="A128" s="18">
-        <v>127</v>
-      </c>
-      <c r="B128" s="12">
-        <v>46223</v>
-      </c>
-      <c r="C128" s="10" t="s">
-        <v>368</v>
-      </c>
-      <c r="D128" s="14" t="s">
-        <v>339</v>
-      </c>
-      <c r="E128" s="17" t="s">
-        <v>325</v>
-      </c>
-      <c r="F128" s="14" t="s">
-        <v>236</v>
-      </c>
-      <c r="G128" s="7"/>
-    </row>
-    <row r="129" spans="1:7">
-      <c r="A129" s="18">
-        <v>128</v>
-      </c>
-      <c r="B129" s="12">
-        <v>46223</v>
-      </c>
-      <c r="C129" s="10" t="s">
-        <v>369</v>
-      </c>
-      <c r="D129" s="14" t="s">
-        <v>340</v>
-      </c>
-      <c r="E129" s="17" t="s">
-        <v>325</v>
-      </c>
-      <c r="F129" s="14" t="s">
-        <v>236</v>
-      </c>
-      <c r="G129" s="7"/>
-    </row>
-    <row r="130" spans="1:7">
-      <c r="A130" s="18">
-        <v>129</v>
-      </c>
-      <c r="B130" s="12">
-        <v>46223</v>
-      </c>
-      <c r="C130" s="10" t="s">
-        <v>370</v>
-      </c>
-      <c r="D130" s="14" t="s">
-        <v>341</v>
-      </c>
-      <c r="E130" s="17" t="s">
-        <v>325</v>
-      </c>
-      <c r="F130" s="14" t="s">
-        <v>236</v>
-      </c>
-      <c r="G130" s="7"/>
-    </row>
-    <row r="131" spans="1:7">
-      <c r="A131" s="18">
-        <v>130</v>
-      </c>
-      <c r="B131" s="12">
-        <v>46223</v>
-      </c>
-      <c r="C131" s="10" t="s">
-        <v>371</v>
-      </c>
-      <c r="D131" s="14" t="s">
-        <v>342</v>
-      </c>
-      <c r="E131" s="17" t="s">
-        <v>325</v>
-      </c>
-      <c r="F131" s="14" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="132" spans="1:7">
-      <c r="A132" s="18">
-        <v>131</v>
-      </c>
-      <c r="B132" s="12">
-        <v>46223</v>
-      </c>
-      <c r="C132" s="10" t="s">
-        <v>372</v>
-      </c>
-      <c r="D132" s="14" t="s">
-        <v>343</v>
-      </c>
-      <c r="E132" s="17" t="s">
-        <v>325</v>
-      </c>
-      <c r="F132" s="14" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="133" spans="1:7">
-      <c r="A133" s="18">
-        <v>132</v>
-      </c>
-      <c r="B133" s="12">
-        <v>46224</v>
-      </c>
-      <c r="C133" s="18" t="s">
-        <v>307</v>
-      </c>
-      <c r="D133" s="19" t="s">
-        <v>269</v>
-      </c>
-      <c r="E133" s="17" t="s">
-        <v>238</v>
-      </c>
-      <c r="F133" s="14" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="134" spans="1:7">
-      <c r="A134" s="18">
-        <v>133</v>
-      </c>
-      <c r="B134" s="12">
-        <v>46225</v>
-      </c>
-      <c r="C134" s="20" t="s">
-        <v>308</v>
-      </c>
-      <c r="D134" s="19" t="s">
-        <v>270</v>
-      </c>
-      <c r="E134" s="17" t="s">
-        <v>238</v>
-      </c>
-      <c r="F134" s="14" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="135" spans="1:7">
-      <c r="A135" s="18">
-        <v>134</v>
-      </c>
-      <c r="B135" s="12">
-        <v>46225</v>
-      </c>
-      <c r="C135" s="18" t="s">
-        <v>302</v>
-      </c>
-      <c r="D135" s="21" t="s">
-        <v>271</v>
-      </c>
-      <c r="E135" s="17" t="s">
-        <v>238</v>
-      </c>
-      <c r="F135" s="14" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="136" spans="1:7">
-      <c r="A136" s="18">
-        <v>135</v>
-      </c>
-      <c r="B136" s="11">
-        <v>46225</v>
-      </c>
-      <c r="C136" s="10" t="s">
-        <v>373</v>
-      </c>
-      <c r="D136" s="14" t="s">
-        <v>344</v>
-      </c>
-      <c r="E136" s="17" t="s">
-        <v>326</v>
-      </c>
-      <c r="F136" s="14" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="137" spans="1:7">
-      <c r="A137" s="18">
-        <v>136</v>
-      </c>
-      <c r="B137" s="12">
-        <v>46225</v>
-      </c>
-      <c r="C137" s="10" t="s">
-        <v>374</v>
-      </c>
-      <c r="D137" s="14" t="s">
-        <v>345</v>
-      </c>
-      <c r="E137" s="17" t="s">
-        <v>325</v>
-      </c>
-      <c r="F137" s="14" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="138" spans="1:7">
-      <c r="A138" s="18">
-        <v>137</v>
-      </c>
-      <c r="B138" s="12">
-        <v>46225</v>
-      </c>
-      <c r="C138" s="10" t="s">
-        <v>364</v>
-      </c>
-      <c r="D138" s="14" t="s">
-        <v>346</v>
-      </c>
-      <c r="E138" s="17" t="s">
-        <v>325</v>
-      </c>
-      <c r="F138" s="14" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="139" spans="1:7">
-      <c r="A139" s="18">
-        <v>138</v>
-      </c>
-      <c r="B139" s="12">
-        <v>46225</v>
-      </c>
-      <c r="C139" s="10" t="s">
-        <v>375</v>
-      </c>
-      <c r="D139" s="14" t="s">
-        <v>347</v>
-      </c>
-      <c r="E139" s="17" t="s">
-        <v>325</v>
-      </c>
-      <c r="F139" s="14" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="140" spans="1:7">
-      <c r="A140" s="18">
-        <v>139</v>
-      </c>
-      <c r="B140" s="12">
-        <v>46225</v>
-      </c>
-      <c r="C140" s="10" t="s">
-        <v>376</v>
-      </c>
-      <c r="D140" s="14" t="s">
-        <v>348</v>
-      </c>
-      <c r="E140" s="17" t="s">
-        <v>325</v>
-      </c>
-      <c r="F140" s="14" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="141" spans="1:7">
-      <c r="A141" s="18">
-        <v>140</v>
-      </c>
-      <c r="B141" s="12">
-        <v>46225</v>
-      </c>
-      <c r="C141" s="10" t="s">
-        <v>377</v>
-      </c>
-      <c r="D141" s="14" t="s">
-        <v>349</v>
-      </c>
-      <c r="E141" s="17" t="s">
-        <v>325</v>
-      </c>
-      <c r="F141" s="14" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="142" spans="1:7">
-      <c r="A142" s="18">
-        <v>141</v>
-      </c>
-      <c r="B142" s="12">
-        <v>46225</v>
-      </c>
-      <c r="C142" s="10" t="s">
-        <v>378</v>
-      </c>
-      <c r="D142" s="14" t="s">
-        <v>350</v>
-      </c>
-      <c r="E142" s="17" t="s">
-        <v>325</v>
-      </c>
-      <c r="F142" s="14" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="143" spans="1:7">
-      <c r="A143" s="18">
-        <v>142</v>
-      </c>
-      <c r="B143" s="12">
-        <v>46225</v>
-      </c>
-      <c r="C143" s="10" t="s">
-        <v>378</v>
-      </c>
-      <c r="D143" s="14" t="s">
-        <v>351</v>
-      </c>
-      <c r="E143" s="17" t="s">
-        <v>325</v>
-      </c>
-      <c r="F143" s="14" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="144" spans="1:7">
-      <c r="A144" s="18">
-        <v>143</v>
-      </c>
-      <c r="B144" s="12">
-        <v>46225</v>
-      </c>
-      <c r="C144" s="10" t="s">
-        <v>378</v>
-      </c>
-      <c r="D144" s="22" t="s">
-        <v>352</v>
-      </c>
-      <c r="E144" s="17" t="s">
-        <v>325</v>
-      </c>
-      <c r="F144" s="14" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="145" spans="1:6">
-      <c r="A145" s="18">
-        <v>144</v>
-      </c>
-      <c r="B145" s="12">
-        <v>46225</v>
-      </c>
-      <c r="C145" s="10" t="s">
-        <v>379</v>
-      </c>
-      <c r="D145" s="22" t="s">
-        <v>353</v>
-      </c>
-      <c r="E145" s="17" t="s">
-        <v>325</v>
-      </c>
-      <c r="F145" s="14" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="146" spans="1:6">
-      <c r="A146" s="18">
-        <v>145</v>
-      </c>
-      <c r="B146" s="12">
-        <v>46225</v>
-      </c>
-      <c r="C146" s="10" t="s">
-        <v>380</v>
-      </c>
-      <c r="D146" s="22" t="s">
-        <v>354</v>
-      </c>
-      <c r="E146" s="17" t="s">
-        <v>325</v>
-      </c>
-      <c r="F146" s="14" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="147" spans="1:6">
-      <c r="A147" s="18">
-        <v>146</v>
-      </c>
-      <c r="B147" s="12">
-        <v>46225</v>
-      </c>
-      <c r="C147" s="10" t="s">
-        <v>364</v>
-      </c>
-      <c r="D147" s="14" t="s">
-        <v>355</v>
-      </c>
-      <c r="E147" s="17" t="s">
-        <v>325</v>
-      </c>
-      <c r="F147" s="14" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="148" spans="1:6" ht="49.5">
-      <c r="A148" s="18">
-        <v>147</v>
-      </c>
-      <c r="B148" s="12">
-        <v>46226</v>
-      </c>
-      <c r="C148" s="18" t="s">
-        <v>310</v>
-      </c>
-      <c r="D148" s="21" t="s">
-        <v>272</v>
-      </c>
-      <c r="E148" s="17" t="s">
-        <v>238</v>
-      </c>
-      <c r="F148" s="14" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="149" spans="1:6" ht="33">
-      <c r="A149" s="18">
-        <v>148</v>
-      </c>
-      <c r="B149" s="12">
-        <v>46226</v>
-      </c>
-      <c r="C149" s="18" t="s">
-        <v>311</v>
-      </c>
-      <c r="D149" s="21" t="s">
-        <v>273</v>
-      </c>
-      <c r="E149" s="17" t="s">
-        <v>238</v>
-      </c>
-      <c r="F149" s="14" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="150" spans="1:6">
-      <c r="A150" s="18">
-        <v>149</v>
-      </c>
-      <c r="B150" s="12">
-        <v>46226</v>
-      </c>
-      <c r="C150" s="18" t="s">
-        <v>312</v>
-      </c>
-      <c r="D150" s="21" t="s">
-        <v>274</v>
-      </c>
-      <c r="E150" s="17" t="s">
-        <v>194</v>
-      </c>
-      <c r="F150" s="14" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="151" spans="1:6">
-      <c r="A151" s="18">
-        <v>150</v>
-      </c>
-      <c r="B151" s="11">
-        <v>46226</v>
-      </c>
-      <c r="C151" s="10" t="s">
-        <v>381</v>
-      </c>
-      <c r="D151" s="14" t="s">
-        <v>356</v>
-      </c>
-      <c r="E151" s="17" t="s">
-        <v>237</v>
-      </c>
-      <c r="F151" s="14" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="152" spans="1:6">
-      <c r="A152" s="18">
-        <v>151</v>
-      </c>
-      <c r="B152" s="12">
-        <v>46230</v>
-      </c>
-      <c r="C152" s="18" t="s">
-        <v>313</v>
-      </c>
-      <c r="D152" s="21" t="s">
-        <v>275</v>
-      </c>
-      <c r="E152" s="17" t="s">
-        <v>238</v>
-      </c>
-      <c r="F152" s="14" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="153" spans="1:6">
-      <c r="A153" s="18">
-        <v>152</v>
-      </c>
-      <c r="B153" s="12">
-        <v>46230</v>
-      </c>
-      <c r="C153" s="18" t="s">
-        <v>314</v>
-      </c>
-      <c r="D153" s="21" t="s">
-        <v>316</v>
-      </c>
-      <c r="E153" s="17" t="s">
-        <v>194</v>
-      </c>
-      <c r="F153" s="14" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="154" spans="1:6">
-      <c r="A154" s="18">
-        <v>153</v>
-      </c>
-      <c r="B154" s="12">
-        <v>46230</v>
-      </c>
-      <c r="C154" s="18" t="s">
-        <v>315</v>
-      </c>
-      <c r="D154" s="21" t="s">
-        <v>317</v>
-      </c>
-      <c r="E154" s="17" t="s">
-        <v>194</v>
-      </c>
-      <c r="F154" s="14" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="155" spans="1:6">
-      <c r="A155" s="18">
-        <v>154</v>
-      </c>
-      <c r="B155" s="12">
-        <v>46234</v>
-      </c>
-      <c r="C155" s="18" t="s">
-        <v>318</v>
-      </c>
-      <c r="D155" s="21" t="s">
-        <v>276</v>
-      </c>
-      <c r="E155" s="17" t="s">
-        <v>238</v>
-      </c>
-      <c r="F155" s="14" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="156" spans="1:6" ht="33">
-      <c r="A156" s="18">
-        <v>155</v>
-      </c>
-      <c r="B156" s="12">
-        <v>46234</v>
-      </c>
-      <c r="C156" s="18" t="s">
-        <v>319</v>
-      </c>
-      <c r="D156" s="21" t="s">
-        <v>277</v>
-      </c>
-      <c r="E156" s="17" t="s">
-        <v>238</v>
-      </c>
-      <c r="F156" s="14" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="157" spans="1:6">
-      <c r="A157" s="18">
-        <v>156</v>
-      </c>
-      <c r="B157" s="11">
-        <v>46234</v>
-      </c>
-      <c r="C157" s="10" t="s">
-        <v>301</v>
-      </c>
-      <c r="D157" s="14" t="s">
-        <v>357</v>
-      </c>
-      <c r="E157" s="17" t="s">
-        <v>327</v>
-      </c>
-      <c r="F157" s="14" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="158" spans="1:6">
-      <c r="A158" s="18">
-        <v>157</v>
-      </c>
-      <c r="B158" s="12">
-        <v>46237</v>
-      </c>
-      <c r="C158" s="18" t="s">
-        <v>320</v>
-      </c>
-      <c r="D158" s="21" t="s">
-        <v>278</v>
-      </c>
-      <c r="E158" s="17" t="s">
-        <v>194</v>
-      </c>
-      <c r="F158" s="14" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="159" spans="1:6">
-      <c r="A159" s="18">
-        <v>158</v>
-      </c>
-      <c r="B159" s="12">
-        <v>46237</v>
-      </c>
-      <c r="C159" s="18" t="s">
-        <v>321</v>
-      </c>
-      <c r="D159" s="21" t="s">
-        <v>279</v>
-      </c>
-      <c r="E159" s="17" t="s">
-        <v>194</v>
-      </c>
-      <c r="F159" s="14" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="160" spans="1:6">
-      <c r="F160" s="6"/>
+      <c r="G220" s="3"/>
+      <c r="H220" s="3"/>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B109:F159">
     <sortCondition ref="B109:B159"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
+  <dataValidations count="1">
+    <dataValidation type="list" sqref="F191:F193 F203 F205:F209 F213:F214" xr:uid="{C3438CA2-EDBD-4100-A34A-63C2985D9BBF}">
+      <formula1>"미완료,처리 중,확인 중,완료"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
